--- a/artfynd/A 20531-2025 artfynd.xlsx
+++ b/artfynd/A 20531-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ139"/>
+  <dimension ref="A1:AZ147"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2204,7 +2204,7 @@
         <v>136689343</v>
       </c>
       <c r="B15" t="n">
-        <v>91881</v>
+        <v>91882</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2316,7 +2316,7 @@
         <v>136689338</v>
       </c>
       <c r="B16" t="n">
-        <v>93047</v>
+        <v>93048</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2428,7 +2428,7 @@
         <v>136689333</v>
       </c>
       <c r="B17" t="n">
-        <v>93075</v>
+        <v>93076</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2540,7 +2540,7 @@
         <v>136689344</v>
       </c>
       <c r="B18" t="n">
-        <v>93075</v>
+        <v>93076</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2652,7 +2652,7 @@
         <v>136689356</v>
       </c>
       <c r="B19" t="n">
-        <v>93075</v>
+        <v>93076</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2764,7 +2764,7 @@
         <v>136689357</v>
       </c>
       <c r="B20" t="n">
-        <v>93075</v>
+        <v>93076</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2880,7 +2880,7 @@
         <v>136689363</v>
       </c>
       <c r="B21" t="n">
-        <v>93075</v>
+        <v>93076</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2989,48 +2989,52 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>126480241</v>
+        <v>136699216</v>
       </c>
       <c r="B22" t="n">
-        <v>79327</v>
+        <v>93076</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6425</v>
+        <v>4769</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr"/>
+          <t>(Scop.) Fr.</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="P22" t="inlineStr">
         <is>
           <t>Kölbron, Dlr</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>464760</v>
+        <v>464850</v>
       </c>
       <c r="R22" t="n">
-        <v>6784613</v>
+        <v>6784665</v>
       </c>
       <c r="S22" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -3054,22 +3058,22 @@
       </c>
       <c r="Y22" t="inlineStr">
         <is>
-          <t>2025-07-07</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>09:28</t>
+          <t>10:45</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>2025-07-07</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>09:28</t>
+          <t>10:45</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3089,19 +3093,19 @@
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Håkan Thenander, Bengt Oldhammer, Peter Turander, Birgitta Kvist</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
       <c r="AZ22" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/126480241</t>
+          <t>https://artportalen.se/Sighting/136699216</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>126480512</v>
+        <v>126480241</v>
       </c>
       <c r="B23" t="n">
         <v>79327</v>
@@ -3132,14 +3136,14 @@
       <c r="I23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Kölbron, Kölbron, Dlr</t>
+          <t>Kölbron, Dlr</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>464743</v>
+        <v>464760</v>
       </c>
       <c r="R23" t="n">
-        <v>6784623</v>
+        <v>6784613</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3171,7 +3175,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>09:31</t>
+          <t>09:28</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3181,7 +3185,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>09:31</t>
+          <t>09:28</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3196,24 +3200,24 @@
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer, Birgitta Kvist, Håkan Thenander, Peter Turander</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
       <c r="AZ23" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/126480512</t>
+          <t>https://artportalen.se/Sighting/126480241</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>126480526</v>
+        <v>126480512</v>
       </c>
       <c r="B24" t="n">
         <v>79327</v>
@@ -3244,14 +3248,14 @@
       <c r="I24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Kölbron, Dlr</t>
+          <t>Kölbron, Kölbron, Dlr</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>464766</v>
+        <v>464743</v>
       </c>
       <c r="R24" t="n">
-        <v>6784628</v>
+        <v>6784623</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3283,7 +3287,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>09:28</t>
+          <t>09:31</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3293,7 +3297,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>09:28</t>
+          <t>09:31</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3308,24 +3312,24 @@
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bengt Oldhammer</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bengt Oldhammer, Birgitta Kvist, Håkan Thenander, Peter Turander</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
       <c r="AZ24" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/126480526</t>
+          <t>https://artportalen.se/Sighting/126480512</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>126481466</v>
+        <v>126480526</v>
       </c>
       <c r="B25" t="n">
         <v>79327</v>
@@ -3356,14 +3360,14 @@
       <c r="I25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Kölbron, Kölbron, Dlr</t>
+          <t>Kölbron, Dlr</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>464730</v>
+        <v>464766</v>
       </c>
       <c r="R25" t="n">
-        <v>6784658</v>
+        <v>6784628</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3395,7 +3399,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>09:31</t>
+          <t>09:28</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3405,7 +3409,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>09:31</t>
+          <t>09:28</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3420,24 +3424,24 @@
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer, Birgitta Kvist, Håkan Thenander, Peter Turander</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
       <c r="AZ25" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/126481466</t>
+          <t>https://artportalen.se/Sighting/126480526</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>126481494</v>
+        <v>126481466</v>
       </c>
       <c r="B26" t="n">
         <v>79327</v>
@@ -3468,14 +3472,14 @@
       <c r="I26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Kölbron, Dlr</t>
+          <t>Kölbron, Kölbron, Dlr</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>464766</v>
+        <v>464730</v>
       </c>
       <c r="R26" t="n">
-        <v>6784648</v>
+        <v>6784658</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3507,7 +3511,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>09:28</t>
+          <t>09:31</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3517,7 +3521,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>09:28</t>
+          <t>09:31</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3532,24 +3536,24 @@
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bengt Oldhammer</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bengt Oldhammer, Birgitta Kvist, Håkan Thenander, Peter Turander</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
       <c r="AZ26" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/126481494</t>
+          <t>https://artportalen.se/Sighting/126481466</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>126481699</v>
+        <v>126481494</v>
       </c>
       <c r="B27" t="n">
         <v>79327</v>
@@ -3584,10 +3588,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>464778</v>
+        <v>464766</v>
       </c>
       <c r="R27" t="n">
-        <v>6784647</v>
+        <v>6784648</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3655,13 +3659,13 @@
       <c r="AY27" t="inlineStr"/>
       <c r="AZ27" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/126481699</t>
+          <t>https://artportalen.se/Sighting/126481494</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>126482131</v>
+        <v>126481699</v>
       </c>
       <c r="B28" t="n">
         <v>79327</v>
@@ -3696,10 +3700,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>464774</v>
+        <v>464778</v>
       </c>
       <c r="R28" t="n">
-        <v>6784611</v>
+        <v>6784647</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3767,13 +3771,13 @@
       <c r="AY28" t="inlineStr"/>
       <c r="AZ28" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/126482131</t>
+          <t>https://artportalen.se/Sighting/126481699</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>126482224</v>
+        <v>126482131</v>
       </c>
       <c r="B29" t="n">
         <v>79327</v>
@@ -3808,10 +3812,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>464765</v>
+        <v>464774</v>
       </c>
       <c r="R29" t="n">
-        <v>6784612</v>
+        <v>6784611</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3879,13 +3883,13 @@
       <c r="AY29" t="inlineStr"/>
       <c r="AZ29" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/126482224</t>
+          <t>https://artportalen.se/Sighting/126482131</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>126482400</v>
+        <v>126482224</v>
       </c>
       <c r="B30" t="n">
         <v>79327</v>
@@ -3920,10 +3924,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>464778</v>
+        <v>464765</v>
       </c>
       <c r="R30" t="n">
-        <v>6784658</v>
+        <v>6784612</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3991,13 +3995,13 @@
       <c r="AY30" t="inlineStr"/>
       <c r="AZ30" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/126482400</t>
+          <t>https://artportalen.se/Sighting/126482224</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>126482486</v>
+        <v>126482400</v>
       </c>
       <c r="B31" t="n">
         <v>79327</v>
@@ -4028,14 +4032,14 @@
       <c r="I31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Kölbron, Kölbron, Dlr</t>
+          <t>Kölbron, Dlr</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>464743</v>
+        <v>464778</v>
       </c>
       <c r="R31" t="n">
-        <v>6784670</v>
+        <v>6784658</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -4067,7 +4071,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>09:31</t>
+          <t>09:28</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -4077,7 +4081,7 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>09:31</t>
+          <t>09:28</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4092,24 +4096,24 @@
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer, Birgitta Kvist, Håkan Thenander, Peter Turander</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
       <c r="AZ31" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/126482486</t>
+          <t>https://artportalen.se/Sighting/126482400</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>126482505</v>
+        <v>126482486</v>
       </c>
       <c r="B32" t="n">
         <v>79327</v>
@@ -4140,14 +4144,14 @@
       <c r="I32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Kölbron, Dlr</t>
+          <t>Kölbron, Kölbron, Dlr</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>464732</v>
+        <v>464743</v>
       </c>
       <c r="R32" t="n">
-        <v>6784654</v>
+        <v>6784670</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4179,7 +4183,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>09:28</t>
+          <t>09:31</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -4189,7 +4193,7 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>09:28</t>
+          <t>09:31</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4204,24 +4208,24 @@
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bengt Oldhammer</t>
         </is>
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bengt Oldhammer, Birgitta Kvist, Håkan Thenander, Peter Turander</t>
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
       <c r="AZ32" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/126482505</t>
+          <t>https://artportalen.se/Sighting/126482486</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>126483268</v>
+        <v>126482505</v>
       </c>
       <c r="B33" t="n">
         <v>79327</v>
@@ -4259,7 +4263,7 @@
         <v>464732</v>
       </c>
       <c r="R33" t="n">
-        <v>6784658</v>
+        <v>6784654</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4291,7 +4295,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>09:56</t>
+          <t>09:28</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -4301,7 +4305,7 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>09:56</t>
+          <t>09:28</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4327,13 +4331,13 @@
       <c r="AY33" t="inlineStr"/>
       <c r="AZ33" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/126483268</t>
+          <t>https://artportalen.se/Sighting/126482505</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>126484512</v>
+        <v>126483268</v>
       </c>
       <c r="B34" t="n">
         <v>79327</v>
@@ -4368,10 +4372,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>464760</v>
+        <v>464732</v>
       </c>
       <c r="R34" t="n">
-        <v>6784680</v>
+        <v>6784658</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4439,13 +4443,13 @@
       <c r="AY34" t="inlineStr"/>
       <c r="AZ34" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/126484512</t>
+          <t>https://artportalen.se/Sighting/126483268</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>126484814</v>
+        <v>126484512</v>
       </c>
       <c r="B35" t="n">
         <v>79327</v>
@@ -4480,10 +4484,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>464806</v>
+        <v>464760</v>
       </c>
       <c r="R35" t="n">
-        <v>6784704</v>
+        <v>6784680</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4551,13 +4555,13 @@
       <c r="AY35" t="inlineStr"/>
       <c r="AZ35" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/126484814</t>
+          <t>https://artportalen.se/Sighting/126484512</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>126484941</v>
+        <v>126484814</v>
       </c>
       <c r="B36" t="n">
         <v>79327</v>
@@ -4588,14 +4592,14 @@
       <c r="I36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
-          <t>Kölbron, Kölbron, Dlr</t>
+          <t>Kölbron, Dlr</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>464775</v>
+        <v>464806</v>
       </c>
       <c r="R36" t="n">
-        <v>6784702</v>
+        <v>6784704</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4627,7 +4631,7 @@
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>10:25</t>
+          <t>09:56</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
@@ -4637,7 +4641,7 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>10:25</t>
+          <t>09:56</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4652,24 +4656,24 @@
       <c r="AT36" t="inlineStr"/>
       <c r="AW36" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX36" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer, Birgitta Kvist, Håkan Thenander, Peter Turander</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
       <c r="AZ36" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/126484941</t>
+          <t>https://artportalen.se/Sighting/126484814</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>126484942</v>
+        <v>126484941</v>
       </c>
       <c r="B37" t="n">
         <v>79327</v>
@@ -4700,14 +4704,14 @@
       <c r="I37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
-          <t>Kölbron, Dlr</t>
+          <t>Kölbron, Kölbron, Dlr</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>464828</v>
+        <v>464775</v>
       </c>
       <c r="R37" t="n">
-        <v>6784703</v>
+        <v>6784702</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4739,7 +4743,7 @@
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>09:56</t>
+          <t>10:25</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
@@ -4749,7 +4753,7 @@
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>09:56</t>
+          <t>10:25</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4764,24 +4768,24 @@
       <c r="AT37" t="inlineStr"/>
       <c r="AW37" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bengt Oldhammer</t>
         </is>
       </c>
       <c r="AX37" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bengt Oldhammer, Birgitta Kvist, Håkan Thenander, Peter Turander</t>
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
       <c r="AZ37" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/126484942</t>
+          <t>https://artportalen.se/Sighting/126484941</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>126485023</v>
+        <v>126484942</v>
       </c>
       <c r="B38" t="n">
         <v>79327</v>
@@ -4812,14 +4816,14 @@
       <c r="I38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
-          <t>Kölbron, Kölbron, Dlr</t>
+          <t>Kölbron, Dlr</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>464772</v>
+        <v>464828</v>
       </c>
       <c r="R38" t="n">
-        <v>6784708</v>
+        <v>6784703</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4851,7 +4855,7 @@
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>10:28</t>
+          <t>09:56</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
@@ -4861,7 +4865,7 @@
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>10:28</t>
+          <t>09:56</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4876,24 +4880,24 @@
       <c r="AT38" t="inlineStr"/>
       <c r="AW38" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX38" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer, Birgitta Kvist, Håkan Thenander, Peter Turander</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
       <c r="AZ38" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/126485023</t>
+          <t>https://artportalen.se/Sighting/126484942</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>126485026</v>
+        <v>126485023</v>
       </c>
       <c r="B39" t="n">
         <v>79327</v>
@@ -4924,14 +4928,14 @@
       <c r="I39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
-          <t>Kölbron, Dlr</t>
+          <t>Kölbron, Kölbron, Dlr</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>464849</v>
+        <v>464772</v>
       </c>
       <c r="R39" t="n">
-        <v>6784700</v>
+        <v>6784708</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4963,7 +4967,7 @@
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>09:56</t>
+          <t>10:28</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
@@ -4973,7 +4977,7 @@
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>09:56</t>
+          <t>10:28</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4988,24 +4992,24 @@
       <c r="AT39" t="inlineStr"/>
       <c r="AW39" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bengt Oldhammer</t>
         </is>
       </c>
       <c r="AX39" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bengt Oldhammer, Birgitta Kvist, Håkan Thenander, Peter Turander</t>
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
       <c r="AZ39" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/126485026</t>
+          <t>https://artportalen.se/Sighting/126485023</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>126485104</v>
+        <v>126485026</v>
       </c>
       <c r="B40" t="n">
         <v>79327</v>
@@ -5040,10 +5044,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>464857</v>
+        <v>464849</v>
       </c>
       <c r="R40" t="n">
-        <v>6784710</v>
+        <v>6784700</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -5111,13 +5115,13 @@
       <c r="AY40" t="inlineStr"/>
       <c r="AZ40" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/126485104</t>
+          <t>https://artportalen.se/Sighting/126485026</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>126485142</v>
+        <v>126485104</v>
       </c>
       <c r="B41" t="n">
         <v>79327</v>
@@ -5152,10 +5156,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>464821</v>
+        <v>464857</v>
       </c>
       <c r="R41" t="n">
-        <v>6784726</v>
+        <v>6784710</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -5223,13 +5227,13 @@
       <c r="AY41" t="inlineStr"/>
       <c r="AZ41" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/126485142</t>
+          <t>https://artportalen.se/Sighting/126485104</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>126485215</v>
+        <v>126485142</v>
       </c>
       <c r="B42" t="n">
         <v>79327</v>
@@ -5264,10 +5268,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>464798</v>
+        <v>464821</v>
       </c>
       <c r="R42" t="n">
-        <v>6784753</v>
+        <v>6784726</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5335,13 +5339,13 @@
       <c r="AY42" t="inlineStr"/>
       <c r="AZ42" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/126485215</t>
+          <t>https://artportalen.se/Sighting/126485142</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>126485359</v>
+        <v>126485215</v>
       </c>
       <c r="B43" t="n">
         <v>79327</v>
@@ -5376,10 +5380,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>464793</v>
+        <v>464798</v>
       </c>
       <c r="R43" t="n">
-        <v>6784773</v>
+        <v>6784753</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5447,13 +5451,13 @@
       <c r="AY43" t="inlineStr"/>
       <c r="AZ43" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/126485359</t>
+          <t>https://artportalen.se/Sighting/126485215</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>126485580</v>
+        <v>126485359</v>
       </c>
       <c r="B44" t="n">
         <v>79327</v>
@@ -5488,13 +5492,13 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>464777</v>
+        <v>464793</v>
       </c>
       <c r="R44" t="n">
-        <v>6784791</v>
+        <v>6784773</v>
       </c>
       <c r="S44" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T44" t="inlineStr">
         <is>
@@ -5559,13 +5563,13 @@
       <c r="AY44" t="inlineStr"/>
       <c r="AZ44" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/126485580</t>
+          <t>https://artportalen.se/Sighting/126485359</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>126485608</v>
+        <v>126485580</v>
       </c>
       <c r="B45" t="n">
         <v>79327</v>
@@ -5600,13 +5604,13 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>464769</v>
+        <v>464777</v>
       </c>
       <c r="R45" t="n">
-        <v>6784801</v>
+        <v>6784791</v>
       </c>
       <c r="S45" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T45" t="inlineStr">
         <is>
@@ -5671,13 +5675,13 @@
       <c r="AY45" t="inlineStr"/>
       <c r="AZ45" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/126485608</t>
+          <t>https://artportalen.se/Sighting/126485580</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>126485702</v>
+        <v>126485608</v>
       </c>
       <c r="B46" t="n">
         <v>79327</v>
@@ -5712,10 +5716,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>464760</v>
+        <v>464769</v>
       </c>
       <c r="R46" t="n">
-        <v>6784816</v>
+        <v>6784801</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5783,13 +5787,13 @@
       <c r="AY46" t="inlineStr"/>
       <c r="AZ46" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/126485702</t>
+          <t>https://artportalen.se/Sighting/126485608</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>126485741</v>
+        <v>126485702</v>
       </c>
       <c r="B47" t="n">
         <v>79327</v>
@@ -5824,13 +5828,13 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>464743</v>
+        <v>464760</v>
       </c>
       <c r="R47" t="n">
-        <v>6784824</v>
+        <v>6784816</v>
       </c>
       <c r="S47" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T47" t="inlineStr">
         <is>
@@ -5870,11 +5874,6 @@
       <c r="AB47" t="inlineStr">
         <is>
           <t>09:56</t>
-        </is>
-      </c>
-      <c r="AC47" t="inlineStr">
-        <is>
-          <t>Rikligt i en radie på ca 50 meter.</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5900,13 +5899,13 @@
       <c r="AY47" t="inlineStr"/>
       <c r="AZ47" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/126485741</t>
+          <t>https://artportalen.se/Sighting/126485702</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>126585245</v>
+        <v>126485741</v>
       </c>
       <c r="B48" t="n">
         <v>79327</v>
@@ -5935,22 +5934,19 @@
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
-      <c r="J48" t="inlineStr"/>
-      <c r="K48" t="inlineStr"/>
-      <c r="N48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
         <is>
           <t>Kölbron, Dlr</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>464749</v>
+        <v>464743</v>
       </c>
       <c r="R48" t="n">
-        <v>6784609</v>
+        <v>6784824</v>
       </c>
       <c r="S48" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T48" t="inlineStr">
         <is>
@@ -5974,27 +5970,27 @@
       </c>
       <c r="Y48" t="inlineStr">
         <is>
-          <t>2025-07-11</t>
+          <t>2025-07-07</t>
         </is>
       </c>
       <c r="Z48" t="inlineStr">
         <is>
-          <t>14:15</t>
+          <t>09:56</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
         <is>
-          <t>2025-07-11</t>
+          <t>2025-07-07</t>
         </is>
       </c>
       <c r="AB48" t="inlineStr">
         <is>
-          <t>14:15</t>
+          <t>09:56</t>
         </is>
       </c>
       <c r="AC48" t="inlineStr">
         <is>
-          <t>Miljöbild. Rikligt med garnlav synligt bakom avverkningsanmälan, Bergkvist Siljan.</t>
+          <t>Rikligt i en radie på ca 50 meter.</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -6003,7 +5999,6 @@
       <c r="AE48" t="b">
         <v>0</v>
       </c>
-      <c r="AF48" t="inlineStr"/>
       <c r="AG48" t="b">
         <v>0</v>
       </c>
@@ -6021,13 +6016,13 @@
       <c r="AY48" t="inlineStr"/>
       <c r="AZ48" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/126585245</t>
+          <t>https://artportalen.se/Sighting/126485741</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>126585428</v>
+        <v>126585245</v>
       </c>
       <c r="B49" t="n">
         <v>79327</v>
@@ -6056,19 +6051,22 @@
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
+      <c r="J49" t="inlineStr"/>
+      <c r="K49" t="inlineStr"/>
+      <c r="N49" t="inlineStr"/>
       <c r="P49" t="inlineStr">
         <is>
           <t>Kölbron, Dlr</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>464725</v>
+        <v>464749</v>
       </c>
       <c r="R49" t="n">
-        <v>6784623</v>
+        <v>6784609</v>
       </c>
       <c r="S49" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T49" t="inlineStr">
         <is>
@@ -6097,7 +6095,7 @@
       </c>
       <c r="Z49" t="inlineStr">
         <is>
-          <t>14:22</t>
+          <t>14:15</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
@@ -6107,7 +6105,12 @@
       </c>
       <c r="AB49" t="inlineStr">
         <is>
-          <t>14:22</t>
+          <t>14:15</t>
+        </is>
+      </c>
+      <c r="AC49" t="inlineStr">
+        <is>
+          <t>Miljöbild. Rikligt med garnlav synligt bakom avverkningsanmälan, Bergkvist Siljan.</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -6116,6 +6119,7 @@
       <c r="AE49" t="b">
         <v>0</v>
       </c>
+      <c r="AF49" t="inlineStr"/>
       <c r="AG49" t="b">
         <v>0</v>
       </c>
@@ -6133,13 +6137,13 @@
       <c r="AY49" t="inlineStr"/>
       <c r="AZ49" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/126585428</t>
+          <t>https://artportalen.se/Sighting/126585245</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>126585536</v>
+        <v>126585428</v>
       </c>
       <c r="B50" t="n">
         <v>79327</v>
@@ -6174,10 +6178,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>464689</v>
+        <v>464725</v>
       </c>
       <c r="R50" t="n">
-        <v>6784645</v>
+        <v>6784623</v>
       </c>
       <c r="S50" t="n">
         <v>50</v>
@@ -6245,13 +6249,13 @@
       <c r="AY50" t="inlineStr"/>
       <c r="AZ50" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/126585536</t>
+          <t>https://artportalen.se/Sighting/126585428</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>126585619</v>
+        <v>126585536</v>
       </c>
       <c r="B51" t="n">
         <v>79327</v>
@@ -6286,13 +6290,13 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>464704</v>
+        <v>464689</v>
       </c>
       <c r="R51" t="n">
-        <v>6784647</v>
+        <v>6784645</v>
       </c>
       <c r="S51" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T51" t="inlineStr">
         <is>
@@ -6357,13 +6361,13 @@
       <c r="AY51" t="inlineStr"/>
       <c r="AZ51" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/126585619</t>
+          <t>https://artportalen.se/Sighting/126585536</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>126585736</v>
+        <v>126585619</v>
       </c>
       <c r="B52" t="n">
         <v>79327</v>
@@ -6398,10 +6402,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>464720</v>
+        <v>464704</v>
       </c>
       <c r="R52" t="n">
-        <v>6784658</v>
+        <v>6784647</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -6469,13 +6473,13 @@
       <c r="AY52" t="inlineStr"/>
       <c r="AZ52" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/126585736</t>
+          <t>https://artportalen.se/Sighting/126585619</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>126586047</v>
+        <v>126585736</v>
       </c>
       <c r="B53" t="n">
         <v>79327</v>
@@ -6510,10 +6514,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>464730</v>
+        <v>464720</v>
       </c>
       <c r="R53" t="n">
-        <v>6784662</v>
+        <v>6784658</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6581,13 +6585,13 @@
       <c r="AY53" t="inlineStr"/>
       <c r="AZ53" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/126586047</t>
+          <t>https://artportalen.se/Sighting/126585736</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>126586092</v>
+        <v>126586047</v>
       </c>
       <c r="B54" t="n">
         <v>79327</v>
@@ -6622,10 +6626,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>464712</v>
+        <v>464730</v>
       </c>
       <c r="R54" t="n">
-        <v>6784680</v>
+        <v>6784662</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6693,13 +6697,13 @@
       <c r="AY54" t="inlineStr"/>
       <c r="AZ54" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/126586092</t>
+          <t>https://artportalen.se/Sighting/126586047</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>126586589</v>
+        <v>126586092</v>
       </c>
       <c r="B55" t="n">
         <v>79327</v>
@@ -6734,10 +6738,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>464639</v>
+        <v>464712</v>
       </c>
       <c r="R55" t="n">
-        <v>6784741</v>
+        <v>6784680</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6805,13 +6809,13 @@
       <c r="AY55" t="inlineStr"/>
       <c r="AZ55" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/126586589</t>
+          <t>https://artportalen.se/Sighting/126586092</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>126586650</v>
+        <v>126586589</v>
       </c>
       <c r="B56" t="n">
         <v>79327</v>
@@ -6846,10 +6850,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>464649</v>
+        <v>464639</v>
       </c>
       <c r="R56" t="n">
-        <v>6784725</v>
+        <v>6784741</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6917,13 +6921,13 @@
       <c r="AY56" t="inlineStr"/>
       <c r="AZ56" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/126586650</t>
+          <t>https://artportalen.se/Sighting/126586589</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>126586891</v>
+        <v>126586650</v>
       </c>
       <c r="B57" t="n">
         <v>79327</v>
@@ -6958,10 +6962,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>464671</v>
+        <v>464649</v>
       </c>
       <c r="R57" t="n">
-        <v>6784711</v>
+        <v>6784725</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -7029,13 +7033,13 @@
       <c r="AY57" t="inlineStr"/>
       <c r="AZ57" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/126586891</t>
+          <t>https://artportalen.se/Sighting/126586650</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>126587405</v>
+        <v>126586891</v>
       </c>
       <c r="B58" t="n">
         <v>79327</v>
@@ -7070,10 +7074,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>464814</v>
+        <v>464671</v>
       </c>
       <c r="R58" t="n">
-        <v>6784654</v>
+        <v>6784711</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -7141,13 +7145,13 @@
       <c r="AY58" t="inlineStr"/>
       <c r="AZ58" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/126587405</t>
+          <t>https://artportalen.se/Sighting/126586891</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>126588667</v>
+        <v>126587405</v>
       </c>
       <c r="B59" t="n">
         <v>79327</v>
@@ -7176,19 +7180,16 @@
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
-      <c r="J59" t="inlineStr"/>
-      <c r="K59" t="inlineStr"/>
-      <c r="N59" t="inlineStr"/>
       <c r="P59" t="inlineStr">
         <is>
           <t>Kölbron, Dlr</t>
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>464831</v>
+        <v>464814</v>
       </c>
       <c r="R59" t="n">
-        <v>6784672</v>
+        <v>6784654</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -7220,7 +7221,7 @@
       </c>
       <c r="Z59" t="inlineStr">
         <is>
-          <t>16:38</t>
+          <t>14:22</t>
         </is>
       </c>
       <c r="AA59" t="inlineStr">
@@ -7230,12 +7231,7 @@
       </c>
       <c r="AB59" t="inlineStr">
         <is>
-          <t>16:38</t>
-        </is>
-      </c>
-      <c r="AC59" t="inlineStr">
-        <is>
-          <t>Miljöbilder för närområdet</t>
+          <t>14:22</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -7244,7 +7240,6 @@
       <c r="AE59" t="b">
         <v>0</v>
       </c>
-      <c r="AF59" t="inlineStr"/>
       <c r="AG59" t="b">
         <v>0</v>
       </c>
@@ -7262,13 +7257,13 @@
       <c r="AY59" t="inlineStr"/>
       <c r="AZ59" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/126588667</t>
+          <t>https://artportalen.se/Sighting/126587405</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>126589398</v>
+        <v>126588667</v>
       </c>
       <c r="B60" t="n">
         <v>79327</v>
@@ -7297,16 +7292,19 @@
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
+      <c r="J60" t="inlineStr"/>
+      <c r="K60" t="inlineStr"/>
+      <c r="N60" t="inlineStr"/>
       <c r="P60" t="inlineStr">
         <is>
           <t>Kölbron, Dlr</t>
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>464858</v>
+        <v>464831</v>
       </c>
       <c r="R60" t="n">
-        <v>6784712</v>
+        <v>6784672</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -7351,12 +7349,18 @@
           <t>16:38</t>
         </is>
       </c>
+      <c r="AC60" t="inlineStr">
+        <is>
+          <t>Miljöbilder för närområdet</t>
+        </is>
+      </c>
       <c r="AD60" t="b">
         <v>0</v>
       </c>
       <c r="AE60" t="b">
         <v>0</v>
       </c>
+      <c r="AF60" t="inlineStr"/>
       <c r="AG60" t="b">
         <v>0</v>
       </c>
@@ -7374,13 +7378,13 @@
       <c r="AY60" t="inlineStr"/>
       <c r="AZ60" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/126589398</t>
+          <t>https://artportalen.se/Sighting/126588667</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>126589408</v>
+        <v>126589398</v>
       </c>
       <c r="B61" t="n">
         <v>79327</v>
@@ -7415,7 +7419,7 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>464857</v>
+        <v>464858</v>
       </c>
       <c r="R61" t="n">
         <v>6784712</v>
@@ -7486,13 +7490,13 @@
       <c r="AY61" t="inlineStr"/>
       <c r="AZ61" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/126589408</t>
+          <t>https://artportalen.se/Sighting/126589398</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>126589776</v>
+        <v>126589408</v>
       </c>
       <c r="B62" t="n">
         <v>79327</v>
@@ -7527,10 +7531,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>464839</v>
+        <v>464857</v>
       </c>
       <c r="R62" t="n">
-        <v>6784720</v>
+        <v>6784712</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -7598,13 +7602,13 @@
       <c r="AY62" t="inlineStr"/>
       <c r="AZ62" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/126589776</t>
+          <t>https://artportalen.se/Sighting/126589408</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>126589816</v>
+        <v>126589776</v>
       </c>
       <c r="B63" t="n">
         <v>79327</v>
@@ -7639,10 +7643,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>464831</v>
+        <v>464839</v>
       </c>
       <c r="R63" t="n">
-        <v>6784718</v>
+        <v>6784720</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -7710,13 +7714,13 @@
       <c r="AY63" t="inlineStr"/>
       <c r="AZ63" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/126589816</t>
+          <t>https://artportalen.se/Sighting/126589776</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>126590106</v>
+        <v>126589816</v>
       </c>
       <c r="B64" t="n">
         <v>79327</v>
@@ -7751,10 +7755,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>464803</v>
+        <v>464831</v>
       </c>
       <c r="R64" t="n">
-        <v>6784725</v>
+        <v>6784718</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -7822,13 +7826,13 @@
       <c r="AY64" t="inlineStr"/>
       <c r="AZ64" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/126590106</t>
+          <t>https://artportalen.se/Sighting/126589816</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>126590186</v>
+        <v>126590106</v>
       </c>
       <c r="B65" t="n">
         <v>79327</v>
@@ -7863,10 +7867,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>464816</v>
+        <v>464803</v>
       </c>
       <c r="R65" t="n">
-        <v>6784753</v>
+        <v>6784725</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7934,13 +7938,13 @@
       <c r="AY65" t="inlineStr"/>
       <c r="AZ65" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/126590186</t>
+          <t>https://artportalen.se/Sighting/126590106</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>126590480</v>
+        <v>126590186</v>
       </c>
       <c r="B66" t="n">
         <v>79327</v>
@@ -7975,10 +7979,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>464755</v>
+        <v>464816</v>
       </c>
       <c r="R66" t="n">
-        <v>6784795</v>
+        <v>6784753</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -8010,7 +8014,7 @@
       </c>
       <c r="Z66" t="inlineStr">
         <is>
-          <t>17:39</t>
+          <t>16:38</t>
         </is>
       </c>
       <c r="AA66" t="inlineStr">
@@ -8020,7 +8024,7 @@
       </c>
       <c r="AB66" t="inlineStr">
         <is>
-          <t>17:39</t>
+          <t>16:38</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -8046,13 +8050,13 @@
       <c r="AY66" t="inlineStr"/>
       <c r="AZ66" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/126590480</t>
+          <t>https://artportalen.se/Sighting/126590186</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>126590826</v>
+        <v>126590480</v>
       </c>
       <c r="B67" t="n">
         <v>79327</v>
@@ -8087,10 +8091,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>464741</v>
+        <v>464755</v>
       </c>
       <c r="R67" t="n">
-        <v>6784807</v>
+        <v>6784795</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -8158,13 +8162,13 @@
       <c r="AY67" t="inlineStr"/>
       <c r="AZ67" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/126590826</t>
+          <t>https://artportalen.se/Sighting/126590480</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>126590840</v>
+        <v>126590826</v>
       </c>
       <c r="B68" t="n">
         <v>79327</v>
@@ -8199,10 +8203,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>464734</v>
+        <v>464741</v>
       </c>
       <c r="R68" t="n">
-        <v>6784815</v>
+        <v>6784807</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -8270,13 +8274,13 @@
       <c r="AY68" t="inlineStr"/>
       <c r="AZ68" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/126590840</t>
+          <t>https://artportalen.se/Sighting/126590826</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>126590850</v>
+        <v>126590840</v>
       </c>
       <c r="B69" t="n">
         <v>79327</v>
@@ -8311,10 +8315,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>464724</v>
+        <v>464734</v>
       </c>
       <c r="R69" t="n">
-        <v>6784810</v>
+        <v>6784815</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -8382,13 +8386,13 @@
       <c r="AY69" t="inlineStr"/>
       <c r="AZ69" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/126590850</t>
+          <t>https://artportalen.se/Sighting/126590840</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>126590867</v>
+        <v>126590850</v>
       </c>
       <c r="B70" t="n">
         <v>79327</v>
@@ -8423,10 +8427,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>464730</v>
+        <v>464724</v>
       </c>
       <c r="R70" t="n">
-        <v>6784826</v>
+        <v>6784810</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -8494,13 +8498,13 @@
       <c r="AY70" t="inlineStr"/>
       <c r="AZ70" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/126590867</t>
+          <t>https://artportalen.se/Sighting/126590850</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>126591007</v>
+        <v>126590867</v>
       </c>
       <c r="B71" t="n">
         <v>79327</v>
@@ -8535,10 +8539,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>464744</v>
+        <v>464730</v>
       </c>
       <c r="R71" t="n">
-        <v>6784847</v>
+        <v>6784826</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -8606,13 +8610,13 @@
       <c r="AY71" t="inlineStr"/>
       <c r="AZ71" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/126591007</t>
+          <t>https://artportalen.se/Sighting/126590867</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>126591506</v>
+        <v>126591007</v>
       </c>
       <c r="B72" t="n">
         <v>79327</v>
@@ -8647,10 +8651,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>464757</v>
+        <v>464744</v>
       </c>
       <c r="R72" t="n">
-        <v>6784856</v>
+        <v>6784847</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -8718,13 +8722,13 @@
       <c r="AY72" t="inlineStr"/>
       <c r="AZ72" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/126591506</t>
+          <t>https://artportalen.se/Sighting/126591007</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>126591615</v>
+        <v>126591506</v>
       </c>
       <c r="B73" t="n">
         <v>79327</v>
@@ -8759,10 +8763,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>464711</v>
+        <v>464757</v>
       </c>
       <c r="R73" t="n">
-        <v>6784812</v>
+        <v>6784856</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -8830,13 +8834,13 @@
       <c r="AY73" t="inlineStr"/>
       <c r="AZ73" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/126591615</t>
+          <t>https://artportalen.se/Sighting/126591506</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>126592098</v>
+        <v>126591615</v>
       </c>
       <c r="B74" t="n">
         <v>79327</v>
@@ -8871,10 +8875,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>464676</v>
+        <v>464711</v>
       </c>
       <c r="R74" t="n">
-        <v>6784780</v>
+        <v>6784812</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -8919,11 +8923,6 @@
           <t>17:39</t>
         </is>
       </c>
-      <c r="AC74" t="inlineStr">
-        <is>
-          <t>Garn vid rullstensås</t>
-        </is>
-      </c>
       <c r="AD74" t="b">
         <v>0</v>
       </c>
@@ -8947,13 +8946,13 @@
       <c r="AY74" t="inlineStr"/>
       <c r="AZ74" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/126592098</t>
+          <t>https://artportalen.se/Sighting/126591615</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>127528615</v>
+        <v>126592098</v>
       </c>
       <c r="B75" t="n">
         <v>79327</v>
@@ -8988,10 +8987,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>464875</v>
+        <v>464676</v>
       </c>
       <c r="R75" t="n">
-        <v>6784695</v>
+        <v>6784780</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -9018,22 +9017,27 @@
       </c>
       <c r="Y75" t="inlineStr">
         <is>
-          <t>2025-08-15</t>
+          <t>2025-07-11</t>
         </is>
       </c>
       <c r="Z75" t="inlineStr">
         <is>
-          <t>09:17</t>
+          <t>17:39</t>
         </is>
       </c>
       <c r="AA75" t="inlineStr">
         <is>
-          <t>2025-08-15</t>
+          <t>2025-07-11</t>
         </is>
       </c>
       <c r="AB75" t="inlineStr">
         <is>
-          <t>09:17</t>
+          <t>17:39</t>
+        </is>
+      </c>
+      <c r="AC75" t="inlineStr">
+        <is>
+          <t>Garn vid rullstensås</t>
         </is>
       </c>
       <c r="AD75" t="b">
@@ -9059,13 +9063,13 @@
       <c r="AY75" t="inlineStr"/>
       <c r="AZ75" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/127528615</t>
+          <t>https://artportalen.se/Sighting/126592098</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>127530663</v>
+        <v>127528615</v>
       </c>
       <c r="B76" t="n">
         <v>79327</v>
@@ -9100,10 +9104,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>464850</v>
+        <v>464875</v>
       </c>
       <c r="R76" t="n">
-        <v>6784699</v>
+        <v>6784695</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -9171,13 +9175,13 @@
       <c r="AY76" t="inlineStr"/>
       <c r="AZ76" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/127530663</t>
+          <t>https://artportalen.se/Sighting/127528615</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>127536063</v>
+        <v>127530663</v>
       </c>
       <c r="B77" t="n">
         <v>79327</v>
@@ -9212,10 +9216,10 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>464819</v>
+        <v>464850</v>
       </c>
       <c r="R77" t="n">
-        <v>6784639</v>
+        <v>6784699</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -9283,13 +9287,13 @@
       <c r="AY77" t="inlineStr"/>
       <c r="AZ77" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/127536063</t>
+          <t>https://artportalen.se/Sighting/127530663</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>127627114</v>
+        <v>127536063</v>
       </c>
       <c r="B78" t="n">
         <v>79327</v>
@@ -9318,19 +9322,16 @@
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
-      <c r="J78" t="inlineStr"/>
-      <c r="K78" t="inlineStr"/>
-      <c r="N78" t="inlineStr"/>
       <c r="P78" t="inlineStr">
         <is>
           <t>Kölbron, Dlr</t>
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>464868</v>
+        <v>464819</v>
       </c>
       <c r="R78" t="n">
-        <v>6784685</v>
+        <v>6784639</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -9360,14 +9361,19 @@
           <t>2025-08-15</t>
         </is>
       </c>
+      <c r="Z78" t="inlineStr">
+        <is>
+          <t>09:17</t>
+        </is>
+      </c>
       <c r="AA78" t="inlineStr">
         <is>
           <t>2025-08-15</t>
         </is>
       </c>
-      <c r="AC78" t="inlineStr">
-        <is>
-          <t>På gran</t>
+      <c r="AB78" t="inlineStr">
+        <is>
+          <t>09:17</t>
         </is>
       </c>
       <c r="AD78" t="b">
@@ -9376,31 +9382,30 @@
       <c r="AE78" t="b">
         <v>0</v>
       </c>
-      <c r="AF78" t="inlineStr"/>
       <c r="AG78" t="b">
         <v>0</v>
       </c>
       <c r="AT78" t="inlineStr"/>
       <c r="AW78" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX78" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY78" t="inlineStr"/>
       <c r="AZ78" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/127627114</t>
+          <t>https://artportalen.se/Sighting/127536063</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>127627165</v>
+        <v>127627114</v>
       </c>
       <c r="B79" t="n">
         <v>79327</v>
@@ -9438,10 +9443,10 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>464808</v>
+        <v>464868</v>
       </c>
       <c r="R79" t="n">
-        <v>6784637</v>
+        <v>6784685</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -9476,6 +9481,11 @@
           <t>2025-08-15</t>
         </is>
       </c>
+      <c r="AC79" t="inlineStr">
+        <is>
+          <t>På gran</t>
+        </is>
+      </c>
       <c r="AD79" t="b">
         <v>0</v>
       </c>
@@ -9500,13 +9510,13 @@
       <c r="AY79" t="inlineStr"/>
       <c r="AZ79" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/127627165</t>
+          <t>https://artportalen.se/Sighting/127627114</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>127627174</v>
+        <v>127627165</v>
       </c>
       <c r="B80" t="n">
         <v>79327</v>
@@ -9544,10 +9554,10 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>464796</v>
+        <v>464808</v>
       </c>
       <c r="R80" t="n">
-        <v>6784631</v>
+        <v>6784637</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -9606,13 +9616,13 @@
       <c r="AY80" t="inlineStr"/>
       <c r="AZ80" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/127627174</t>
+          <t>https://artportalen.se/Sighting/127627165</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>127627233</v>
+        <v>127627174</v>
       </c>
       <c r="B81" t="n">
         <v>79327</v>
@@ -9650,10 +9660,10 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>464804</v>
+        <v>464796</v>
       </c>
       <c r="R81" t="n">
-        <v>6784620</v>
+        <v>6784631</v>
       </c>
       <c r="S81" t="n">
         <v>10</v>
@@ -9688,11 +9698,6 @@
           <t>2025-08-15</t>
         </is>
       </c>
-      <c r="AC81" t="inlineStr">
-        <is>
-          <t>På 6 tallstammar</t>
-        </is>
-      </c>
       <c r="AD81" t="b">
         <v>0</v>
       </c>
@@ -9717,16 +9722,16 @@
       <c r="AY81" t="inlineStr"/>
       <c r="AZ81" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/127627233</t>
+          <t>https://artportalen.se/Sighting/127627174</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>136689324</v>
+        <v>127627233</v>
       </c>
       <c r="B82" t="n">
-        <v>79474</v>
+        <v>79327</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -9752,19 +9757,22 @@
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
+      <c r="J82" t="inlineStr"/>
+      <c r="K82" t="inlineStr"/>
+      <c r="N82" t="inlineStr"/>
       <c r="P82" t="inlineStr">
         <is>
           <t>Kölbron, Dlr</t>
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>464774</v>
+        <v>464804</v>
       </c>
       <c r="R82" t="n">
-        <v>6784621</v>
+        <v>6784620</v>
       </c>
       <c r="S82" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T82" t="inlineStr">
         <is>
@@ -9788,22 +9796,17 @@
       </c>
       <c r="Y82" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
-        </is>
-      </c>
-      <c r="Z82" t="inlineStr">
-        <is>
-          <t>11:42</t>
+          <t>2025-08-15</t>
         </is>
       </c>
       <c r="AA82" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
-        </is>
-      </c>
-      <c r="AB82" t="inlineStr">
-        <is>
-          <t>11:42</t>
+          <t>2025-08-15</t>
+        </is>
+      </c>
+      <c r="AC82" t="inlineStr">
+        <is>
+          <t>På 6 tallstammar</t>
         </is>
       </c>
       <c r="AD82" t="b">
@@ -9812,30 +9815,31 @@
       <c r="AE82" t="b">
         <v>0</v>
       </c>
+      <c r="AF82" t="inlineStr"/>
       <c r="AG82" t="b">
         <v>0</v>
       </c>
       <c r="AT82" t="inlineStr"/>
       <c r="AW82" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX82" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY82" t="inlineStr"/>
       <c r="AZ82" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136689324</t>
+          <t>https://artportalen.se/Sighting/127627233</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>136689329</v>
+        <v>136689324</v>
       </c>
       <c r="B83" t="n">
         <v>79474</v>
@@ -9870,10 +9874,10 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>464698</v>
+        <v>464774</v>
       </c>
       <c r="R83" t="n">
-        <v>6784656</v>
+        <v>6784621</v>
       </c>
       <c r="S83" t="n">
         <v>5</v>
@@ -9905,7 +9909,7 @@
       </c>
       <c r="Z83" t="inlineStr">
         <is>
-          <t>11:53</t>
+          <t>11:42</t>
         </is>
       </c>
       <c r="AA83" t="inlineStr">
@@ -9915,7 +9919,7 @@
       </c>
       <c r="AB83" t="inlineStr">
         <is>
-          <t>11:53</t>
+          <t>11:42</t>
         </is>
       </c>
       <c r="AD83" t="b">
@@ -9941,54 +9945,54 @@
       <c r="AY83" t="inlineStr"/>
       <c r="AZ83" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136689329</t>
+          <t>https://artportalen.se/Sighting/136689324</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>126482418</v>
+        <v>136689329</v>
       </c>
       <c r="B84" t="n">
-        <v>79351</v>
+        <v>79474</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E84" t="n">
-        <v>6434</v>
+        <v>6425</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Nästlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Bryoria furcellata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I84" t="inlineStr"/>
       <c r="P84" t="inlineStr">
         <is>
-          <t>Kölbron, Kölbron, Dlr</t>
+          <t>Kölbron, Dlr</t>
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>464743</v>
+        <v>464698</v>
       </c>
       <c r="R84" t="n">
-        <v>6784670</v>
+        <v>6784656</v>
       </c>
       <c r="S84" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T84" t="inlineStr">
         <is>
@@ -10012,22 +10016,22 @@
       </c>
       <c r="Y84" t="inlineStr">
         <is>
-          <t>2025-07-07</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="Z84" t="inlineStr">
         <is>
-          <t>09:31</t>
+          <t>11:53</t>
         </is>
       </c>
       <c r="AA84" t="inlineStr">
         <is>
-          <t>2025-07-07</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="AB84" t="inlineStr">
         <is>
-          <t>09:31</t>
+          <t>11:53</t>
         </is>
       </c>
       <c r="AD84" t="b">
@@ -10047,57 +10051,57 @@
       </c>
       <c r="AX84" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer, Birgitta Kvist, Håkan Thenander, Peter Turander</t>
+          <t>Bengt Oldhammer</t>
         </is>
       </c>
       <c r="AY84" t="inlineStr"/>
       <c r="AZ84" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/126482418</t>
+          <t>https://artportalen.se/Sighting/136689329</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>126487403</v>
+        <v>126482418</v>
       </c>
       <c r="B85" t="n">
-        <v>83307</v>
+        <v>79351</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E85" t="n">
-        <v>6440</v>
+        <v>6434</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Nästlav</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Bryoria furcellata</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I85" t="inlineStr"/>
       <c r="P85" t="inlineStr">
         <is>
-          <t>Kölbron, Dlr</t>
+          <t>Kölbron, Kölbron, Dlr</t>
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>464751</v>
+        <v>464743</v>
       </c>
       <c r="R85" t="n">
-        <v>6784883</v>
+        <v>6784670</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>
@@ -10129,7 +10133,7 @@
       </c>
       <c r="Z85" t="inlineStr">
         <is>
-          <t>11:15</t>
+          <t>09:31</t>
         </is>
       </c>
       <c r="AA85" t="inlineStr">
@@ -10139,7 +10143,7 @@
       </c>
       <c r="AB85" t="inlineStr">
         <is>
-          <t>11:15</t>
+          <t>09:31</t>
         </is>
       </c>
       <c r="AD85" t="b">
@@ -10154,24 +10158,24 @@
       <c r="AT85" t="inlineStr"/>
       <c r="AW85" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bengt Oldhammer</t>
         </is>
       </c>
       <c r="AX85" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bengt Oldhammer, Birgitta Kvist, Håkan Thenander, Peter Turander</t>
         </is>
       </c>
       <c r="AY85" t="inlineStr"/>
       <c r="AZ85" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/126487403</t>
+          <t>https://artportalen.se/Sighting/126482418</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>126586084</v>
+        <v>126487403</v>
       </c>
       <c r="B86" t="n">
         <v>83307</v>
@@ -10200,19 +10204,16 @@
         </is>
       </c>
       <c r="I86" t="inlineStr"/>
-      <c r="J86" t="inlineStr"/>
-      <c r="K86" t="inlineStr"/>
-      <c r="N86" t="inlineStr"/>
       <c r="P86" t="inlineStr">
         <is>
           <t>Kölbron, Dlr</t>
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>464712</v>
+        <v>464751</v>
       </c>
       <c r="R86" t="n">
-        <v>6784680</v>
+        <v>6784883</v>
       </c>
       <c r="S86" t="n">
         <v>10</v>
@@ -10239,27 +10240,22 @@
       </c>
       <c r="Y86" t="inlineStr">
         <is>
-          <t>2025-07-11</t>
+          <t>2025-07-07</t>
         </is>
       </c>
       <c r="Z86" t="inlineStr">
         <is>
-          <t>14:22</t>
+          <t>11:15</t>
         </is>
       </c>
       <c r="AA86" t="inlineStr">
         <is>
-          <t>2025-07-11</t>
+          <t>2025-07-07</t>
         </is>
       </c>
       <c r="AB86" t="inlineStr">
         <is>
-          <t>14:22</t>
-        </is>
-      </c>
-      <c r="AC86" t="inlineStr">
-        <is>
-          <t>Miljöbilder för närområdet</t>
+          <t>11:15</t>
         </is>
       </c>
       <c r="AD86" t="b">
@@ -10268,7 +10264,6 @@
       <c r="AE86" t="b">
         <v>0</v>
       </c>
-      <c r="AF86" t="inlineStr"/>
       <c r="AG86" t="b">
         <v>0</v>
       </c>
@@ -10286,13 +10281,13 @@
       <c r="AY86" t="inlineStr"/>
       <c r="AZ86" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/126586084</t>
+          <t>https://artportalen.se/Sighting/126487403</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>127518186</v>
+        <v>126586084</v>
       </c>
       <c r="B87" t="n">
         <v>83307</v>
@@ -10321,16 +10316,19 @@
         </is>
       </c>
       <c r="I87" t="inlineStr"/>
+      <c r="J87" t="inlineStr"/>
+      <c r="K87" t="inlineStr"/>
+      <c r="N87" t="inlineStr"/>
       <c r="P87" t="inlineStr">
         <is>
           <t>Kölbron, Dlr</t>
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>464838</v>
+        <v>464712</v>
       </c>
       <c r="R87" t="n">
-        <v>6784648</v>
+        <v>6784680</v>
       </c>
       <c r="S87" t="n">
         <v>10</v>
@@ -10357,22 +10355,27 @@
       </c>
       <c r="Y87" t="inlineStr">
         <is>
-          <t>2025-08-15</t>
+          <t>2025-07-11</t>
         </is>
       </c>
       <c r="Z87" t="inlineStr">
         <is>
-          <t>09:17</t>
+          <t>14:22</t>
         </is>
       </c>
       <c r="AA87" t="inlineStr">
         <is>
-          <t>2025-08-15</t>
+          <t>2025-07-11</t>
         </is>
       </c>
       <c r="AB87" t="inlineStr">
         <is>
-          <t>09:17</t>
+          <t>14:22</t>
+        </is>
+      </c>
+      <c r="AC87" t="inlineStr">
+        <is>
+          <t>Miljöbilder för närområdet</t>
         </is>
       </c>
       <c r="AD87" t="b">
@@ -10381,6 +10384,7 @@
       <c r="AE87" t="b">
         <v>0</v>
       </c>
+      <c r="AF87" t="inlineStr"/>
       <c r="AG87" t="b">
         <v>0</v>
       </c>
@@ -10398,13 +10402,13 @@
       <c r="AY87" t="inlineStr"/>
       <c r="AZ87" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/127518186</t>
+          <t>https://artportalen.se/Sighting/126586084</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>127521304</v>
+        <v>127518186</v>
       </c>
       <c r="B88" t="n">
         <v>83307</v>
@@ -10439,10 +10443,10 @@
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>464831</v>
+        <v>464838</v>
       </c>
       <c r="R88" t="n">
-        <v>6784672</v>
+        <v>6784648</v>
       </c>
       <c r="S88" t="n">
         <v>10</v>
@@ -10487,11 +10491,6 @@
           <t>09:17</t>
         </is>
       </c>
-      <c r="AC88" t="inlineStr">
-        <is>
-          <t>Bild på kraftig gran vid gränsen</t>
-        </is>
-      </c>
       <c r="AD88" t="b">
         <v>0</v>
       </c>
@@ -10515,13 +10514,13 @@
       <c r="AY88" t="inlineStr"/>
       <c r="AZ88" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/127521304</t>
+          <t>https://artportalen.se/Sighting/127518186</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>127524724</v>
+        <v>127521304</v>
       </c>
       <c r="B89" t="n">
         <v>83307</v>
@@ -10556,10 +10555,10 @@
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>464825</v>
+        <v>464831</v>
       </c>
       <c r="R89" t="n">
-        <v>6784652</v>
+        <v>6784672</v>
       </c>
       <c r="S89" t="n">
         <v>10</v>
@@ -10604,6 +10603,11 @@
           <t>09:17</t>
         </is>
       </c>
+      <c r="AC89" t="inlineStr">
+        <is>
+          <t>Bild på kraftig gran vid gränsen</t>
+        </is>
+      </c>
       <c r="AD89" t="b">
         <v>0</v>
       </c>
@@ -10627,13 +10631,13 @@
       <c r="AY89" t="inlineStr"/>
       <c r="AZ89" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/127524724</t>
+          <t>https://artportalen.se/Sighting/127521304</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>127627101</v>
+        <v>127524724</v>
       </c>
       <c r="B90" t="n">
         <v>83307</v>
@@ -10662,19 +10666,16 @@
         </is>
       </c>
       <c r="I90" t="inlineStr"/>
-      <c r="J90" t="inlineStr"/>
-      <c r="K90" t="inlineStr"/>
-      <c r="N90" t="inlineStr"/>
       <c r="P90" t="inlineStr">
         <is>
           <t>Kölbron, Dlr</t>
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>464854</v>
+        <v>464825</v>
       </c>
       <c r="R90" t="n">
-        <v>6784664</v>
+        <v>6784652</v>
       </c>
       <c r="S90" t="n">
         <v>10</v>
@@ -10704,45 +10705,54 @@
           <t>2025-08-15</t>
         </is>
       </c>
+      <c r="Z90" t="inlineStr">
+        <is>
+          <t>09:17</t>
+        </is>
+      </c>
       <c r="AA90" t="inlineStr">
         <is>
           <t>2025-08-15</t>
         </is>
       </c>
+      <c r="AB90" t="inlineStr">
+        <is>
+          <t>09:17</t>
+        </is>
+      </c>
       <c r="AD90" t="b">
         <v>0</v>
       </c>
       <c r="AE90" t="b">
         <v>0</v>
       </c>
-      <c r="AF90" t="inlineStr"/>
       <c r="AG90" t="b">
         <v>0</v>
       </c>
       <c r="AT90" t="inlineStr"/>
       <c r="AW90" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX90" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY90" t="inlineStr"/>
       <c r="AZ90" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/127627101</t>
+          <t>https://artportalen.se/Sighting/127524724</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>136689345</v>
+        <v>127627101</v>
       </c>
       <c r="B91" t="n">
-        <v>83461</v>
+        <v>83307</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -10768,19 +10778,22 @@
         </is>
       </c>
       <c r="I91" t="inlineStr"/>
+      <c r="J91" t="inlineStr"/>
+      <c r="K91" t="inlineStr"/>
+      <c r="N91" t="inlineStr"/>
       <c r="P91" t="inlineStr">
         <is>
           <t>Kölbron, Dlr</t>
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>464739</v>
+        <v>464854</v>
       </c>
       <c r="R91" t="n">
-        <v>6784695</v>
+        <v>6784664</v>
       </c>
       <c r="S91" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T91" t="inlineStr">
         <is>
@@ -10804,22 +10817,12 @@
       </c>
       <c r="Y91" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
-        </is>
-      </c>
-      <c r="Z91" t="inlineStr">
-        <is>
-          <t>12:29</t>
+          <t>2025-08-15</t>
         </is>
       </c>
       <c r="AA91" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
-        </is>
-      </c>
-      <c r="AB91" t="inlineStr">
-        <is>
-          <t>12:29</t>
+          <t>2025-08-15</t>
         </is>
       </c>
       <c r="AD91" t="b">
@@ -10828,33 +10831,34 @@
       <c r="AE91" t="b">
         <v>0</v>
       </c>
+      <c r="AF91" t="inlineStr"/>
       <c r="AG91" t="b">
         <v>0</v>
       </c>
       <c r="AT91" t="inlineStr"/>
       <c r="AW91" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX91" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer, Birgitta Kvist, Håkan Thenander, Peter Turander</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY91" t="inlineStr"/>
       <c r="AZ91" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136689345</t>
+          <t>https://artportalen.se/Sighting/127627101</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>126480574</v>
+        <v>136689345</v>
       </c>
       <c r="B92" t="n">
-        <v>79084</v>
+        <v>83461</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -10862,37 +10866,37 @@
         </is>
       </c>
       <c r="E92" t="n">
-        <v>6446</v>
+        <v>6440</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I92" t="inlineStr"/>
       <c r="P92" t="inlineStr">
         <is>
-          <t>Kölbron, Kölbron, Dlr</t>
+          <t>Kölbron, Dlr</t>
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>464743</v>
+        <v>464739</v>
       </c>
       <c r="R92" t="n">
-        <v>6784623</v>
+        <v>6784695</v>
       </c>
       <c r="S92" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T92" t="inlineStr">
         <is>
@@ -10916,22 +10920,22 @@
       </c>
       <c r="Y92" t="inlineStr">
         <is>
-          <t>2025-07-07</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="Z92" t="inlineStr">
         <is>
-          <t>09:31</t>
+          <t>12:29</t>
         </is>
       </c>
       <c r="AA92" t="inlineStr">
         <is>
-          <t>2025-07-07</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="AB92" t="inlineStr">
         <is>
-          <t>09:31</t>
+          <t>12:29</t>
         </is>
       </c>
       <c r="AD92" t="b">
@@ -10957,16 +10961,16 @@
       <c r="AY92" t="inlineStr"/>
       <c r="AZ92" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/126480574</t>
+          <t>https://artportalen.se/Sighting/136689345</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>126480896</v>
+        <v>136699227</v>
       </c>
       <c r="B93" t="n">
-        <v>79946</v>
+        <v>83461</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -10974,37 +10978,37 @@
         </is>
       </c>
       <c r="E93" t="n">
-        <v>6453</v>
+        <v>6440</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I93" t="inlineStr"/>
       <c r="P93" t="inlineStr">
         <is>
-          <t>Kölbron, Kölbron, Dlr</t>
+          <t>Kölbron, Dlr</t>
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>464743</v>
+        <v>464836</v>
       </c>
       <c r="R93" t="n">
-        <v>6784623</v>
+        <v>6784711</v>
       </c>
       <c r="S93" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T93" t="inlineStr">
         <is>
@@ -11028,22 +11032,22 @@
       </c>
       <c r="Y93" t="inlineStr">
         <is>
-          <t>2025-07-07</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="Z93" t="inlineStr">
         <is>
-          <t>09:31</t>
+          <t>13:05</t>
         </is>
       </c>
       <c r="AA93" t="inlineStr">
         <is>
-          <t>2025-07-07</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="AB93" t="inlineStr">
         <is>
-          <t>09:31</t>
+          <t>13:05</t>
         </is>
       </c>
       <c r="AD93" t="b">
@@ -11058,27 +11062,27 @@
       <c r="AT93" t="inlineStr"/>
       <c r="AW93" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX93" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer, Birgitta Kvist, Håkan Thenander, Peter Turander</t>
+          <t>Håkan Thenander, Bengt Oldhammer, Peter Turander, Birgitta Kvist</t>
         </is>
       </c>
       <c r="AY93" t="inlineStr"/>
       <c r="AZ93" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/126480896</t>
+          <t>https://artportalen.se/Sighting/136699227</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>126481544</v>
+        <v>126480574</v>
       </c>
       <c r="B94" t="n">
-        <v>79946</v>
+        <v>79084</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -11086,34 +11090,34 @@
         </is>
       </c>
       <c r="E94" t="n">
-        <v>6453</v>
+        <v>6446</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I94" t="inlineStr"/>
       <c r="P94" t="inlineStr">
         <is>
-          <t>Kölbron, Dlr</t>
+          <t>Kölbron, Kölbron, Dlr</t>
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>464778</v>
+        <v>464743</v>
       </c>
       <c r="R94" t="n">
-        <v>6784647</v>
+        <v>6784623</v>
       </c>
       <c r="S94" t="n">
         <v>10</v>
@@ -11145,7 +11149,7 @@
       </c>
       <c r="Z94" t="inlineStr">
         <is>
-          <t>09:28</t>
+          <t>09:31</t>
         </is>
       </c>
       <c r="AA94" t="inlineStr">
@@ -11155,7 +11159,7 @@
       </c>
       <c r="AB94" t="inlineStr">
         <is>
-          <t>09:28</t>
+          <t>09:31</t>
         </is>
       </c>
       <c r="AD94" t="b">
@@ -11170,24 +11174,24 @@
       <c r="AT94" t="inlineStr"/>
       <c r="AW94" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bengt Oldhammer</t>
         </is>
       </c>
       <c r="AX94" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bengt Oldhammer, Birgitta Kvist, Håkan Thenander, Peter Turander</t>
         </is>
       </c>
       <c r="AY94" t="inlineStr"/>
       <c r="AZ94" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/126481544</t>
+          <t>https://artportalen.se/Sighting/126480574</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>126586980</v>
+        <v>126480896</v>
       </c>
       <c r="B95" t="n">
         <v>79946</v>
@@ -11218,14 +11222,14 @@
       <c r="I95" t="inlineStr"/>
       <c r="P95" t="inlineStr">
         <is>
-          <t>Kölbron, Dlr</t>
+          <t>Kölbron, Kölbron, Dlr</t>
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>464671</v>
+        <v>464743</v>
       </c>
       <c r="R95" t="n">
-        <v>6784711</v>
+        <v>6784623</v>
       </c>
       <c r="S95" t="n">
         <v>10</v>
@@ -11252,22 +11256,22 @@
       </c>
       <c r="Y95" t="inlineStr">
         <is>
-          <t>2025-07-11</t>
+          <t>2025-07-07</t>
         </is>
       </c>
       <c r="Z95" t="inlineStr">
         <is>
-          <t>14:22</t>
+          <t>09:31</t>
         </is>
       </c>
       <c r="AA95" t="inlineStr">
         <is>
-          <t>2025-07-11</t>
+          <t>2025-07-07</t>
         </is>
       </c>
       <c r="AB95" t="inlineStr">
         <is>
-          <t>14:22</t>
+          <t>09:31</t>
         </is>
       </c>
       <c r="AD95" t="b">
@@ -11282,62 +11286,62 @@
       <c r="AT95" t="inlineStr"/>
       <c r="AW95" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bengt Oldhammer</t>
         </is>
       </c>
       <c r="AX95" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bengt Oldhammer, Birgitta Kvist, Håkan Thenander, Peter Turander</t>
         </is>
       </c>
       <c r="AY95" t="inlineStr"/>
       <c r="AZ95" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/126586980</t>
+          <t>https://artportalen.se/Sighting/126480896</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>126485124</v>
+        <v>126481544</v>
       </c>
       <c r="B96" t="n">
-        <v>80468</v>
+        <v>79946</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E96" t="n">
-        <v>6464</v>
+        <v>6453</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I96" t="inlineStr"/>
       <c r="P96" t="inlineStr">
         <is>
-          <t>Bjönsaberg, Bjönsaberg, Dlr</t>
+          <t>Kölbron, Dlr</t>
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>464772</v>
+        <v>464778</v>
       </c>
       <c r="R96" t="n">
-        <v>6784708</v>
+        <v>6784647</v>
       </c>
       <c r="S96" t="n">
         <v>10</v>
@@ -11369,7 +11373,7 @@
       </c>
       <c r="Z96" t="inlineStr">
         <is>
-          <t>10:30</t>
+          <t>09:28</t>
         </is>
       </c>
       <c r="AA96" t="inlineStr">
@@ -11379,7 +11383,7 @@
       </c>
       <c r="AB96" t="inlineStr">
         <is>
-          <t>10:30</t>
+          <t>09:28</t>
         </is>
       </c>
       <c r="AD96" t="b">
@@ -11394,67 +11398,62 @@
       <c r="AT96" t="inlineStr"/>
       <c r="AW96" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX96" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer, Birgitta Kvist, Håkan Thenander, Peter Turander</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY96" t="inlineStr"/>
       <c r="AZ96" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/126485124</t>
+          <t>https://artportalen.se/Sighting/126481544</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>126481501</v>
+        <v>126586980</v>
       </c>
       <c r="B97" t="n">
-        <v>57950</v>
+        <v>79946</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E97" t="n">
-        <v>100049</v>
+        <v>6453</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I97" t="inlineStr"/>
-      <c r="M97" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P97" t="inlineStr">
         <is>
-          <t>Kölbron, Kölbron, Dlr</t>
+          <t>Kölbron, Dlr</t>
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>464730</v>
+        <v>464671</v>
       </c>
       <c r="R97" t="n">
-        <v>6784658</v>
+        <v>6784711</v>
       </c>
       <c r="S97" t="n">
         <v>10</v>
@@ -11481,22 +11480,22 @@
       </c>
       <c r="Y97" t="inlineStr">
         <is>
-          <t>2025-07-07</t>
+          <t>2025-07-11</t>
         </is>
       </c>
       <c r="Z97" t="inlineStr">
         <is>
-          <t>09:31</t>
+          <t>14:22</t>
         </is>
       </c>
       <c r="AA97" t="inlineStr">
         <is>
-          <t>2025-07-07</t>
+          <t>2025-07-11</t>
         </is>
       </c>
       <c r="AB97" t="inlineStr">
         <is>
-          <t>09:31</t>
+          <t>14:22</t>
         </is>
       </c>
       <c r="AD97" t="b">
@@ -11511,27 +11510,27 @@
       <c r="AT97" t="inlineStr"/>
       <c r="AW97" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX97" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer, Birgitta Kvist, Håkan Thenander, Peter Turander</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY97" t="inlineStr"/>
       <c r="AZ97" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/126481501</t>
+          <t>https://artportalen.se/Sighting/126586980</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>126483169</v>
+        <v>126485124</v>
       </c>
       <c r="B98" t="n">
-        <v>57950</v>
+        <v>80468</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -11539,39 +11538,34 @@
         </is>
       </c>
       <c r="E98" t="n">
-        <v>100049</v>
+        <v>6464</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I98" t="inlineStr"/>
-      <c r="M98" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P98" t="inlineStr">
         <is>
-          <t>Kölbron, Dlr</t>
+          <t>Bjönsaberg, Bjönsaberg, Dlr</t>
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>464732</v>
+        <v>464772</v>
       </c>
       <c r="R98" t="n">
-        <v>6784654</v>
+        <v>6784708</v>
       </c>
       <c r="S98" t="n">
         <v>10</v>
@@ -11603,7 +11597,7 @@
       </c>
       <c r="Z98" t="inlineStr">
         <is>
-          <t>09:56</t>
+          <t>10:30</t>
         </is>
       </c>
       <c r="AA98" t="inlineStr">
@@ -11613,7 +11607,7 @@
       </c>
       <c r="AB98" t="inlineStr">
         <is>
-          <t>09:56</t>
+          <t>10:30</t>
         </is>
       </c>
       <c r="AD98" t="b">
@@ -11628,24 +11622,24 @@
       <c r="AT98" t="inlineStr"/>
       <c r="AW98" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bengt Oldhammer</t>
         </is>
       </c>
       <c r="AX98" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bengt Oldhammer, Birgitta Kvist, Håkan Thenander, Peter Turander</t>
         </is>
       </c>
       <c r="AY98" t="inlineStr"/>
       <c r="AZ98" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/126483169</t>
+          <t>https://artportalen.se/Sighting/126485124</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>126485146</v>
+        <v>126481501</v>
       </c>
       <c r="B99" t="n">
         <v>57950</v>
@@ -11685,10 +11679,10 @@
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>464765</v>
+        <v>464730</v>
       </c>
       <c r="R99" t="n">
-        <v>6784693</v>
+        <v>6784658</v>
       </c>
       <c r="S99" t="n">
         <v>10</v>
@@ -11720,7 +11714,7 @@
       </c>
       <c r="Z99" t="inlineStr">
         <is>
-          <t>10:35</t>
+          <t>09:31</t>
         </is>
       </c>
       <c r="AA99" t="inlineStr">
@@ -11730,7 +11724,7 @@
       </c>
       <c r="AB99" t="inlineStr">
         <is>
-          <t>10:35</t>
+          <t>09:31</t>
         </is>
       </c>
       <c r="AD99" t="b">
@@ -11756,13 +11750,13 @@
       <c r="AY99" t="inlineStr"/>
       <c r="AZ99" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/126485146</t>
+          <t>https://artportalen.se/Sighting/126481501</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>126585359</v>
+        <v>126483169</v>
       </c>
       <c r="B100" t="n">
         <v>57950</v>
@@ -11793,7 +11787,7 @@
       <c r="I100" t="inlineStr"/>
       <c r="M100" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P100" t="inlineStr">
@@ -11802,10 +11796,10 @@
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>464766</v>
+        <v>464732</v>
       </c>
       <c r="R100" t="n">
-        <v>6784628</v>
+        <v>6784654</v>
       </c>
       <c r="S100" t="n">
         <v>10</v>
@@ -11832,22 +11826,22 @@
       </c>
       <c r="Y100" t="inlineStr">
         <is>
-          <t>2025-07-11</t>
+          <t>2025-07-07</t>
         </is>
       </c>
       <c r="Z100" t="inlineStr">
         <is>
-          <t>14:15</t>
+          <t>09:56</t>
         </is>
       </c>
       <c r="AA100" t="inlineStr">
         <is>
-          <t>2025-07-11</t>
+          <t>2025-07-07</t>
         </is>
       </c>
       <c r="AB100" t="inlineStr">
         <is>
-          <t>14:15</t>
+          <t>09:56</t>
         </is>
       </c>
       <c r="AD100" t="b">
@@ -11873,13 +11867,13 @@
       <c r="AY100" t="inlineStr"/>
       <c r="AZ100" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/126585359</t>
+          <t>https://artportalen.se/Sighting/126483169</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>126585897</v>
+        <v>126485146</v>
       </c>
       <c r="B101" t="n">
         <v>57950</v>
@@ -11910,19 +11904,19 @@
       <c r="I101" t="inlineStr"/>
       <c r="M101" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P101" t="inlineStr">
         <is>
-          <t>Kölbron, Dlr</t>
+          <t>Kölbron, Kölbron, Dlr</t>
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>464732</v>
+        <v>464765</v>
       </c>
       <c r="R101" t="n">
-        <v>6784658</v>
+        <v>6784693</v>
       </c>
       <c r="S101" t="n">
         <v>10</v>
@@ -11949,22 +11943,22 @@
       </c>
       <c r="Y101" t="inlineStr">
         <is>
-          <t>2025-07-11</t>
+          <t>2025-07-07</t>
         </is>
       </c>
       <c r="Z101" t="inlineStr">
         <is>
-          <t>14:22</t>
+          <t>10:35</t>
         </is>
       </c>
       <c r="AA101" t="inlineStr">
         <is>
-          <t>2025-07-11</t>
+          <t>2025-07-07</t>
         </is>
       </c>
       <c r="AB101" t="inlineStr">
         <is>
-          <t>14:22</t>
+          <t>10:35</t>
         </is>
       </c>
       <c r="AD101" t="b">
@@ -11979,27 +11973,27 @@
       <c r="AT101" t="inlineStr"/>
       <c r="AW101" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bengt Oldhammer</t>
         </is>
       </c>
       <c r="AX101" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bengt Oldhammer, Birgitta Kvist, Håkan Thenander, Peter Turander</t>
         </is>
       </c>
       <c r="AY101" t="inlineStr"/>
       <c r="AZ101" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/126585897</t>
+          <t>https://artportalen.se/Sighting/126485146</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>136689339</v>
+        <v>126585359</v>
       </c>
       <c r="B102" t="n">
-        <v>57193</v>
+        <v>57950</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -12007,37 +12001,42 @@
         </is>
       </c>
       <c r="E102" t="n">
-        <v>100138</v>
+        <v>100049</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I102" t="inlineStr"/>
+      <c r="M102" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="P102" t="inlineStr">
         <is>
           <t>Kölbron, Dlr</t>
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>464678</v>
+        <v>464766</v>
       </c>
       <c r="R102" t="n">
-        <v>6784706</v>
+        <v>6784628</v>
       </c>
       <c r="S102" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T102" t="inlineStr">
         <is>
@@ -12061,27 +12060,22 @@
       </c>
       <c r="Y102" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2025-07-11</t>
         </is>
       </c>
       <c r="Z102" t="inlineStr">
         <is>
-          <t>12:12</t>
+          <t>14:15</t>
         </is>
       </c>
       <c r="AA102" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2025-07-11</t>
         </is>
       </c>
       <c r="AB102" t="inlineStr">
         <is>
-          <t>12:12</t>
-        </is>
-      </c>
-      <c r="AC102" t="inlineStr">
-        <is>
-          <t>Fjäder höna</t>
+          <t>14:15</t>
         </is>
       </c>
       <c r="AD102" t="b">
@@ -12096,27 +12090,27 @@
       <c r="AT102" t="inlineStr"/>
       <c r="AW102" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX102" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY102" t="inlineStr"/>
       <c r="AZ102" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136689339</t>
+          <t>https://artportalen.se/Sighting/126585359</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>136689328</v>
+        <v>126585897</v>
       </c>
       <c r="B103" t="n">
-        <v>5182</v>
+        <v>57950</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -12124,27 +12118,27 @@
         </is>
       </c>
       <c r="E103" t="n">
-        <v>100526</v>
+        <v>100049</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I103" t="inlineStr"/>
       <c r="M103" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P103" t="inlineStr">
@@ -12153,13 +12147,13 @@
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>464694</v>
+        <v>464732</v>
       </c>
       <c r="R103" t="n">
         <v>6784658</v>
       </c>
       <c r="S103" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T103" t="inlineStr">
         <is>
@@ -12183,22 +12177,22 @@
       </c>
       <c r="Y103" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2025-07-11</t>
         </is>
       </c>
       <c r="Z103" t="inlineStr">
         <is>
-          <t>11:52</t>
+          <t>14:22</t>
         </is>
       </c>
       <c r="AA103" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2025-07-11</t>
         </is>
       </c>
       <c r="AB103" t="inlineStr">
         <is>
-          <t>11:52</t>
+          <t>14:22</t>
         </is>
       </c>
       <c r="AD103" t="b">
@@ -12213,44 +12207,44 @@
       <c r="AT103" t="inlineStr"/>
       <c r="AW103" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX103" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY103" t="inlineStr"/>
       <c r="AZ103" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136689328</t>
+          <t>https://artportalen.se/Sighting/126585897</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>126485436</v>
+        <v>136699220</v>
       </c>
       <c r="B104" t="n">
-        <v>57774</v>
+        <v>58006</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E104" t="n">
-        <v>102976</v>
+        <v>100109</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Tornseglare</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>Apus apus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
@@ -12261,7 +12255,7 @@
       <c r="I104" t="inlineStr"/>
       <c r="M104" t="inlineStr">
         <is>
-          <t>födosökande</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P104" t="inlineStr">
@@ -12270,13 +12264,13 @@
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>464793</v>
+        <v>464683</v>
       </c>
       <c r="R104" t="n">
-        <v>6784773</v>
+        <v>6784674</v>
       </c>
       <c r="S104" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T104" t="inlineStr">
         <is>
@@ -12300,22 +12294,22 @@
       </c>
       <c r="Y104" t="inlineStr">
         <is>
-          <t>2025-07-07</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="Z104" t="inlineStr">
         <is>
-          <t>09:56</t>
+          <t>11:58</t>
         </is>
       </c>
       <c r="AA104" t="inlineStr">
         <is>
-          <t>2025-07-07</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="AB104" t="inlineStr">
         <is>
-          <t>09:56</t>
+          <t>11:58</t>
         </is>
       </c>
       <c r="AD104" t="b">
@@ -12335,39 +12329,39 @@
       </c>
       <c r="AX104" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Håkan Thenander, Bengt Oldhammer, Peter Turander, Birgitta Kvist</t>
         </is>
       </c>
       <c r="AY104" t="inlineStr"/>
       <c r="AZ104" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/126485436</t>
+          <t>https://artportalen.se/Sighting/136699220</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>126485010</v>
+        <v>136699222</v>
       </c>
       <c r="B105" t="n">
-        <v>58327</v>
+        <v>58006</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E105" t="n">
-        <v>103015</v>
+        <v>100109</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
@@ -12378,7 +12372,7 @@
       <c r="I105" t="inlineStr"/>
       <c r="M105" t="inlineStr">
         <is>
-          <t>spel/sång</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P105" t="inlineStr">
@@ -12387,13 +12381,13 @@
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>464828</v>
+        <v>464745</v>
       </c>
       <c r="R105" t="n">
-        <v>6784703</v>
+        <v>6784670</v>
       </c>
       <c r="S105" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="T105" t="inlineStr">
         <is>
@@ -12417,22 +12411,22 @@
       </c>
       <c r="Y105" t="inlineStr">
         <is>
-          <t>2025-07-07</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="Z105" t="inlineStr">
         <is>
-          <t>09:56</t>
+          <t>12:31</t>
         </is>
       </c>
       <c r="AA105" t="inlineStr">
         <is>
-          <t>2025-07-07</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="AB105" t="inlineStr">
         <is>
-          <t>09:56</t>
+          <t>12:31</t>
         </is>
       </c>
       <c r="AD105" t="b">
@@ -12452,22 +12446,22 @@
       </c>
       <c r="AX105" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Håkan Thenander, Bengt Oldhammer, Peter Turander, Birgitta Kvist</t>
         </is>
       </c>
       <c r="AY105" t="inlineStr"/>
       <c r="AZ105" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/126485010</t>
+          <t>https://artportalen.se/Sighting/136699222</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>136689332</v>
+        <v>136699223</v>
       </c>
       <c r="B106" t="n">
-        <v>58167</v>
+        <v>58006</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -12475,37 +12469,42 @@
         </is>
       </c>
       <c r="E106" t="n">
-        <v>103021</v>
+        <v>100109</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I106" t="inlineStr"/>
+      <c r="M106" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P106" t="inlineStr">
         <is>
           <t>Kölbron, Dlr</t>
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>464682</v>
+        <v>464746</v>
       </c>
       <c r="R106" t="n">
-        <v>6784686</v>
+        <v>6784670</v>
       </c>
       <c r="S106" t="n">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="T106" t="inlineStr">
         <is>
@@ -12534,7 +12533,7 @@
       </c>
       <c r="Z106" t="inlineStr">
         <is>
-          <t>11:59</t>
+          <t>12:34</t>
         </is>
       </c>
       <c r="AA106" t="inlineStr">
@@ -12544,7 +12543,7 @@
       </c>
       <c r="AB106" t="inlineStr">
         <is>
-          <t>11:59</t>
+          <t>12:34</t>
         </is>
       </c>
       <c r="AD106" t="b">
@@ -12559,55 +12558,59 @@
       <c r="AT106" t="inlineStr"/>
       <c r="AW106" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX106" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer</t>
+          <t>Håkan Thenander, Bengt Oldhammer, Peter Turander, Birgitta Kvist</t>
         </is>
       </c>
       <c r="AY106" t="inlineStr"/>
       <c r="AZ106" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136689332</t>
+          <t>https://artportalen.se/Sighting/136699223</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>136689326</v>
+        <v>136699229</v>
       </c>
       <c r="B107" t="n">
-        <v>58627</v>
+        <v>58006</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E107" t="n">
-        <v>103041</v>
+        <v>100109</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Bergfink</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>Fringilla montifringilla</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I107" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I107" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="M107" t="inlineStr">
         <is>
-          <t>sträckande</t>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="P107" t="inlineStr">
@@ -12616,13 +12619,13 @@
         </is>
       </c>
       <c r="Q107" t="n">
-        <v>464735</v>
+        <v>464742</v>
       </c>
       <c r="R107" t="n">
-        <v>6784626</v>
+        <v>6784839</v>
       </c>
       <c r="S107" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="T107" t="inlineStr">
         <is>
@@ -12651,7 +12654,7 @@
       </c>
       <c r="Z107" t="inlineStr">
         <is>
-          <t>11:45</t>
+          <t>13:29</t>
         </is>
       </c>
       <c r="AA107" t="inlineStr">
@@ -12661,7 +12664,12 @@
       </c>
       <c r="AB107" t="inlineStr">
         <is>
-          <t>11:45</t>
+          <t>13:29</t>
+        </is>
+      </c>
+      <c r="AC107" t="inlineStr">
+        <is>
+          <t>Troligen hona med unge, födosökande och revirtrummande.</t>
         </is>
       </c>
       <c r="AD107" t="b">
@@ -12676,27 +12684,27 @@
       <c r="AT107" t="inlineStr"/>
       <c r="AW107" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX107" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer</t>
+          <t>Håkan Thenander, Bengt Oldhammer, Peter Turander, Birgitta Kvist</t>
         </is>
       </c>
       <c r="AY107" t="inlineStr"/>
       <c r="AZ107" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136689326</t>
+          <t>https://artportalen.se/Sighting/136699229</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>136689334</v>
+        <v>136689339</v>
       </c>
       <c r="B108" t="n">
-        <v>58665</v>
+        <v>57193</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -12704,42 +12712,37 @@
         </is>
       </c>
       <c r="E108" t="n">
-        <v>103046</v>
+        <v>100138</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Gråsiska</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>Acanthis flammea</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I108" t="inlineStr"/>
-      <c r="M108" t="inlineStr">
-        <is>
-          <t>förbiflygande</t>
-        </is>
-      </c>
       <c r="P108" t="inlineStr">
         <is>
           <t>Kölbron, Dlr</t>
         </is>
       </c>
       <c r="Q108" t="n">
-        <v>464680</v>
+        <v>464678</v>
       </c>
       <c r="R108" t="n">
-        <v>6784680</v>
+        <v>6784706</v>
       </c>
       <c r="S108" t="n">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="T108" t="inlineStr">
         <is>
@@ -12768,7 +12771,7 @@
       </c>
       <c r="Z108" t="inlineStr">
         <is>
-          <t>12:03</t>
+          <t>12:12</t>
         </is>
       </c>
       <c r="AA108" t="inlineStr">
@@ -12778,7 +12781,12 @@
       </c>
       <c r="AB108" t="inlineStr">
         <is>
-          <t>12:03</t>
+          <t>12:12</t>
+        </is>
+      </c>
+      <c r="AC108" t="inlineStr">
+        <is>
+          <t>Fjäder höna</t>
         </is>
       </c>
       <c r="AD108" t="b">
@@ -12804,16 +12812,16 @@
       <c r="AY108" t="inlineStr"/>
       <c r="AZ108" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136689334</t>
+          <t>https://artportalen.se/Sighting/136689339</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>136689330</v>
+        <v>136689328</v>
       </c>
       <c r="B109" t="n">
-        <v>5202</v>
+        <v>5182</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -12821,21 +12829,21 @@
         </is>
       </c>
       <c r="E109" t="n">
-        <v>105930</v>
+        <v>100526</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I109" t="inlineStr"/>
@@ -12850,13 +12858,13 @@
         </is>
       </c>
       <c r="Q109" t="n">
-        <v>464681</v>
+        <v>464694</v>
       </c>
       <c r="R109" t="n">
-        <v>6784664</v>
+        <v>6784658</v>
       </c>
       <c r="S109" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T109" t="inlineStr">
         <is>
@@ -12885,7 +12893,7 @@
       </c>
       <c r="Z109" t="inlineStr">
         <is>
-          <t>11:56</t>
+          <t>11:52</t>
         </is>
       </c>
       <c r="AA109" t="inlineStr">
@@ -12895,7 +12903,7 @@
       </c>
       <c r="AB109" t="inlineStr">
         <is>
-          <t>11:56</t>
+          <t>11:52</t>
         </is>
       </c>
       <c r="AD109" t="b">
@@ -12921,56 +12929,56 @@
       <c r="AY109" t="inlineStr"/>
       <c r="AZ109" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136689330</t>
+          <t>https://artportalen.se/Sighting/136689328</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>126481482</v>
+        <v>126485436</v>
       </c>
       <c r="B110" t="n">
-        <v>8455</v>
+        <v>57774</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E110" t="n">
-        <v>106545</v>
+        <v>102976</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Tornseglare</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Apus apus</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I110" t="inlineStr"/>
       <c r="M110" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
+          <t>födosökande</t>
         </is>
       </c>
       <c r="P110" t="inlineStr">
         <is>
-          <t>Kölbron, Kölbron, Dlr</t>
+          <t>Kölbron, Dlr</t>
         </is>
       </c>
       <c r="Q110" t="n">
-        <v>464730</v>
+        <v>464793</v>
       </c>
       <c r="R110" t="n">
-        <v>6784658</v>
+        <v>6784773</v>
       </c>
       <c r="S110" t="n">
         <v>10</v>
@@ -13002,7 +13010,7 @@
       </c>
       <c r="Z110" t="inlineStr">
         <is>
-          <t>09:31</t>
+          <t>09:56</t>
         </is>
       </c>
       <c r="AA110" t="inlineStr">
@@ -13012,7 +13020,7 @@
       </c>
       <c r="AB110" t="inlineStr">
         <is>
-          <t>09:31</t>
+          <t>09:56</t>
         </is>
       </c>
       <c r="AD110" t="b">
@@ -13027,27 +13035,27 @@
       <c r="AT110" t="inlineStr"/>
       <c r="AW110" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX110" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer, Birgitta Kvist, Håkan Thenander, Peter Turander</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY110" t="inlineStr"/>
       <c r="AZ110" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/126481482</t>
+          <t>https://artportalen.se/Sighting/126485436</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="n">
-        <v>126483158</v>
+        <v>126485010</v>
       </c>
       <c r="B111" t="n">
-        <v>8455</v>
+        <v>58327</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -13055,34 +13063,39 @@
         </is>
       </c>
       <c r="E111" t="n">
-        <v>106545</v>
+        <v>103015</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I111" t="inlineStr"/>
+      <c r="M111" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="P111" t="inlineStr">
         <is>
           <t>Kölbron, Dlr</t>
         </is>
       </c>
       <c r="Q111" t="n">
-        <v>464732</v>
+        <v>464828</v>
       </c>
       <c r="R111" t="n">
-        <v>6784654</v>
+        <v>6784703</v>
       </c>
       <c r="S111" t="n">
         <v>10</v>
@@ -13150,59 +13163,54 @@
       <c r="AY111" t="inlineStr"/>
       <c r="AZ111" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/126483158</t>
+          <t>https://artportalen.se/Sighting/126485010</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="n">
-        <v>126484808</v>
+        <v>136689332</v>
       </c>
       <c r="B112" t="n">
-        <v>8455</v>
+        <v>58167</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E112" t="n">
-        <v>106545</v>
+        <v>103021</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I112" t="inlineStr"/>
-      <c r="M112" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P112" t="inlineStr">
         <is>
-          <t>Kölbron, Kölbron, Dlr</t>
+          <t>Kölbron, Dlr</t>
         </is>
       </c>
       <c r="Q112" t="n">
-        <v>464775</v>
+        <v>464682</v>
       </c>
       <c r="R112" t="n">
-        <v>6784702</v>
+        <v>6784686</v>
       </c>
       <c r="S112" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="T112" t="inlineStr">
         <is>
@@ -13226,22 +13234,22 @@
       </c>
       <c r="Y112" t="inlineStr">
         <is>
-          <t>2025-07-07</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="Z112" t="inlineStr">
         <is>
-          <t>10:22</t>
+          <t>11:59</t>
         </is>
       </c>
       <c r="AA112" t="inlineStr">
         <is>
-          <t>2025-07-07</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="AB112" t="inlineStr">
         <is>
-          <t>10:22</t>
+          <t>11:59</t>
         </is>
       </c>
       <c r="AD112" t="b">
@@ -13261,22 +13269,22 @@
       </c>
       <c r="AX112" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer, Birgitta Kvist, Håkan Thenander, Peter Turander</t>
+          <t>Bengt Oldhammer</t>
         </is>
       </c>
       <c r="AY112" t="inlineStr"/>
       <c r="AZ112" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/126484808</t>
+          <t>https://artportalen.se/Sighting/136689332</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>126485952</v>
+        <v>136689326</v>
       </c>
       <c r="B113" t="n">
-        <v>8455</v>
+        <v>58627</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -13284,42 +13292,42 @@
         </is>
       </c>
       <c r="E113" t="n">
-        <v>106545</v>
+        <v>103041</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Bergfink</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Fringilla montifringilla</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I113" t="inlineStr"/>
       <c r="M113" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
+          <t>sträckande</t>
         </is>
       </c>
       <c r="P113" t="inlineStr">
         <is>
-          <t>Kölbron, Kölbron, Dlr</t>
+          <t>Kölbron, Dlr</t>
         </is>
       </c>
       <c r="Q113" t="n">
-        <v>464750</v>
+        <v>464735</v>
       </c>
       <c r="R113" t="n">
-        <v>6784735</v>
+        <v>6784626</v>
       </c>
       <c r="S113" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="T113" t="inlineStr">
         <is>
@@ -13343,22 +13351,22 @@
       </c>
       <c r="Y113" t="inlineStr">
         <is>
-          <t>2025-07-07</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="Z113" t="inlineStr">
         <is>
-          <t>10:35</t>
+          <t>11:45</t>
         </is>
       </c>
       <c r="AA113" t="inlineStr">
         <is>
-          <t>2025-07-07</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="AB113" t="inlineStr">
         <is>
-          <t>10:35</t>
+          <t>11:45</t>
         </is>
       </c>
       <c r="AD113" t="b">
@@ -13378,22 +13386,22 @@
       </c>
       <c r="AX113" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer, Birgitta Kvist, Håkan Thenander, Peter Turander</t>
+          <t>Bengt Oldhammer</t>
         </is>
       </c>
       <c r="AY113" t="inlineStr"/>
       <c r="AZ113" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/126485952</t>
+          <t>https://artportalen.se/Sighting/136689326</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>126585639</v>
+        <v>136689334</v>
       </c>
       <c r="B114" t="n">
-        <v>8455</v>
+        <v>58665</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -13401,37 +13409,42 @@
         </is>
       </c>
       <c r="E114" t="n">
-        <v>106545</v>
+        <v>103046</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Gråsiska</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Acanthis flammea</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I114" t="inlineStr"/>
+      <c r="M114" t="inlineStr">
+        <is>
+          <t>förbiflygande</t>
+        </is>
+      </c>
       <c r="P114" t="inlineStr">
         <is>
           <t>Kölbron, Dlr</t>
         </is>
       </c>
       <c r="Q114" t="n">
-        <v>464704</v>
+        <v>464680</v>
       </c>
       <c r="R114" t="n">
-        <v>6784647</v>
+        <v>6784680</v>
       </c>
       <c r="S114" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="T114" t="inlineStr">
         <is>
@@ -13455,22 +13468,22 @@
       </c>
       <c r="Y114" t="inlineStr">
         <is>
-          <t>2025-07-11</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="Z114" t="inlineStr">
         <is>
-          <t>14:22</t>
+          <t>12:03</t>
         </is>
       </c>
       <c r="AA114" t="inlineStr">
         <is>
-          <t>2025-07-11</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="AB114" t="inlineStr">
         <is>
-          <t>14:22</t>
+          <t>12:03</t>
         </is>
       </c>
       <c r="AD114" t="b">
@@ -13485,27 +13498,27 @@
       <c r="AT114" t="inlineStr"/>
       <c r="AW114" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bengt Oldhammer</t>
         </is>
       </c>
       <c r="AX114" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bengt Oldhammer</t>
         </is>
       </c>
       <c r="AY114" t="inlineStr"/>
       <c r="AZ114" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/126585639</t>
+          <t>https://artportalen.se/Sighting/136689334</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>126589767</v>
+        <v>136689330</v>
       </c>
       <c r="B115" t="n">
-        <v>8455</v>
+        <v>5202</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -13513,34 +13526,39 @@
         </is>
       </c>
       <c r="E115" t="n">
-        <v>106545</v>
+        <v>105930</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I115" t="inlineStr"/>
+      <c r="M115" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P115" t="inlineStr">
         <is>
           <t>Kölbron, Dlr</t>
         </is>
       </c>
       <c r="Q115" t="n">
-        <v>464839</v>
+        <v>464681</v>
       </c>
       <c r="R115" t="n">
-        <v>6784720</v>
+        <v>6784664</v>
       </c>
       <c r="S115" t="n">
         <v>10</v>
@@ -13567,22 +13585,22 @@
       </c>
       <c r="Y115" t="inlineStr">
         <is>
-          <t>2025-07-11</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="Z115" t="inlineStr">
         <is>
-          <t>16:38</t>
+          <t>11:56</t>
         </is>
       </c>
       <c r="AA115" t="inlineStr">
         <is>
-          <t>2025-07-11</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="AB115" t="inlineStr">
         <is>
-          <t>16:38</t>
+          <t>11:56</t>
         </is>
       </c>
       <c r="AD115" t="b">
@@ -13597,24 +13615,24 @@
       <c r="AT115" t="inlineStr"/>
       <c r="AW115" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bengt Oldhammer</t>
         </is>
       </c>
       <c r="AX115" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bengt Oldhammer</t>
         </is>
       </c>
       <c r="AY115" t="inlineStr"/>
       <c r="AZ115" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/126589767</t>
+          <t>https://artportalen.se/Sighting/136689330</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>126589818</v>
+        <v>126481482</v>
       </c>
       <c r="B116" t="n">
         <v>8455</v>
@@ -13643,16 +13661,21 @@
         </is>
       </c>
       <c r="I116" t="inlineStr"/>
+      <c r="M116" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P116" t="inlineStr">
         <is>
-          <t>Kölbron, Dlr</t>
+          <t>Kölbron, Kölbron, Dlr</t>
         </is>
       </c>
       <c r="Q116" t="n">
-        <v>464831</v>
+        <v>464730</v>
       </c>
       <c r="R116" t="n">
-        <v>6784718</v>
+        <v>6784658</v>
       </c>
       <c r="S116" t="n">
         <v>10</v>
@@ -13679,22 +13702,22 @@
       </c>
       <c r="Y116" t="inlineStr">
         <is>
-          <t>2025-07-11</t>
+          <t>2025-07-07</t>
         </is>
       </c>
       <c r="Z116" t="inlineStr">
         <is>
-          <t>16:38</t>
+          <t>09:31</t>
         </is>
       </c>
       <c r="AA116" t="inlineStr">
         <is>
-          <t>2025-07-11</t>
+          <t>2025-07-07</t>
         </is>
       </c>
       <c r="AB116" t="inlineStr">
         <is>
-          <t>16:38</t>
+          <t>09:31</t>
         </is>
       </c>
       <c r="AD116" t="b">
@@ -13709,27 +13732,27 @@
       <c r="AT116" t="inlineStr"/>
       <c r="AW116" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bengt Oldhammer</t>
         </is>
       </c>
       <c r="AX116" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bengt Oldhammer, Birgitta Kvist, Håkan Thenander, Peter Turander</t>
         </is>
       </c>
       <c r="AY116" t="inlineStr"/>
       <c r="AZ116" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/126589818</t>
+          <t>https://artportalen.se/Sighting/126481482</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>136361108</v>
+        <v>126483158</v>
       </c>
       <c r="B117" t="n">
-        <v>8463</v>
+        <v>8455</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -13755,24 +13778,19 @@
         </is>
       </c>
       <c r="I117" t="inlineStr"/>
-      <c r="M117" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P117" t="inlineStr">
         <is>
           <t>Kölbron, Dlr</t>
         </is>
       </c>
       <c r="Q117" t="n">
-        <v>464700</v>
+        <v>464732</v>
       </c>
       <c r="R117" t="n">
-        <v>6784824</v>
+        <v>6784654</v>
       </c>
       <c r="S117" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T117" t="inlineStr">
         <is>
@@ -13796,22 +13814,22 @@
       </c>
       <c r="Y117" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2025-07-07</t>
         </is>
       </c>
       <c r="Z117" t="inlineStr">
         <is>
-          <t>11:53</t>
+          <t>09:56</t>
         </is>
       </c>
       <c r="AA117" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2025-07-07</t>
         </is>
       </c>
       <c r="AB117" t="inlineStr">
         <is>
-          <t>11:53</t>
+          <t>09:56</t>
         </is>
       </c>
       <c r="AD117" t="b">
@@ -13837,16 +13855,16 @@
       <c r="AY117" t="inlineStr"/>
       <c r="AZ117" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136361108</t>
+          <t>https://artportalen.se/Sighting/126483158</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="n">
-        <v>136689325</v>
+        <v>126484808</v>
       </c>
       <c r="B118" t="n">
-        <v>8463</v>
+        <v>8455</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -13879,17 +13897,17 @@
       </c>
       <c r="P118" t="inlineStr">
         <is>
-          <t>Kölbron, Dlr</t>
+          <t>Kölbron, Kölbron, Dlr</t>
         </is>
       </c>
       <c r="Q118" t="n">
-        <v>464761</v>
+        <v>464775</v>
       </c>
       <c r="R118" t="n">
-        <v>6784614</v>
+        <v>6784702</v>
       </c>
       <c r="S118" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T118" t="inlineStr">
         <is>
@@ -13913,22 +13931,22 @@
       </c>
       <c r="Y118" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2025-07-07</t>
         </is>
       </c>
       <c r="Z118" t="inlineStr">
         <is>
-          <t>11:42</t>
+          <t>10:22</t>
         </is>
       </c>
       <c r="AA118" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2025-07-07</t>
         </is>
       </c>
       <c r="AB118" t="inlineStr">
         <is>
-          <t>11:42</t>
+          <t>10:22</t>
         </is>
       </c>
       <c r="AD118" t="b">
@@ -13948,22 +13966,22 @@
       </c>
       <c r="AX118" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer</t>
+          <t>Bengt Oldhammer, Birgitta Kvist, Håkan Thenander, Peter Turander</t>
         </is>
       </c>
       <c r="AY118" t="inlineStr"/>
       <c r="AZ118" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136689325</t>
+          <t>https://artportalen.se/Sighting/126484808</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="n">
-        <v>126483693</v>
+        <v>126485952</v>
       </c>
       <c r="B119" t="n">
-        <v>99035</v>
+        <v>8455</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -13971,37 +13989,42 @@
         </is>
       </c>
       <c r="E119" t="n">
-        <v>219790</v>
+        <v>106545</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I119" t="inlineStr"/>
+      <c r="M119" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P119" t="inlineStr">
         <is>
-          <t>Kölbron, Dlr</t>
+          <t>Kölbron, Kölbron, Dlr</t>
         </is>
       </c>
       <c r="Q119" t="n">
-        <v>464741</v>
+        <v>464750</v>
       </c>
       <c r="R119" t="n">
-        <v>6784664</v>
+        <v>6784735</v>
       </c>
       <c r="S119" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T119" t="inlineStr">
         <is>
@@ -14030,7 +14053,7 @@
       </c>
       <c r="Z119" t="inlineStr">
         <is>
-          <t>09:56</t>
+          <t>10:35</t>
         </is>
       </c>
       <c r="AA119" t="inlineStr">
@@ -14040,7 +14063,7 @@
       </c>
       <c r="AB119" t="inlineStr">
         <is>
-          <t>09:56</t>
+          <t>10:35</t>
         </is>
       </c>
       <c r="AD119" t="b">
@@ -14055,27 +14078,27 @@
       <c r="AT119" t="inlineStr"/>
       <c r="AW119" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bengt Oldhammer</t>
         </is>
       </c>
       <c r="AX119" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bengt Oldhammer, Birgitta Kvist, Håkan Thenander, Peter Turander</t>
         </is>
       </c>
       <c r="AY119" t="inlineStr"/>
       <c r="AZ119" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/126483693</t>
+          <t>https://artportalen.se/Sighting/126485952</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="n">
-        <v>136689348</v>
+        <v>126585639</v>
       </c>
       <c r="B120" t="n">
-        <v>108370</v>
+        <v>8455</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -14083,21 +14106,21 @@
         </is>
       </c>
       <c r="E120" t="n">
-        <v>220083</v>
+        <v>106545</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Brudborste</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>Cirsium heterophyllum</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>(L.) Hill</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I120" t="inlineStr"/>
@@ -14107,13 +14130,13 @@
         </is>
       </c>
       <c r="Q120" t="n">
-        <v>464746</v>
+        <v>464704</v>
       </c>
       <c r="R120" t="n">
-        <v>6784686</v>
+        <v>6784647</v>
       </c>
       <c r="S120" t="n">
-        <v>62</v>
+        <v>10</v>
       </c>
       <c r="T120" t="inlineStr">
         <is>
@@ -14137,22 +14160,22 @@
       </c>
       <c r="Y120" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2025-07-11</t>
         </is>
       </c>
       <c r="Z120" t="inlineStr">
         <is>
-          <t>12:36</t>
+          <t>14:22</t>
         </is>
       </c>
       <c r="AA120" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2025-07-11</t>
         </is>
       </c>
       <c r="AB120" t="inlineStr">
         <is>
-          <t>12:36</t>
+          <t>14:22</t>
         </is>
       </c>
       <c r="AD120" t="b">
@@ -14167,27 +14190,27 @@
       <c r="AT120" t="inlineStr"/>
       <c r="AW120" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX120" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer, Birgitta Kvist, Håkan Thenander, Peter Turander</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY120" t="inlineStr"/>
       <c r="AZ120" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136689348</t>
+          <t>https://artportalen.se/Sighting/126585639</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="n">
-        <v>136689336</v>
+        <v>126589767</v>
       </c>
       <c r="B121" t="n">
-        <v>108440</v>
+        <v>8455</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -14195,21 +14218,21 @@
         </is>
       </c>
       <c r="E121" t="n">
-        <v>220102</v>
+        <v>106545</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Kärrfibbla</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>Crepis paludosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>(L.) Moench</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I121" t="inlineStr"/>
@@ -14219,13 +14242,13 @@
         </is>
       </c>
       <c r="Q121" t="n">
-        <v>464683</v>
+        <v>464839</v>
       </c>
       <c r="R121" t="n">
-        <v>6784681</v>
+        <v>6784720</v>
       </c>
       <c r="S121" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T121" t="inlineStr">
         <is>
@@ -14249,22 +14272,22 @@
       </c>
       <c r="Y121" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2025-07-11</t>
         </is>
       </c>
       <c r="Z121" t="inlineStr">
         <is>
-          <t>12:04</t>
+          <t>16:38</t>
         </is>
       </c>
       <c r="AA121" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2025-07-11</t>
         </is>
       </c>
       <c r="AB121" t="inlineStr">
         <is>
-          <t>12:04</t>
+          <t>16:38</t>
         </is>
       </c>
       <c r="AD121" t="b">
@@ -14279,27 +14302,27 @@
       <c r="AT121" t="inlineStr"/>
       <c r="AW121" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX121" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY121" t="inlineStr"/>
       <c r="AZ121" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136689336</t>
+          <t>https://artportalen.se/Sighting/126589767</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="n">
-        <v>127020539</v>
+        <v>126589818</v>
       </c>
       <c r="B122" t="n">
-        <v>97989</v>
+        <v>8455</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
@@ -14307,45 +14330,37 @@
         </is>
       </c>
       <c r="E122" t="n">
-        <v>221941</v>
+        <v>106545</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I122" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J122" t="inlineStr"/>
-      <c r="K122" t="inlineStr"/>
-      <c r="L122" t="inlineStr"/>
-      <c r="N122" t="inlineStr"/>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I122" t="inlineStr"/>
       <c r="P122" t="inlineStr">
         <is>
           <t>Kölbron, Dlr</t>
         </is>
       </c>
       <c r="Q122" t="n">
-        <v>464774</v>
+        <v>464831</v>
       </c>
       <c r="R122" t="n">
-        <v>6784776</v>
+        <v>6784718</v>
       </c>
       <c r="S122" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T122" t="inlineStr">
         <is>
@@ -14369,17 +14384,22 @@
       </c>
       <c r="Y122" t="inlineStr">
         <is>
-          <t>2025-07-07</t>
+          <t>2025-07-11</t>
+        </is>
+      </c>
+      <c r="Z122" t="inlineStr">
+        <is>
+          <t>16:38</t>
         </is>
       </c>
       <c r="AA122" t="inlineStr">
         <is>
-          <t>2025-07-07</t>
-        </is>
-      </c>
-      <c r="AC122" t="inlineStr">
-        <is>
-          <t>Rikligt till sparsamt i området</t>
+          <t>2025-07-11</t>
+        </is>
+      </c>
+      <c r="AB122" t="inlineStr">
+        <is>
+          <t>16:38</t>
         </is>
       </c>
       <c r="AD122" t="b">
@@ -14388,7 +14408,6 @@
       <c r="AE122" t="b">
         <v>0</v>
       </c>
-      <c r="AF122" t="inlineStr"/>
       <c r="AG122" t="b">
         <v>0</v>
       </c>
@@ -14406,16 +14425,16 @@
       <c r="AY122" t="inlineStr"/>
       <c r="AZ122" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/127020539</t>
+          <t>https://artportalen.se/Sighting/126589818</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="n">
-        <v>127020521</v>
+        <v>136361108</v>
       </c>
       <c r="B123" t="n">
-        <v>97983</v>
+        <v>8463</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -14423,41 +14442,42 @@
         </is>
       </c>
       <c r="E123" t="n">
-        <v>221945</v>
+        <v>106545</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H123" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I123" t="inlineStr"/>
-      <c r="J123" t="inlineStr"/>
-      <c r="K123" t="inlineStr"/>
-      <c r="L123" t="inlineStr"/>
-      <c r="N123" t="inlineStr"/>
+      <c r="M123" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P123" t="inlineStr">
         <is>
           <t>Kölbron, Dlr</t>
         </is>
       </c>
       <c r="Q123" t="n">
-        <v>464774</v>
+        <v>464700</v>
       </c>
       <c r="R123" t="n">
-        <v>6784776</v>
+        <v>6784824</v>
       </c>
       <c r="S123" t="n">
-        <v>50</v>
+        <v>5</v>
       </c>
       <c r="T123" t="inlineStr">
         <is>
@@ -14481,12 +14501,22 @@
       </c>
       <c r="Y123" t="inlineStr">
         <is>
-          <t>2025-07-07</t>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+      <c r="Z123" t="inlineStr">
+        <is>
+          <t>11:53</t>
         </is>
       </c>
       <c r="AA123" t="inlineStr">
         <is>
-          <t>2025-07-07</t>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+      <c r="AB123" t="inlineStr">
+        <is>
+          <t>11:53</t>
         </is>
       </c>
       <c r="AD123" t="b">
@@ -14495,7 +14525,6 @@
       <c r="AE123" t="b">
         <v>0</v>
       </c>
-      <c r="AF123" t="inlineStr"/>
       <c r="AG123" t="b">
         <v>0</v>
       </c>
@@ -14513,16 +14542,16 @@
       <c r="AY123" t="inlineStr"/>
       <c r="AZ123" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/127020521</t>
+          <t>https://artportalen.se/Sighting/136361108</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="n">
-        <v>136689318</v>
+        <v>136689325</v>
       </c>
       <c r="B124" t="n">
-        <v>98207</v>
+        <v>8463</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -14530,34 +14559,39 @@
         </is>
       </c>
       <c r="E124" t="n">
-        <v>221945</v>
+        <v>106545</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H124" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I124" t="inlineStr"/>
+      <c r="M124" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P124" t="inlineStr">
         <is>
           <t>Kölbron, Dlr</t>
         </is>
       </c>
       <c r="Q124" t="n">
-        <v>464849</v>
+        <v>464761</v>
       </c>
       <c r="R124" t="n">
-        <v>6784669</v>
+        <v>6784614</v>
       </c>
       <c r="S124" t="n">
         <v>5</v>
@@ -14589,7 +14623,7 @@
       </c>
       <c r="Z124" t="inlineStr">
         <is>
-          <t>10:57</t>
+          <t>11:42</t>
         </is>
       </c>
       <c r="AA124" t="inlineStr">
@@ -14599,7 +14633,7 @@
       </c>
       <c r="AB124" t="inlineStr">
         <is>
-          <t>10:57</t>
+          <t>11:42</t>
         </is>
       </c>
       <c r="AD124" t="b">
@@ -14625,16 +14659,16 @@
       <c r="AY124" t="inlineStr"/>
       <c r="AZ124" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136689318</t>
+          <t>https://artportalen.se/Sighting/136689325</t>
         </is>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="n">
-        <v>136689331</v>
+        <v>126483693</v>
       </c>
       <c r="B125" t="n">
-        <v>98207</v>
+        <v>99035</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -14642,21 +14676,21 @@
         </is>
       </c>
       <c r="E125" t="n">
-        <v>221945</v>
+        <v>219790</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H125" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I125" t="inlineStr"/>
@@ -14666,13 +14700,13 @@
         </is>
       </c>
       <c r="Q125" t="n">
-        <v>464688</v>
+        <v>464741</v>
       </c>
       <c r="R125" t="n">
         <v>6784664</v>
       </c>
       <c r="S125" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T125" t="inlineStr">
         <is>
@@ -14696,22 +14730,22 @@
       </c>
       <c r="Y125" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2025-07-07</t>
         </is>
       </c>
       <c r="Z125" t="inlineStr">
         <is>
-          <t>11:56</t>
+          <t>09:56</t>
         </is>
       </c>
       <c r="AA125" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2025-07-07</t>
         </is>
       </c>
       <c r="AB125" t="inlineStr">
         <is>
-          <t>11:56</t>
+          <t>09:56</t>
         </is>
       </c>
       <c r="AD125" t="b">
@@ -14726,27 +14760,27 @@
       <c r="AT125" t="inlineStr"/>
       <c r="AW125" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX125" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY125" t="inlineStr"/>
       <c r="AZ125" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136689331</t>
+          <t>https://artportalen.se/Sighting/126483693</t>
         </is>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="n">
-        <v>136689342</v>
+        <v>136689348</v>
       </c>
       <c r="B126" t="n">
-        <v>98207</v>
+        <v>108371</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -14754,21 +14788,21 @@
         </is>
       </c>
       <c r="E126" t="n">
-        <v>221945</v>
+        <v>220083</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Brudborste</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Cirsium heterophyllum</t>
         </is>
       </c>
       <c r="H126" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Hill</t>
         </is>
       </c>
       <c r="I126" t="inlineStr"/>
@@ -14778,13 +14812,13 @@
         </is>
       </c>
       <c r="Q126" t="n">
-        <v>464685</v>
+        <v>464746</v>
       </c>
       <c r="R126" t="n">
-        <v>6784727</v>
+        <v>6784686</v>
       </c>
       <c r="S126" t="n">
-        <v>5</v>
+        <v>62</v>
       </c>
       <c r="T126" t="inlineStr">
         <is>
@@ -14813,7 +14847,7 @@
       </c>
       <c r="Z126" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>12:36</t>
         </is>
       </c>
       <c r="AA126" t="inlineStr">
@@ -14823,7 +14857,7 @@
       </c>
       <c r="AB126" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>12:36</t>
         </is>
       </c>
       <c r="AD126" t="b">
@@ -14843,22 +14877,22 @@
       </c>
       <c r="AX126" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer</t>
+          <t>Bengt Oldhammer, Birgitta Kvist, Håkan Thenander, Peter Turander</t>
         </is>
       </c>
       <c r="AY126" t="inlineStr"/>
       <c r="AZ126" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136689342</t>
+          <t>https://artportalen.se/Sighting/136689348</t>
         </is>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="n">
-        <v>126482525</v>
+        <v>136689336</v>
       </c>
       <c r="B127" t="n">
-        <v>104628</v>
+        <v>108441</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -14866,37 +14900,37 @@
         </is>
       </c>
       <c r="E127" t="n">
-        <v>222412</v>
+        <v>220102</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Tibast</t>
+          <t>Kärrfibbla</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>Daphne mezereum</t>
+          <t>Crepis paludosa</t>
         </is>
       </c>
       <c r="H127" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Moench</t>
         </is>
       </c>
       <c r="I127" t="inlineStr"/>
       <c r="P127" t="inlineStr">
         <is>
-          <t>Västersvedbäcken, Kölbron, Dlr</t>
+          <t>Kölbron, Dlr</t>
         </is>
       </c>
       <c r="Q127" t="n">
-        <v>464743</v>
+        <v>464683</v>
       </c>
       <c r="R127" t="n">
-        <v>6784670</v>
+        <v>6784681</v>
       </c>
       <c r="S127" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T127" t="inlineStr">
         <is>
@@ -14920,22 +14954,22 @@
       </c>
       <c r="Y127" t="inlineStr">
         <is>
-          <t>2025-07-07</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="Z127" t="inlineStr">
         <is>
-          <t>09:53</t>
+          <t>12:04</t>
         </is>
       </c>
       <c r="AA127" t="inlineStr">
         <is>
-          <t>2025-07-07</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="AB127" t="inlineStr">
         <is>
-          <t>09:53</t>
+          <t>12:04</t>
         </is>
       </c>
       <c r="AD127" t="b">
@@ -14955,22 +14989,22 @@
       </c>
       <c r="AX127" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer, Birgitta Kvist, Håkan Thenander, Peter Turander</t>
+          <t>Bengt Oldhammer</t>
         </is>
       </c>
       <c r="AY127" t="inlineStr"/>
       <c r="AZ127" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/126482525</t>
+          <t>https://artportalen.se/Sighting/136689336</t>
         </is>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="n">
-        <v>127627149</v>
+        <v>127020539</v>
       </c>
       <c r="B128" t="n">
-        <v>104628</v>
+        <v>97989</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -14978,16 +15012,16 @@
         </is>
       </c>
       <c r="E128" t="n">
-        <v>222412</v>
+        <v>221941</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>Tibast</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>Daphne mezereum</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H128" t="inlineStr">
@@ -14995,7 +15029,11 @@
           <t>L.</t>
         </is>
       </c>
-      <c r="I128" t="inlineStr"/>
+      <c r="I128" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="J128" t="inlineStr"/>
       <c r="K128" t="inlineStr"/>
       <c r="L128" t="inlineStr"/>
@@ -15006,13 +15044,13 @@
         </is>
       </c>
       <c r="Q128" t="n">
-        <v>464860</v>
+        <v>464774</v>
       </c>
       <c r="R128" t="n">
-        <v>6784675</v>
+        <v>6784776</v>
       </c>
       <c r="S128" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T128" t="inlineStr">
         <is>
@@ -15036,12 +15074,17 @@
       </c>
       <c r="Y128" t="inlineStr">
         <is>
-          <t>2025-08-15</t>
+          <t>2025-07-07</t>
         </is>
       </c>
       <c r="AA128" t="inlineStr">
         <is>
-          <t>2025-08-15</t>
+          <t>2025-07-07</t>
+        </is>
+      </c>
+      <c r="AC128" t="inlineStr">
+        <is>
+          <t>Rikligt till sparsamt i området</t>
         </is>
       </c>
       <c r="AD128" t="b">
@@ -15057,27 +15100,27 @@
       <c r="AT128" t="inlineStr"/>
       <c r="AW128" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX128" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY128" t="inlineStr"/>
       <c r="AZ128" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/127627149</t>
+          <t>https://artportalen.se/Sighting/127020539</t>
         </is>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="n">
-        <v>136689346</v>
+        <v>127020521</v>
       </c>
       <c r="B129" t="n">
-        <v>104868</v>
+        <v>97983</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
@@ -15085,16 +15128,16 @@
         </is>
       </c>
       <c r="E129" t="n">
-        <v>222412</v>
+        <v>221945</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>Tibast</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>Daphne mezereum</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H129" t="inlineStr">
@@ -15102,24 +15145,24 @@
           <t>L.</t>
         </is>
       </c>
-      <c r="I129" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
+      <c r="I129" t="inlineStr"/>
+      <c r="J129" t="inlineStr"/>
+      <c r="K129" t="inlineStr"/>
+      <c r="L129" t="inlineStr"/>
+      <c r="N129" t="inlineStr"/>
       <c r="P129" t="inlineStr">
         <is>
           <t>Kölbron, Dlr</t>
         </is>
       </c>
       <c r="Q129" t="n">
-        <v>464741</v>
+        <v>464774</v>
       </c>
       <c r="R129" t="n">
-        <v>6784699</v>
+        <v>6784776</v>
       </c>
       <c r="S129" t="n">
-        <v>5</v>
+        <v>50</v>
       </c>
       <c r="T129" t="inlineStr">
         <is>
@@ -15143,22 +15186,12 @@
       </c>
       <c r="Y129" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
-        </is>
-      </c>
-      <c r="Z129" t="inlineStr">
-        <is>
-          <t>12:31</t>
+          <t>2025-07-07</t>
         </is>
       </c>
       <c r="AA129" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
-        </is>
-      </c>
-      <c r="AB129" t="inlineStr">
-        <is>
-          <t>12:31</t>
+          <t>2025-07-07</t>
         </is>
       </c>
       <c r="AD129" t="b">
@@ -15167,33 +15200,34 @@
       <c r="AE129" t="b">
         <v>0</v>
       </c>
+      <c r="AF129" t="inlineStr"/>
       <c r="AG129" t="b">
         <v>0</v>
       </c>
       <c r="AT129" t="inlineStr"/>
       <c r="AW129" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX129" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer, Birgitta Kvist, Håkan Thenander, Peter Turander</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY129" t="inlineStr"/>
       <c r="AZ129" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136689346</t>
+          <t>https://artportalen.se/Sighting/127020521</t>
         </is>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="n">
-        <v>136689350</v>
+        <v>136689318</v>
       </c>
       <c r="B130" t="n">
-        <v>104868</v>
+        <v>98208</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
@@ -15201,16 +15235,16 @@
         </is>
       </c>
       <c r="E130" t="n">
-        <v>222412</v>
+        <v>221945</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>Tibast</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>Daphne mezereum</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H130" t="inlineStr">
@@ -15225,10 +15259,10 @@
         </is>
       </c>
       <c r="Q130" t="n">
-        <v>464776</v>
+        <v>464849</v>
       </c>
       <c r="R130" t="n">
-        <v>6784700</v>
+        <v>6784669</v>
       </c>
       <c r="S130" t="n">
         <v>5</v>
@@ -15260,7 +15294,7 @@
       </c>
       <c r="Z130" t="inlineStr">
         <is>
-          <t>12:39</t>
+          <t>10:57</t>
         </is>
       </c>
       <c r="AA130" t="inlineStr">
@@ -15270,7 +15304,7 @@
       </c>
       <c r="AB130" t="inlineStr">
         <is>
-          <t>12:39</t>
+          <t>10:57</t>
         </is>
       </c>
       <c r="AD130" t="b">
@@ -15290,22 +15324,22 @@
       </c>
       <c r="AX130" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer, Birgitta Kvist, Håkan Thenander, Peter Turander</t>
+          <t>Bengt Oldhammer</t>
         </is>
       </c>
       <c r="AY130" t="inlineStr"/>
       <c r="AZ130" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136689350</t>
+          <t>https://artportalen.se/Sighting/136689318</t>
         </is>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="n">
-        <v>136689358</v>
+        <v>136689331</v>
       </c>
       <c r="B131" t="n">
-        <v>104868</v>
+        <v>98208</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
@@ -15313,16 +15347,16 @@
         </is>
       </c>
       <c r="E131" t="n">
-        <v>222412</v>
+        <v>221945</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>Tibast</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>Daphne mezereum</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H131" t="inlineStr">
@@ -15337,10 +15371,10 @@
         </is>
       </c>
       <c r="Q131" t="n">
-        <v>464826</v>
+        <v>464688</v>
       </c>
       <c r="R131" t="n">
-        <v>6784683</v>
+        <v>6784664</v>
       </c>
       <c r="S131" t="n">
         <v>5</v>
@@ -15372,7 +15406,7 @@
       </c>
       <c r="Z131" t="inlineStr">
         <is>
-          <t>12:53</t>
+          <t>11:56</t>
         </is>
       </c>
       <c r="AA131" t="inlineStr">
@@ -15382,7 +15416,7 @@
       </c>
       <c r="AB131" t="inlineStr">
         <is>
-          <t>12:53</t>
+          <t>11:56</t>
         </is>
       </c>
       <c r="AD131" t="b">
@@ -15402,22 +15436,22 @@
       </c>
       <c r="AX131" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer, Birgitta Kvist, Håkan Thenander, Peter Turander</t>
+          <t>Bengt Oldhammer</t>
         </is>
       </c>
       <c r="AY131" t="inlineStr"/>
       <c r="AZ131" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136689358</t>
+          <t>https://artportalen.se/Sighting/136689331</t>
         </is>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="n">
-        <v>136689352</v>
+        <v>136689342</v>
       </c>
       <c r="B132" t="n">
-        <v>99622</v>
+        <v>98208</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
@@ -15425,16 +15459,16 @@
         </is>
       </c>
       <c r="E132" t="n">
-        <v>222812</v>
+        <v>221945</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>Liljekonvalj</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>Convallaria majalis</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H132" t="inlineStr">
@@ -15449,13 +15483,13 @@
         </is>
       </c>
       <c r="Q132" t="n">
-        <v>464817</v>
+        <v>464685</v>
       </c>
       <c r="R132" t="n">
-        <v>6784696</v>
+        <v>6784727</v>
       </c>
       <c r="S132" t="n">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="T132" t="inlineStr">
         <is>
@@ -15484,7 +15518,7 @@
       </c>
       <c r="Z132" t="inlineStr">
         <is>
-          <t>12:45</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="AA132" t="inlineStr">
@@ -15494,7 +15528,7 @@
       </c>
       <c r="AB132" t="inlineStr">
         <is>
-          <t>12:45</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="AD132" t="b">
@@ -15514,22 +15548,22 @@
       </c>
       <c r="AX132" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer, Birgitta Kvist, Håkan Thenander, Peter Turander</t>
+          <t>Bengt Oldhammer</t>
         </is>
       </c>
       <c r="AY132" t="inlineStr"/>
       <c r="AZ132" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136689352</t>
+          <t>https://artportalen.se/Sighting/136689342</t>
         </is>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="n">
-        <v>136689353</v>
+        <v>126482525</v>
       </c>
       <c r="B133" t="n">
-        <v>99151</v>
+        <v>104628</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
@@ -15537,16 +15571,16 @@
         </is>
       </c>
       <c r="E133" t="n">
-        <v>223049</v>
+        <v>222412</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>Ormbär</t>
+          <t>Tibast</t>
         </is>
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>Paris quadrifolia</t>
+          <t>Daphne mezereum</t>
         </is>
       </c>
       <c r="H133" t="inlineStr">
@@ -15557,17 +15591,17 @@
       <c r="I133" t="inlineStr"/>
       <c r="P133" t="inlineStr">
         <is>
-          <t>Kölbron, Dlr</t>
+          <t>Västersvedbäcken, Kölbron, Dlr</t>
         </is>
       </c>
       <c r="Q133" t="n">
-        <v>464816</v>
+        <v>464743</v>
       </c>
       <c r="R133" t="n">
-        <v>6784708</v>
+        <v>6784670</v>
       </c>
       <c r="S133" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T133" t="inlineStr">
         <is>
@@ -15591,22 +15625,22 @@
       </c>
       <c r="Y133" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2025-07-07</t>
         </is>
       </c>
       <c r="Z133" t="inlineStr">
         <is>
-          <t>12:48</t>
+          <t>09:53</t>
         </is>
       </c>
       <c r="AA133" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2025-07-07</t>
         </is>
       </c>
       <c r="AB133" t="inlineStr">
         <is>
-          <t>12:48</t>
+          <t>09:53</t>
         </is>
       </c>
       <c r="AD133" t="b">
@@ -15632,16 +15666,16 @@
       <c r="AY133" t="inlineStr"/>
       <c r="AZ133" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136689353</t>
+          <t>https://artportalen.se/Sighting/126482525</t>
         </is>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="n">
-        <v>126483802</v>
+        <v>127627149</v>
       </c>
       <c r="B134" t="n">
-        <v>97985</v>
+        <v>104628</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
@@ -15649,30 +15683,38 @@
         </is>
       </c>
       <c r="E134" t="n">
-        <v>224363</v>
+        <v>222412</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>Vanlig revlummer</t>
+          <t>Tibast</t>
         </is>
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum subsp. annotinum</t>
-        </is>
-      </c>
-      <c r="H134" t="inlineStr"/>
+          <t>Daphne mezereum</t>
+        </is>
+      </c>
+      <c r="H134" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
       <c r="I134" t="inlineStr"/>
+      <c r="J134" t="inlineStr"/>
+      <c r="K134" t="inlineStr"/>
+      <c r="L134" t="inlineStr"/>
+      <c r="N134" t="inlineStr"/>
       <c r="P134" t="inlineStr">
         <is>
-          <t>Kölbron, Kölbron, Dlr</t>
+          <t>Kölbron, Dlr</t>
         </is>
       </c>
       <c r="Q134" t="n">
-        <v>464766</v>
+        <v>464860</v>
       </c>
       <c r="R134" t="n">
-        <v>6784682</v>
+        <v>6784675</v>
       </c>
       <c r="S134" t="n">
         <v>10</v>
@@ -15699,22 +15741,12 @@
       </c>
       <c r="Y134" t="inlineStr">
         <is>
-          <t>2025-07-07</t>
-        </is>
-      </c>
-      <c r="Z134" t="inlineStr">
-        <is>
-          <t>10:01</t>
+          <t>2025-08-15</t>
         </is>
       </c>
       <c r="AA134" t="inlineStr">
         <is>
-          <t>2025-07-07</t>
-        </is>
-      </c>
-      <c r="AB134" t="inlineStr">
-        <is>
-          <t>10:01</t>
+          <t>2025-08-15</t>
         </is>
       </c>
       <c r="AD134" t="b">
@@ -15723,71 +15755,76 @@
       <c r="AE134" t="b">
         <v>0</v>
       </c>
+      <c r="AF134" t="inlineStr"/>
       <c r="AG134" t="b">
         <v>0</v>
       </c>
       <c r="AT134" t="inlineStr"/>
       <c r="AW134" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX134" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer, Birgitta Kvist, Håkan Thenander, Peter Turander</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY134" t="inlineStr"/>
       <c r="AZ134" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/126483802</t>
+          <t>https://artportalen.se/Sighting/127627149</t>
         </is>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="n">
-        <v>126481132</v>
+        <v>136689346</v>
       </c>
       <c r="B135" t="n">
-        <v>79085</v>
+        <v>104869</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E135" t="n">
-        <v>228912</v>
+        <v>222412</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Tibast</t>
         </is>
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Daphne mezereum</t>
         </is>
       </c>
       <c r="H135" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
-        </is>
-      </c>
-      <c r="I135" t="inlineStr"/>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I135" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
       <c r="P135" t="inlineStr">
         <is>
-          <t>Kölbron, Kölbron, Dlr</t>
+          <t>Kölbron, Dlr</t>
         </is>
       </c>
       <c r="Q135" t="n">
-        <v>464743</v>
+        <v>464741</v>
       </c>
       <c r="R135" t="n">
-        <v>6784623</v>
+        <v>6784699</v>
       </c>
       <c r="S135" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T135" t="inlineStr">
         <is>
@@ -15811,22 +15848,22 @@
       </c>
       <c r="Y135" t="inlineStr">
         <is>
-          <t>2025-07-07</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="Z135" t="inlineStr">
         <is>
-          <t>09:31</t>
+          <t>12:31</t>
         </is>
       </c>
       <c r="AA135" t="inlineStr">
         <is>
-          <t>2025-07-07</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="AB135" t="inlineStr">
         <is>
-          <t>09:31</t>
+          <t>12:31</t>
         </is>
       </c>
       <c r="AD135" t="b">
@@ -15852,38 +15889,38 @@
       <c r="AY135" t="inlineStr"/>
       <c r="AZ135" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/126481132</t>
+          <t>https://artportalen.se/Sighting/136689346</t>
         </is>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="n">
-        <v>126481487</v>
+        <v>136689350</v>
       </c>
       <c r="B136" t="n">
-        <v>79917</v>
+        <v>104869</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E136" t="n">
-        <v>229821</v>
+        <v>222412</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Tibast</t>
         </is>
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Daphne mezereum</t>
         </is>
       </c>
       <c r="H136" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I136" t="inlineStr"/>
@@ -15893,13 +15930,13 @@
         </is>
       </c>
       <c r="Q136" t="n">
-        <v>464766</v>
+        <v>464776</v>
       </c>
       <c r="R136" t="n">
-        <v>6784648</v>
+        <v>6784700</v>
       </c>
       <c r="S136" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T136" t="inlineStr">
         <is>
@@ -15923,22 +15960,22 @@
       </c>
       <c r="Y136" t="inlineStr">
         <is>
-          <t>2025-07-07</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="Z136" t="inlineStr">
         <is>
-          <t>09:28</t>
+          <t>12:39</t>
         </is>
       </c>
       <c r="AA136" t="inlineStr">
         <is>
-          <t>2025-07-07</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="AB136" t="inlineStr">
         <is>
-          <t>09:28</t>
+          <t>12:39</t>
         </is>
       </c>
       <c r="AD136" t="b">
@@ -15953,49 +15990,49 @@
       <c r="AT136" t="inlineStr"/>
       <c r="AW136" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bengt Oldhammer</t>
         </is>
       </c>
       <c r="AX136" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bengt Oldhammer, Birgitta Kvist, Håkan Thenander, Peter Turander</t>
         </is>
       </c>
       <c r="AY136" t="inlineStr"/>
       <c r="AZ136" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/126481487</t>
+          <t>https://artportalen.se/Sighting/136689350</t>
         </is>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="n">
-        <v>127530350</v>
+        <v>136689358</v>
       </c>
       <c r="B137" t="n">
-        <v>79328</v>
+        <v>104869</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E137" t="n">
-        <v>230405</v>
+        <v>222412</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>Garnlav (ssp. sarmentosa)</t>
+          <t>Tibast</t>
         </is>
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa subsp. sarmentosa</t>
+          <t>Daphne mezereum</t>
         </is>
       </c>
       <c r="H137" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I137" t="inlineStr"/>
@@ -16005,13 +16042,13 @@
         </is>
       </c>
       <c r="Q137" t="n">
-        <v>464867</v>
+        <v>464826</v>
       </c>
       <c r="R137" t="n">
-        <v>6784698</v>
+        <v>6784683</v>
       </c>
       <c r="S137" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T137" t="inlineStr">
         <is>
@@ -16035,27 +16072,22 @@
       </c>
       <c r="Y137" t="inlineStr">
         <is>
-          <t>2025-08-15</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="Z137" t="inlineStr">
         <is>
-          <t>09:17</t>
+          <t>12:53</t>
         </is>
       </c>
       <c r="AA137" t="inlineStr">
         <is>
-          <t>2025-08-15</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="AB137" t="inlineStr">
         <is>
-          <t>09:17</t>
-        </is>
-      </c>
-      <c r="AC137" t="inlineStr">
-        <is>
-          <t>Bilder på gran med garn</t>
+          <t>12:53</t>
         </is>
       </c>
       <c r="AD137" t="b">
@@ -16070,65 +16102,69 @@
       <c r="AT137" t="inlineStr"/>
       <c r="AW137" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bengt Oldhammer</t>
         </is>
       </c>
       <c r="AX137" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bengt Oldhammer, Birgitta Kvist, Håkan Thenander, Peter Turander</t>
         </is>
       </c>
       <c r="AY137" t="inlineStr"/>
       <c r="AZ137" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/127530350</t>
+          <t>https://artportalen.se/Sighting/136689358</t>
         </is>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="n">
-        <v>126485068</v>
+        <v>136699224</v>
       </c>
       <c r="B138" t="n">
-        <v>79350</v>
+        <v>104869</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E138" t="n">
-        <v>260591</v>
+        <v>222412</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>Talltagel</t>
+          <t>Tibast</t>
         </is>
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>Bryoria fremontii</t>
+          <t>Daphne mezereum</t>
         </is>
       </c>
       <c r="H138" t="inlineStr">
         <is>
-          <t>(Tuck.) Brodo &amp; D.Hawksw.</t>
-        </is>
-      </c>
-      <c r="I138" t="inlineStr"/>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I138" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
       <c r="P138" t="inlineStr">
         <is>
-          <t>Kölbron, Kölbron, Dlr</t>
+          <t>Kölbron, Dlr</t>
         </is>
       </c>
       <c r="Q138" t="n">
-        <v>464772</v>
+        <v>464770</v>
       </c>
       <c r="R138" t="n">
-        <v>6784708</v>
+        <v>6784688</v>
       </c>
       <c r="S138" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T138" t="inlineStr">
         <is>
@@ -16152,22 +16188,22 @@
       </c>
       <c r="Y138" t="inlineStr">
         <is>
-          <t>2025-07-07</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="Z138" t="inlineStr">
         <is>
-          <t>10:30</t>
+          <t>12:45</t>
         </is>
       </c>
       <c r="AA138" t="inlineStr">
         <is>
-          <t>2025-07-07</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="AB138" t="inlineStr">
         <is>
-          <t>10:30</t>
+          <t>12:45</t>
         </is>
       </c>
       <c r="AD138" t="b">
@@ -16182,68 +16218,65 @@
       <c r="AT138" t="inlineStr"/>
       <c r="AW138" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX138" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer, Birgitta Kvist, Håkan Thenander, Peter Turander</t>
+          <t>Håkan Thenander, Bengt Oldhammer, Peter Turander, Birgitta Kvist</t>
         </is>
       </c>
       <c r="AY138" t="inlineStr"/>
       <c r="AZ138" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/126485068</t>
+          <t>https://artportalen.se/Sighting/136699224</t>
         </is>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="n">
-        <v>126492727</v>
+        <v>136699225</v>
       </c>
       <c r="B139" t="n">
-        <v>79350</v>
+        <v>104869</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E139" t="n">
-        <v>260591</v>
+        <v>222412</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>Talltagel</t>
+          <t>Tibast</t>
         </is>
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>Bryoria fremontii</t>
+          <t>Daphne mezereum</t>
         </is>
       </c>
       <c r="H139" t="inlineStr">
         <is>
-          <t>(Tuck.) Brodo &amp; D.Hawksw.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I139" t="inlineStr"/>
-      <c r="J139" t="inlineStr"/>
-      <c r="K139" t="inlineStr"/>
-      <c r="N139" t="inlineStr"/>
       <c r="P139" t="inlineStr">
         <is>
           <t>Kölbron, Dlr</t>
         </is>
       </c>
       <c r="Q139" t="n">
-        <v>464813</v>
+        <v>464809</v>
       </c>
       <c r="R139" t="n">
-        <v>6784739</v>
+        <v>6784685</v>
       </c>
       <c r="S139" t="n">
-        <v>25</v>
+        <v>8</v>
       </c>
       <c r="T139" t="inlineStr">
         <is>
@@ -16267,17 +16300,22 @@
       </c>
       <c r="Y139" t="inlineStr">
         <is>
-          <t>2025-07-07</t>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="Z139" t="inlineStr">
+        <is>
+          <t>12:54</t>
         </is>
       </c>
       <c r="AA139" t="inlineStr">
         <is>
-          <t>2025-07-07</t>
-        </is>
-      </c>
-      <c r="AC139" t="inlineStr">
-        <is>
-          <t>På gran</t>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="AB139" t="inlineStr">
+        <is>
+          <t>12:54</t>
         </is>
       </c>
       <c r="AD139" t="b">
@@ -16286,23 +16324,918 @@
       <c r="AE139" t="b">
         <v>0</v>
       </c>
-      <c r="AF139" t="inlineStr"/>
       <c r="AG139" t="b">
         <v>0</v>
       </c>
       <c r="AT139" t="inlineStr"/>
       <c r="AW139" t="inlineStr">
         <is>
-          <t>Peter Turander</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX139" t="inlineStr">
         <is>
-          <t>Peter Turander</t>
+          <t>Håkan Thenander, Bengt Oldhammer, Peter Turander, Birgitta Kvist</t>
         </is>
       </c>
       <c r="AY139" t="inlineStr"/>
       <c r="AZ139" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136699225</t>
+        </is>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" t="n">
+        <v>136689352</v>
+      </c>
+      <c r="B140" t="n">
+        <v>99623</v>
+      </c>
+      <c r="D140" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E140" t="n">
+        <v>222812</v>
+      </c>
+      <c r="F140" t="inlineStr">
+        <is>
+          <t>Liljekonvalj</t>
+        </is>
+      </c>
+      <c r="G140" t="inlineStr">
+        <is>
+          <t>Convallaria majalis</t>
+        </is>
+      </c>
+      <c r="H140" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I140" t="inlineStr"/>
+      <c r="P140" t="inlineStr">
+        <is>
+          <t>Kölbron, Dlr</t>
+        </is>
+      </c>
+      <c r="Q140" t="n">
+        <v>464817</v>
+      </c>
+      <c r="R140" t="n">
+        <v>6784696</v>
+      </c>
+      <c r="S140" t="n">
+        <v>11</v>
+      </c>
+      <c r="T140" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U140" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V140" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W140" t="inlineStr">
+        <is>
+          <t>Våmhus</t>
+        </is>
+      </c>
+      <c r="Y140" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="Z140" t="inlineStr">
+        <is>
+          <t>12:45</t>
+        </is>
+      </c>
+      <c r="AA140" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="AB140" t="inlineStr">
+        <is>
+          <t>12:45</t>
+        </is>
+      </c>
+      <c r="AD140" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE140" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG140" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT140" t="inlineStr"/>
+      <c r="AW140" t="inlineStr">
+        <is>
+          <t>Bengt Oldhammer</t>
+        </is>
+      </c>
+      <c r="AX140" t="inlineStr">
+        <is>
+          <t>Bengt Oldhammer, Birgitta Kvist, Håkan Thenander, Peter Turander</t>
+        </is>
+      </c>
+      <c r="AY140" t="inlineStr"/>
+      <c r="AZ140" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136689352</t>
+        </is>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" t="n">
+        <v>136689353</v>
+      </c>
+      <c r="B141" t="n">
+        <v>99152</v>
+      </c>
+      <c r="D141" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E141" t="n">
+        <v>223049</v>
+      </c>
+      <c r="F141" t="inlineStr">
+        <is>
+          <t>Ormbär</t>
+        </is>
+      </c>
+      <c r="G141" t="inlineStr">
+        <is>
+          <t>Paris quadrifolia</t>
+        </is>
+      </c>
+      <c r="H141" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I141" t="inlineStr"/>
+      <c r="P141" t="inlineStr">
+        <is>
+          <t>Kölbron, Dlr</t>
+        </is>
+      </c>
+      <c r="Q141" t="n">
+        <v>464816</v>
+      </c>
+      <c r="R141" t="n">
+        <v>6784708</v>
+      </c>
+      <c r="S141" t="n">
+        <v>8</v>
+      </c>
+      <c r="T141" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U141" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V141" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W141" t="inlineStr">
+        <is>
+          <t>Våmhus</t>
+        </is>
+      </c>
+      <c r="Y141" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="Z141" t="inlineStr">
+        <is>
+          <t>12:48</t>
+        </is>
+      </c>
+      <c r="AA141" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="AB141" t="inlineStr">
+        <is>
+          <t>12:48</t>
+        </is>
+      </c>
+      <c r="AD141" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE141" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG141" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT141" t="inlineStr"/>
+      <c r="AW141" t="inlineStr">
+        <is>
+          <t>Bengt Oldhammer</t>
+        </is>
+      </c>
+      <c r="AX141" t="inlineStr">
+        <is>
+          <t>Bengt Oldhammer, Birgitta Kvist, Håkan Thenander, Peter Turander</t>
+        </is>
+      </c>
+      <c r="AY141" t="inlineStr"/>
+      <c r="AZ141" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136689353</t>
+        </is>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" t="n">
+        <v>126483802</v>
+      </c>
+      <c r="B142" t="n">
+        <v>97985</v>
+      </c>
+      <c r="D142" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E142" t="n">
+        <v>224363</v>
+      </c>
+      <c r="F142" t="inlineStr">
+        <is>
+          <t>Vanlig revlummer</t>
+        </is>
+      </c>
+      <c r="G142" t="inlineStr">
+        <is>
+          <t>Lycopodium annotinum subsp. annotinum</t>
+        </is>
+      </c>
+      <c r="H142" t="inlineStr"/>
+      <c r="I142" t="inlineStr"/>
+      <c r="P142" t="inlineStr">
+        <is>
+          <t>Kölbron, Kölbron, Dlr</t>
+        </is>
+      </c>
+      <c r="Q142" t="n">
+        <v>464766</v>
+      </c>
+      <c r="R142" t="n">
+        <v>6784682</v>
+      </c>
+      <c r="S142" t="n">
+        <v>10</v>
+      </c>
+      <c r="T142" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U142" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V142" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W142" t="inlineStr">
+        <is>
+          <t>Våmhus</t>
+        </is>
+      </c>
+      <c r="Y142" t="inlineStr">
+        <is>
+          <t>2025-07-07</t>
+        </is>
+      </c>
+      <c r="Z142" t="inlineStr">
+        <is>
+          <t>10:01</t>
+        </is>
+      </c>
+      <c r="AA142" t="inlineStr">
+        <is>
+          <t>2025-07-07</t>
+        </is>
+      </c>
+      <c r="AB142" t="inlineStr">
+        <is>
+          <t>10:01</t>
+        </is>
+      </c>
+      <c r="AD142" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE142" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG142" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT142" t="inlineStr"/>
+      <c r="AW142" t="inlineStr">
+        <is>
+          <t>Bengt Oldhammer</t>
+        </is>
+      </c>
+      <c r="AX142" t="inlineStr">
+        <is>
+          <t>Bengt Oldhammer, Birgitta Kvist, Håkan Thenander, Peter Turander</t>
+        </is>
+      </c>
+      <c r="AY142" t="inlineStr"/>
+      <c r="AZ142" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126483802</t>
+        </is>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" t="n">
+        <v>126481132</v>
+      </c>
+      <c r="B143" t="n">
+        <v>79085</v>
+      </c>
+      <c r="D143" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E143" t="n">
+        <v>228912</v>
+      </c>
+      <c r="F143" t="inlineStr">
+        <is>
+          <t>Mörk kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G143" t="inlineStr">
+        <is>
+          <t>Carbonicola myrmecina</t>
+        </is>
+      </c>
+      <c r="H143" t="inlineStr">
+        <is>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I143" t="inlineStr"/>
+      <c r="P143" t="inlineStr">
+        <is>
+          <t>Kölbron, Kölbron, Dlr</t>
+        </is>
+      </c>
+      <c r="Q143" t="n">
+        <v>464743</v>
+      </c>
+      <c r="R143" t="n">
+        <v>6784623</v>
+      </c>
+      <c r="S143" t="n">
+        <v>10</v>
+      </c>
+      <c r="T143" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U143" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V143" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W143" t="inlineStr">
+        <is>
+          <t>Våmhus</t>
+        </is>
+      </c>
+      <c r="Y143" t="inlineStr">
+        <is>
+          <t>2025-07-07</t>
+        </is>
+      </c>
+      <c r="Z143" t="inlineStr">
+        <is>
+          <t>09:31</t>
+        </is>
+      </c>
+      <c r="AA143" t="inlineStr">
+        <is>
+          <t>2025-07-07</t>
+        </is>
+      </c>
+      <c r="AB143" t="inlineStr">
+        <is>
+          <t>09:31</t>
+        </is>
+      </c>
+      <c r="AD143" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE143" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG143" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT143" t="inlineStr"/>
+      <c r="AW143" t="inlineStr">
+        <is>
+          <t>Bengt Oldhammer</t>
+        </is>
+      </c>
+      <c r="AX143" t="inlineStr">
+        <is>
+          <t>Bengt Oldhammer, Birgitta Kvist, Håkan Thenander, Peter Turander</t>
+        </is>
+      </c>
+      <c r="AY143" t="inlineStr"/>
+      <c r="AZ143" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126481132</t>
+        </is>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" t="n">
+        <v>126481487</v>
+      </c>
+      <c r="B144" t="n">
+        <v>79917</v>
+      </c>
+      <c r="D144" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E144" t="n">
+        <v>229821</v>
+      </c>
+      <c r="F144" t="inlineStr">
+        <is>
+          <t>Vedflamlav</t>
+        </is>
+      </c>
+      <c r="G144" t="inlineStr">
+        <is>
+          <t>Ramboldia elabens</t>
+        </is>
+      </c>
+      <c r="H144" t="inlineStr">
+        <is>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
+        </is>
+      </c>
+      <c r="I144" t="inlineStr"/>
+      <c r="P144" t="inlineStr">
+        <is>
+          <t>Kölbron, Dlr</t>
+        </is>
+      </c>
+      <c r="Q144" t="n">
+        <v>464766</v>
+      </c>
+      <c r="R144" t="n">
+        <v>6784648</v>
+      </c>
+      <c r="S144" t="n">
+        <v>10</v>
+      </c>
+      <c r="T144" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U144" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V144" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W144" t="inlineStr">
+        <is>
+          <t>Våmhus</t>
+        </is>
+      </c>
+      <c r="Y144" t="inlineStr">
+        <is>
+          <t>2025-07-07</t>
+        </is>
+      </c>
+      <c r="Z144" t="inlineStr">
+        <is>
+          <t>09:28</t>
+        </is>
+      </c>
+      <c r="AA144" t="inlineStr">
+        <is>
+          <t>2025-07-07</t>
+        </is>
+      </c>
+      <c r="AB144" t="inlineStr">
+        <is>
+          <t>09:28</t>
+        </is>
+      </c>
+      <c r="AD144" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE144" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG144" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT144" t="inlineStr"/>
+      <c r="AW144" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AX144" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AY144" t="inlineStr"/>
+      <c r="AZ144" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126481487</t>
+        </is>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" t="n">
+        <v>127530350</v>
+      </c>
+      <c r="B145" t="n">
+        <v>79328</v>
+      </c>
+      <c r="D145" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E145" t="n">
+        <v>230405</v>
+      </c>
+      <c r="F145" t="inlineStr">
+        <is>
+          <t>Garnlav (ssp. sarmentosa)</t>
+        </is>
+      </c>
+      <c r="G145" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa subsp. sarmentosa</t>
+        </is>
+      </c>
+      <c r="H145" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I145" t="inlineStr"/>
+      <c r="P145" t="inlineStr">
+        <is>
+          <t>Kölbron, Dlr</t>
+        </is>
+      </c>
+      <c r="Q145" t="n">
+        <v>464867</v>
+      </c>
+      <c r="R145" t="n">
+        <v>6784698</v>
+      </c>
+      <c r="S145" t="n">
+        <v>10</v>
+      </c>
+      <c r="T145" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U145" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V145" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W145" t="inlineStr">
+        <is>
+          <t>Våmhus</t>
+        </is>
+      </c>
+      <c r="Y145" t="inlineStr">
+        <is>
+          <t>2025-08-15</t>
+        </is>
+      </c>
+      <c r="Z145" t="inlineStr">
+        <is>
+          <t>09:17</t>
+        </is>
+      </c>
+      <c r="AA145" t="inlineStr">
+        <is>
+          <t>2025-08-15</t>
+        </is>
+      </c>
+      <c r="AB145" t="inlineStr">
+        <is>
+          <t>09:17</t>
+        </is>
+      </c>
+      <c r="AC145" t="inlineStr">
+        <is>
+          <t>Bilder på gran med garn</t>
+        </is>
+      </c>
+      <c r="AD145" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE145" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG145" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT145" t="inlineStr"/>
+      <c r="AW145" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AX145" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AY145" t="inlineStr"/>
+      <c r="AZ145" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127530350</t>
+        </is>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" t="n">
+        <v>126485068</v>
+      </c>
+      <c r="B146" t="n">
+        <v>79350</v>
+      </c>
+      <c r="D146" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E146" t="n">
+        <v>260591</v>
+      </c>
+      <c r="F146" t="inlineStr">
+        <is>
+          <t>Talltagel</t>
+        </is>
+      </c>
+      <c r="G146" t="inlineStr">
+        <is>
+          <t>Bryoria fremontii</t>
+        </is>
+      </c>
+      <c r="H146" t="inlineStr">
+        <is>
+          <t>(Tuck.) Brodo &amp; D.Hawksw.</t>
+        </is>
+      </c>
+      <c r="I146" t="inlineStr"/>
+      <c r="P146" t="inlineStr">
+        <is>
+          <t>Kölbron, Kölbron, Dlr</t>
+        </is>
+      </c>
+      <c r="Q146" t="n">
+        <v>464772</v>
+      </c>
+      <c r="R146" t="n">
+        <v>6784708</v>
+      </c>
+      <c r="S146" t="n">
+        <v>10</v>
+      </c>
+      <c r="T146" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U146" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V146" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W146" t="inlineStr">
+        <is>
+          <t>Våmhus</t>
+        </is>
+      </c>
+      <c r="Y146" t="inlineStr">
+        <is>
+          <t>2025-07-07</t>
+        </is>
+      </c>
+      <c r="Z146" t="inlineStr">
+        <is>
+          <t>10:30</t>
+        </is>
+      </c>
+      <c r="AA146" t="inlineStr">
+        <is>
+          <t>2025-07-07</t>
+        </is>
+      </c>
+      <c r="AB146" t="inlineStr">
+        <is>
+          <t>10:30</t>
+        </is>
+      </c>
+      <c r="AD146" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE146" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG146" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT146" t="inlineStr"/>
+      <c r="AW146" t="inlineStr">
+        <is>
+          <t>Bengt Oldhammer</t>
+        </is>
+      </c>
+      <c r="AX146" t="inlineStr">
+        <is>
+          <t>Bengt Oldhammer, Birgitta Kvist, Håkan Thenander, Peter Turander</t>
+        </is>
+      </c>
+      <c r="AY146" t="inlineStr"/>
+      <c r="AZ146" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126485068</t>
+        </is>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" t="n">
+        <v>126492727</v>
+      </c>
+      <c r="B147" t="n">
+        <v>79350</v>
+      </c>
+      <c r="D147" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E147" t="n">
+        <v>260591</v>
+      </c>
+      <c r="F147" t="inlineStr">
+        <is>
+          <t>Talltagel</t>
+        </is>
+      </c>
+      <c r="G147" t="inlineStr">
+        <is>
+          <t>Bryoria fremontii</t>
+        </is>
+      </c>
+      <c r="H147" t="inlineStr">
+        <is>
+          <t>(Tuck.) Brodo &amp; D.Hawksw.</t>
+        </is>
+      </c>
+      <c r="I147" t="inlineStr"/>
+      <c r="J147" t="inlineStr"/>
+      <c r="K147" t="inlineStr"/>
+      <c r="N147" t="inlineStr"/>
+      <c r="P147" t="inlineStr">
+        <is>
+          <t>Kölbron, Dlr</t>
+        </is>
+      </c>
+      <c r="Q147" t="n">
+        <v>464813</v>
+      </c>
+      <c r="R147" t="n">
+        <v>6784739</v>
+      </c>
+      <c r="S147" t="n">
+        <v>25</v>
+      </c>
+      <c r="T147" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U147" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V147" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W147" t="inlineStr">
+        <is>
+          <t>Våmhus</t>
+        </is>
+      </c>
+      <c r="Y147" t="inlineStr">
+        <is>
+          <t>2025-07-07</t>
+        </is>
+      </c>
+      <c r="AA147" t="inlineStr">
+        <is>
+          <t>2025-07-07</t>
+        </is>
+      </c>
+      <c r="AC147" t="inlineStr">
+        <is>
+          <t>På gran</t>
+        </is>
+      </c>
+      <c r="AD147" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE147" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF147" t="inlineStr"/>
+      <c r="AG147" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT147" t="inlineStr"/>
+      <c r="AW147" t="inlineStr">
+        <is>
+          <t>Peter Turander</t>
+        </is>
+      </c>
+      <c r="AX147" t="inlineStr">
+        <is>
+          <t>Peter Turander</t>
+        </is>
+      </c>
+      <c r="AY147" t="inlineStr"/>
+      <c r="AZ147" t="inlineStr">
         <is>
           <t>https://artportalen.se/Sighting/126492727</t>
         </is>
@@ -16448,6 +17381,14 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ137" r:id="rId136"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ138" r:id="rId137"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ139" r:id="rId138"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ140" r:id="rId139"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ141" r:id="rId140"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ142" r:id="rId141"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ143" r:id="rId142"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ144" r:id="rId143"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ145" r:id="rId144"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ146" r:id="rId145"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ147" r:id="rId146"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 20531-2025 artfynd.xlsx
+++ b/artfynd/A 20531-2025 artfynd.xlsx
@@ -1457,7 +1457,7 @@
         <v>136687803</v>
       </c>
       <c r="B9" t="n">
-        <v>79506</v>
+        <v>79508</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1589,7 +1589,7 @@
         <v>136687805</v>
       </c>
       <c r="B10" t="n">
-        <v>79506</v>
+        <v>79508</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1721,7 +1721,7 @@
         <v>136687806</v>
       </c>
       <c r="B11" t="n">
-        <v>79506</v>
+        <v>79508</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1853,7 +1853,7 @@
         <v>136689322</v>
       </c>
       <c r="B12" t="n">
-        <v>79506</v>
+        <v>79508</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1965,7 +1965,7 @@
         <v>136689361</v>
       </c>
       <c r="B13" t="n">
-        <v>79506</v>
+        <v>79508</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2062,7 +2062,7 @@
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer, Birgitta Kvist, Håkan Thenander, Peter Turander</t>
+          <t>Bengt Oldhammer, Peter Turander, Håkan Thenander, Birgitta Kvist</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
@@ -2077,7 +2077,7 @@
         <v>136687804</v>
       </c>
       <c r="B14" t="n">
-        <v>83341</v>
+        <v>83343</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2204,7 +2204,7 @@
         <v>136689343</v>
       </c>
       <c r="B15" t="n">
-        <v>91882</v>
+        <v>91887</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2301,7 +2301,7 @@
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer, Birgitta Kvist, Håkan Thenander, Peter Turander</t>
+          <t>Bengt Oldhammer, Peter Turander, Håkan Thenander, Birgitta Kvist</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
@@ -2316,7 +2316,7 @@
         <v>136689338</v>
       </c>
       <c r="B16" t="n">
-        <v>93048</v>
+        <v>93053</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2428,7 +2428,7 @@
         <v>136689333</v>
       </c>
       <c r="B17" t="n">
-        <v>93076</v>
+        <v>93081</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2540,7 +2540,7 @@
         <v>136689344</v>
       </c>
       <c r="B18" t="n">
-        <v>93076</v>
+        <v>93081</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2637,7 +2637,7 @@
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer, Birgitta Kvist, Håkan Thenander, Peter Turander</t>
+          <t>Bengt Oldhammer, Peter Turander, Håkan Thenander, Birgitta Kvist</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
@@ -2652,7 +2652,7 @@
         <v>136689356</v>
       </c>
       <c r="B19" t="n">
-        <v>93076</v>
+        <v>93081</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2749,7 +2749,7 @@
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer, Birgitta Kvist, Håkan Thenander, Peter Turander</t>
+          <t>Bengt Oldhammer, Peter Turander, Håkan Thenander, Birgitta Kvist</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
@@ -2764,7 +2764,7 @@
         <v>136689357</v>
       </c>
       <c r="B20" t="n">
-        <v>93076</v>
+        <v>93081</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2865,7 +2865,7 @@
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer, Birgitta Kvist, Håkan Thenander, Peter Turander</t>
+          <t>Bengt Oldhammer, Peter Turander, Håkan Thenander, Birgitta Kvist</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
@@ -2880,7 +2880,7 @@
         <v>136689363</v>
       </c>
       <c r="B21" t="n">
-        <v>93076</v>
+        <v>93081</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2977,7 +2977,7 @@
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer, Birgitta Kvist, Håkan Thenander, Peter Turander</t>
+          <t>Bengt Oldhammer, Peter Turander, Håkan Thenander, Birgitta Kvist</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
@@ -2992,7 +2992,7 @@
         <v>136699216</v>
       </c>
       <c r="B22" t="n">
-        <v>93076</v>
+        <v>93081</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -9842,7 +9842,7 @@
         <v>136689324</v>
       </c>
       <c r="B83" t="n">
-        <v>79474</v>
+        <v>79476</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -9954,7 +9954,7 @@
         <v>136689329</v>
       </c>
       <c r="B84" t="n">
-        <v>79474</v>
+        <v>79476</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -10858,7 +10858,7 @@
         <v>136689345</v>
       </c>
       <c r="B92" t="n">
-        <v>83461</v>
+        <v>83463</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -10955,7 +10955,7 @@
       </c>
       <c r="AX92" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer, Birgitta Kvist, Håkan Thenander, Peter Turander</t>
+          <t>Bengt Oldhammer, Peter Turander, Håkan Thenander, Birgitta Kvist</t>
         </is>
       </c>
       <c r="AY92" t="inlineStr"/>
@@ -10970,7 +10970,7 @@
         <v>136699227</v>
       </c>
       <c r="B93" t="n">
-        <v>83461</v>
+        <v>83463</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -12227,7 +12227,7 @@
         <v>136699220</v>
       </c>
       <c r="B104" t="n">
-        <v>58006</v>
+        <v>58008</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -12344,7 +12344,7 @@
         <v>136699222</v>
       </c>
       <c r="B105" t="n">
-        <v>58006</v>
+        <v>58008</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -12461,7 +12461,7 @@
         <v>136699223</v>
       </c>
       <c r="B106" t="n">
-        <v>58006</v>
+        <v>58008</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -12578,7 +12578,7 @@
         <v>136699229</v>
       </c>
       <c r="B107" t="n">
-        <v>58006</v>
+        <v>58008</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -12704,7 +12704,7 @@
         <v>136689339</v>
       </c>
       <c r="B108" t="n">
-        <v>57193</v>
+        <v>57195</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -13172,7 +13172,7 @@
         <v>136689332</v>
       </c>
       <c r="B112" t="n">
-        <v>58167</v>
+        <v>58169</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -13284,7 +13284,7 @@
         <v>136689326</v>
       </c>
       <c r="B113" t="n">
-        <v>58627</v>
+        <v>58629</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -13401,7 +13401,7 @@
         <v>136689334</v>
       </c>
       <c r="B114" t="n">
-        <v>58665</v>
+        <v>58667</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -14780,7 +14780,7 @@
         <v>136689348</v>
       </c>
       <c r="B126" t="n">
-        <v>108371</v>
+        <v>108376</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -14877,7 +14877,7 @@
       </c>
       <c r="AX126" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer, Birgitta Kvist, Håkan Thenander, Peter Turander</t>
+          <t>Bengt Oldhammer, Peter Turander, Håkan Thenander, Birgitta Kvist</t>
         </is>
       </c>
       <c r="AY126" t="inlineStr"/>
@@ -14892,7 +14892,7 @@
         <v>136689336</v>
       </c>
       <c r="B127" t="n">
-        <v>108441</v>
+        <v>108446</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -15227,7 +15227,7 @@
         <v>136689318</v>
       </c>
       <c r="B130" t="n">
-        <v>98208</v>
+        <v>98213</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
@@ -15339,7 +15339,7 @@
         <v>136689331</v>
       </c>
       <c r="B131" t="n">
-        <v>98208</v>
+        <v>98213</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
@@ -15451,7 +15451,7 @@
         <v>136689342</v>
       </c>
       <c r="B132" t="n">
-        <v>98208</v>
+        <v>98213</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
@@ -15782,7 +15782,7 @@
         <v>136689346</v>
       </c>
       <c r="B135" t="n">
-        <v>104869</v>
+        <v>104874</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
@@ -15883,7 +15883,7 @@
       </c>
       <c r="AX135" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer, Birgitta Kvist, Håkan Thenander, Peter Turander</t>
+          <t>Bengt Oldhammer, Peter Turander, Håkan Thenander, Birgitta Kvist</t>
         </is>
       </c>
       <c r="AY135" t="inlineStr"/>
@@ -15898,7 +15898,7 @@
         <v>136689350</v>
       </c>
       <c r="B136" t="n">
-        <v>104869</v>
+        <v>104874</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
@@ -15995,7 +15995,7 @@
       </c>
       <c r="AX136" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer, Birgitta Kvist, Håkan Thenander, Peter Turander</t>
+          <t>Bengt Oldhammer, Peter Turander, Håkan Thenander, Birgitta Kvist</t>
         </is>
       </c>
       <c r="AY136" t="inlineStr"/>
@@ -16010,7 +16010,7 @@
         <v>136689358</v>
       </c>
       <c r="B137" t="n">
-        <v>104869</v>
+        <v>104874</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
@@ -16107,7 +16107,7 @@
       </c>
       <c r="AX137" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer, Birgitta Kvist, Håkan Thenander, Peter Turander</t>
+          <t>Bengt Oldhammer, Peter Turander, Håkan Thenander, Birgitta Kvist</t>
         </is>
       </c>
       <c r="AY137" t="inlineStr"/>
@@ -16122,7 +16122,7 @@
         <v>136699224</v>
       </c>
       <c r="B138" t="n">
-        <v>104869</v>
+        <v>104874</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
@@ -16238,7 +16238,7 @@
         <v>136699225</v>
       </c>
       <c r="B139" t="n">
-        <v>104869</v>
+        <v>104874</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
@@ -16350,7 +16350,7 @@
         <v>136689352</v>
       </c>
       <c r="B140" t="n">
-        <v>99623</v>
+        <v>99628</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
@@ -16447,7 +16447,7 @@
       </c>
       <c r="AX140" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer, Birgitta Kvist, Håkan Thenander, Peter Turander</t>
+          <t>Bengt Oldhammer, Peter Turander, Håkan Thenander, Birgitta Kvist</t>
         </is>
       </c>
       <c r="AY140" t="inlineStr"/>
@@ -16462,7 +16462,7 @@
         <v>136689353</v>
       </c>
       <c r="B141" t="n">
-        <v>99152</v>
+        <v>99157</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
@@ -16559,7 +16559,7 @@
       </c>
       <c r="AX141" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer, Birgitta Kvist, Håkan Thenander, Peter Turander</t>
+          <t>Bengt Oldhammer, Peter Turander, Håkan Thenander, Birgitta Kvist</t>
         </is>
       </c>
       <c r="AY141" t="inlineStr"/>

--- a/artfynd/A 20531-2025 artfynd.xlsx
+++ b/artfynd/A 20531-2025 artfynd.xlsx
@@ -2062,7 +2062,7 @@
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer, Peter Turander, Håkan Thenander, Birgitta Kvist</t>
+          <t>Bengt Oldhammer, Birgitta Kvist, Håkan Thenander, Peter Turander</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
@@ -2301,7 +2301,7 @@
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer, Peter Turander, Håkan Thenander, Birgitta Kvist</t>
+          <t>Bengt Oldhammer, Birgitta Kvist, Håkan Thenander, Peter Turander</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
@@ -2637,7 +2637,7 @@
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer, Peter Turander, Håkan Thenander, Birgitta Kvist</t>
+          <t>Bengt Oldhammer, Birgitta Kvist, Håkan Thenander, Peter Turander</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
@@ -2749,7 +2749,7 @@
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer, Peter Turander, Håkan Thenander, Birgitta Kvist</t>
+          <t>Bengt Oldhammer, Birgitta Kvist, Håkan Thenander, Peter Turander</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
@@ -2865,7 +2865,7 @@
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer, Peter Turander, Håkan Thenander, Birgitta Kvist</t>
+          <t>Bengt Oldhammer, Birgitta Kvist, Håkan Thenander, Peter Turander</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
@@ -2977,7 +2977,7 @@
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer, Peter Turander, Håkan Thenander, Birgitta Kvist</t>
+          <t>Bengt Oldhammer, Birgitta Kvist, Håkan Thenander, Peter Turander</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
@@ -10955,7 +10955,7 @@
       </c>
       <c r="AX92" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer, Peter Turander, Håkan Thenander, Birgitta Kvist</t>
+          <t>Bengt Oldhammer, Birgitta Kvist, Håkan Thenander, Peter Turander</t>
         </is>
       </c>
       <c r="AY92" t="inlineStr"/>
@@ -14877,7 +14877,7 @@
       </c>
       <c r="AX126" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer, Peter Turander, Håkan Thenander, Birgitta Kvist</t>
+          <t>Bengt Oldhammer, Birgitta Kvist, Håkan Thenander, Peter Turander</t>
         </is>
       </c>
       <c r="AY126" t="inlineStr"/>
@@ -15883,7 +15883,7 @@
       </c>
       <c r="AX135" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer, Peter Turander, Håkan Thenander, Birgitta Kvist</t>
+          <t>Bengt Oldhammer, Birgitta Kvist, Håkan Thenander, Peter Turander</t>
         </is>
       </c>
       <c r="AY135" t="inlineStr"/>
@@ -15995,7 +15995,7 @@
       </c>
       <c r="AX136" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer, Peter Turander, Håkan Thenander, Birgitta Kvist</t>
+          <t>Bengt Oldhammer, Birgitta Kvist, Håkan Thenander, Peter Turander</t>
         </is>
       </c>
       <c r="AY136" t="inlineStr"/>
@@ -16107,7 +16107,7 @@
       </c>
       <c r="AX137" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer, Peter Turander, Håkan Thenander, Birgitta Kvist</t>
+          <t>Bengt Oldhammer, Birgitta Kvist, Håkan Thenander, Peter Turander</t>
         </is>
       </c>
       <c r="AY137" t="inlineStr"/>
@@ -16447,7 +16447,7 @@
       </c>
       <c r="AX140" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer, Peter Turander, Håkan Thenander, Birgitta Kvist</t>
+          <t>Bengt Oldhammer, Birgitta Kvist, Håkan Thenander, Peter Turander</t>
         </is>
       </c>
       <c r="AY140" t="inlineStr"/>
@@ -16559,7 +16559,7 @@
       </c>
       <c r="AX141" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer, Peter Turander, Håkan Thenander, Birgitta Kvist</t>
+          <t>Bengt Oldhammer, Birgitta Kvist, Håkan Thenander, Peter Turander</t>
         </is>
       </c>
       <c r="AY141" t="inlineStr"/>

--- a/artfynd/A 20531-2025 artfynd.xlsx
+++ b/artfynd/A 20531-2025 artfynd.xlsx
@@ -2204,7 +2204,7 @@
         <v>136689343</v>
       </c>
       <c r="B15" t="n">
-        <v>91887</v>
+        <v>91889</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2316,7 +2316,7 @@
         <v>136689338</v>
       </c>
       <c r="B16" t="n">
-        <v>93053</v>
+        <v>93055</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2428,7 +2428,7 @@
         <v>136689333</v>
       </c>
       <c r="B17" t="n">
-        <v>93081</v>
+        <v>93083</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2540,7 +2540,7 @@
         <v>136689344</v>
       </c>
       <c r="B18" t="n">
-        <v>93081</v>
+        <v>93083</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2652,7 +2652,7 @@
         <v>136689356</v>
       </c>
       <c r="B19" t="n">
-        <v>93081</v>
+        <v>93083</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2764,7 +2764,7 @@
         <v>136689357</v>
       </c>
       <c r="B20" t="n">
-        <v>93081</v>
+        <v>93083</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2880,7 +2880,7 @@
         <v>136689363</v>
       </c>
       <c r="B21" t="n">
-        <v>93081</v>
+        <v>93083</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2992,7 +2992,7 @@
         <v>136699216</v>
       </c>
       <c r="B22" t="n">
-        <v>93081</v>
+        <v>93083</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -14780,7 +14780,7 @@
         <v>136689348</v>
       </c>
       <c r="B126" t="n">
-        <v>108376</v>
+        <v>108378</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -14892,7 +14892,7 @@
         <v>136689336</v>
       </c>
       <c r="B127" t="n">
-        <v>108446</v>
+        <v>108448</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -15227,7 +15227,7 @@
         <v>136689318</v>
       </c>
       <c r="B130" t="n">
-        <v>98213</v>
+        <v>98215</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
@@ -15339,7 +15339,7 @@
         <v>136689331</v>
       </c>
       <c r="B131" t="n">
-        <v>98213</v>
+        <v>98215</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
@@ -15451,7 +15451,7 @@
         <v>136689342</v>
       </c>
       <c r="B132" t="n">
-        <v>98213</v>
+        <v>98215</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
@@ -15782,7 +15782,7 @@
         <v>136689346</v>
       </c>
       <c r="B135" t="n">
-        <v>104874</v>
+        <v>104876</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
@@ -15898,7 +15898,7 @@
         <v>136689350</v>
       </c>
       <c r="B136" t="n">
-        <v>104874</v>
+        <v>104876</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
@@ -16010,7 +16010,7 @@
         <v>136689358</v>
       </c>
       <c r="B137" t="n">
-        <v>104874</v>
+        <v>104876</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
@@ -16122,7 +16122,7 @@
         <v>136699224</v>
       </c>
       <c r="B138" t="n">
-        <v>104874</v>
+        <v>104876</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
@@ -16238,7 +16238,7 @@
         <v>136699225</v>
       </c>
       <c r="B139" t="n">
-        <v>104874</v>
+        <v>104876</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
@@ -16350,7 +16350,7 @@
         <v>136689352</v>
       </c>
       <c r="B140" t="n">
-        <v>99628</v>
+        <v>99630</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
@@ -16462,7 +16462,7 @@
         <v>136689353</v>
       </c>
       <c r="B141" t="n">
-        <v>99157</v>
+        <v>99159</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>

--- a/artfynd/A 20531-2025 artfynd.xlsx
+++ b/artfynd/A 20531-2025 artfynd.xlsx
@@ -2062,7 +2062,7 @@
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer, Birgitta Kvist, Håkan Thenander, Peter Turander</t>
+          <t>Bengt Oldhammer, Peter Turander, Håkan Thenander, Birgitta Kvist</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
@@ -2301,7 +2301,7 @@
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer, Birgitta Kvist, Håkan Thenander, Peter Turander</t>
+          <t>Bengt Oldhammer, Peter Turander, Håkan Thenander, Birgitta Kvist</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
@@ -2637,7 +2637,7 @@
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer, Birgitta Kvist, Håkan Thenander, Peter Turander</t>
+          <t>Bengt Oldhammer, Peter Turander, Håkan Thenander, Birgitta Kvist</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
@@ -2749,7 +2749,7 @@
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer, Birgitta Kvist, Håkan Thenander, Peter Turander</t>
+          <t>Bengt Oldhammer, Peter Turander, Håkan Thenander, Birgitta Kvist</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
@@ -2865,7 +2865,7 @@
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer, Birgitta Kvist, Håkan Thenander, Peter Turander</t>
+          <t>Bengt Oldhammer, Peter Turander, Håkan Thenander, Birgitta Kvist</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
@@ -2977,7 +2977,7 @@
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer, Birgitta Kvist, Håkan Thenander, Peter Turander</t>
+          <t>Bengt Oldhammer, Peter Turander, Håkan Thenander, Birgitta Kvist</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
@@ -10955,7 +10955,7 @@
       </c>
       <c r="AX92" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer, Birgitta Kvist, Håkan Thenander, Peter Turander</t>
+          <t>Bengt Oldhammer, Peter Turander, Håkan Thenander, Birgitta Kvist</t>
         </is>
       </c>
       <c r="AY92" t="inlineStr"/>
@@ -14877,7 +14877,7 @@
       </c>
       <c r="AX126" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer, Birgitta Kvist, Håkan Thenander, Peter Turander</t>
+          <t>Bengt Oldhammer, Peter Turander, Håkan Thenander, Birgitta Kvist</t>
         </is>
       </c>
       <c r="AY126" t="inlineStr"/>
@@ -15883,7 +15883,7 @@
       </c>
       <c r="AX135" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer, Birgitta Kvist, Håkan Thenander, Peter Turander</t>
+          <t>Bengt Oldhammer, Peter Turander, Håkan Thenander, Birgitta Kvist</t>
         </is>
       </c>
       <c r="AY135" t="inlineStr"/>
@@ -15995,7 +15995,7 @@
       </c>
       <c r="AX136" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer, Birgitta Kvist, Håkan Thenander, Peter Turander</t>
+          <t>Bengt Oldhammer, Peter Turander, Håkan Thenander, Birgitta Kvist</t>
         </is>
       </c>
       <c r="AY136" t="inlineStr"/>
@@ -16107,7 +16107,7 @@
       </c>
       <c r="AX137" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer, Birgitta Kvist, Håkan Thenander, Peter Turander</t>
+          <t>Bengt Oldhammer, Peter Turander, Håkan Thenander, Birgitta Kvist</t>
         </is>
       </c>
       <c r="AY137" t="inlineStr"/>
@@ -16447,7 +16447,7 @@
       </c>
       <c r="AX140" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer, Birgitta Kvist, Håkan Thenander, Peter Turander</t>
+          <t>Bengt Oldhammer, Peter Turander, Håkan Thenander, Birgitta Kvist</t>
         </is>
       </c>
       <c r="AY140" t="inlineStr"/>
@@ -16559,7 +16559,7 @@
       </c>
       <c r="AX141" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer, Birgitta Kvist, Håkan Thenander, Peter Turander</t>
+          <t>Bengt Oldhammer, Peter Turander, Håkan Thenander, Birgitta Kvist</t>
         </is>
       </c>
       <c r="AY141" t="inlineStr"/>

--- a/artfynd/A 20531-2025 artfynd.xlsx
+++ b/artfynd/A 20531-2025 artfynd.xlsx
@@ -1457,7 +1457,7 @@
         <v>136687803</v>
       </c>
       <c r="B9" t="n">
-        <v>79508</v>
+        <v>79512</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1589,7 +1589,7 @@
         <v>136687805</v>
       </c>
       <c r="B10" t="n">
-        <v>79508</v>
+        <v>79512</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1721,7 +1721,7 @@
         <v>136687806</v>
       </c>
       <c r="B11" t="n">
-        <v>79508</v>
+        <v>79512</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1853,7 +1853,7 @@
         <v>136689322</v>
       </c>
       <c r="B12" t="n">
-        <v>79508</v>
+        <v>79512</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1965,7 +1965,7 @@
         <v>136689361</v>
       </c>
       <c r="B13" t="n">
-        <v>79508</v>
+        <v>79512</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2077,7 +2077,7 @@
         <v>136687804</v>
       </c>
       <c r="B14" t="n">
-        <v>83343</v>
+        <v>83347</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2204,7 +2204,7 @@
         <v>136689343</v>
       </c>
       <c r="B15" t="n">
-        <v>91889</v>
+        <v>91891</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2316,7 +2316,7 @@
         <v>136689338</v>
       </c>
       <c r="B16" t="n">
-        <v>93055</v>
+        <v>93057</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2428,7 +2428,7 @@
         <v>136689333</v>
       </c>
       <c r="B17" t="n">
-        <v>93083</v>
+        <v>93085</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2540,7 +2540,7 @@
         <v>136689344</v>
       </c>
       <c r="B18" t="n">
-        <v>93083</v>
+        <v>93085</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2652,7 +2652,7 @@
         <v>136689356</v>
       </c>
       <c r="B19" t="n">
-        <v>93083</v>
+        <v>93085</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2764,7 +2764,7 @@
         <v>136689357</v>
       </c>
       <c r="B20" t="n">
-        <v>93083</v>
+        <v>93085</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2880,7 +2880,7 @@
         <v>136689363</v>
       </c>
       <c r="B21" t="n">
-        <v>93083</v>
+        <v>93085</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2992,7 +2992,7 @@
         <v>136699216</v>
       </c>
       <c r="B22" t="n">
-        <v>93083</v>
+        <v>93085</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3093,7 +3093,7 @@
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Håkan Thenander, Bengt Oldhammer, Peter Turander, Birgitta Kvist</t>
+          <t>Håkan Thenander, Birgitta Kvist, Peter Turander, Bengt Oldhammer</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
@@ -9842,7 +9842,7 @@
         <v>136689324</v>
       </c>
       <c r="B83" t="n">
-        <v>79476</v>
+        <v>79480</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -9954,7 +9954,7 @@
         <v>136689329</v>
       </c>
       <c r="B84" t="n">
-        <v>79476</v>
+        <v>79480</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -10858,7 +10858,7 @@
         <v>136689345</v>
       </c>
       <c r="B92" t="n">
-        <v>83463</v>
+        <v>83467</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -10970,7 +10970,7 @@
         <v>136699227</v>
       </c>
       <c r="B93" t="n">
-        <v>83463</v>
+        <v>83467</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -11067,7 +11067,7 @@
       </c>
       <c r="AX93" t="inlineStr">
         <is>
-          <t>Håkan Thenander, Bengt Oldhammer, Peter Turander, Birgitta Kvist</t>
+          <t>Håkan Thenander, Birgitta Kvist, Peter Turander, Bengt Oldhammer</t>
         </is>
       </c>
       <c r="AY93" t="inlineStr"/>
@@ -12329,7 +12329,7 @@
       </c>
       <c r="AX104" t="inlineStr">
         <is>
-          <t>Håkan Thenander, Bengt Oldhammer, Peter Turander, Birgitta Kvist</t>
+          <t>Håkan Thenander, Birgitta Kvist, Peter Turander, Bengt Oldhammer</t>
         </is>
       </c>
       <c r="AY104" t="inlineStr"/>
@@ -12446,7 +12446,7 @@
       </c>
       <c r="AX105" t="inlineStr">
         <is>
-          <t>Håkan Thenander, Bengt Oldhammer, Peter Turander, Birgitta Kvist</t>
+          <t>Håkan Thenander, Birgitta Kvist, Peter Turander, Bengt Oldhammer</t>
         </is>
       </c>
       <c r="AY105" t="inlineStr"/>
@@ -12563,7 +12563,7 @@
       </c>
       <c r="AX106" t="inlineStr">
         <is>
-          <t>Håkan Thenander, Bengt Oldhammer, Peter Turander, Birgitta Kvist</t>
+          <t>Håkan Thenander, Birgitta Kvist, Peter Turander, Bengt Oldhammer</t>
         </is>
       </c>
       <c r="AY106" t="inlineStr"/>
@@ -12689,7 +12689,7 @@
       </c>
       <c r="AX107" t="inlineStr">
         <is>
-          <t>Håkan Thenander, Bengt Oldhammer, Peter Turander, Birgitta Kvist</t>
+          <t>Håkan Thenander, Birgitta Kvist, Peter Turander, Bengt Oldhammer</t>
         </is>
       </c>
       <c r="AY107" t="inlineStr"/>
@@ -14780,7 +14780,7 @@
         <v>136689348</v>
       </c>
       <c r="B126" t="n">
-        <v>108378</v>
+        <v>108384</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -14892,7 +14892,7 @@
         <v>136689336</v>
       </c>
       <c r="B127" t="n">
-        <v>108448</v>
+        <v>108454</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -15227,7 +15227,7 @@
         <v>136689318</v>
       </c>
       <c r="B130" t="n">
-        <v>98215</v>
+        <v>98221</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
@@ -15339,7 +15339,7 @@
         <v>136689331</v>
       </c>
       <c r="B131" t="n">
-        <v>98215</v>
+        <v>98221</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
@@ -15451,7 +15451,7 @@
         <v>136689342</v>
       </c>
       <c r="B132" t="n">
-        <v>98215</v>
+        <v>98221</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
@@ -15782,7 +15782,7 @@
         <v>136689346</v>
       </c>
       <c r="B135" t="n">
-        <v>104876</v>
+        <v>104882</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
@@ -15898,7 +15898,7 @@
         <v>136689350</v>
       </c>
       <c r="B136" t="n">
-        <v>104876</v>
+        <v>104882</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
@@ -16010,7 +16010,7 @@
         <v>136689358</v>
       </c>
       <c r="B137" t="n">
-        <v>104876</v>
+        <v>104882</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
@@ -16122,7 +16122,7 @@
         <v>136699224</v>
       </c>
       <c r="B138" t="n">
-        <v>104876</v>
+        <v>104882</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
@@ -16223,7 +16223,7 @@
       </c>
       <c r="AX138" t="inlineStr">
         <is>
-          <t>Håkan Thenander, Bengt Oldhammer, Peter Turander, Birgitta Kvist</t>
+          <t>Håkan Thenander, Birgitta Kvist, Peter Turander, Bengt Oldhammer</t>
         </is>
       </c>
       <c r="AY138" t="inlineStr"/>
@@ -16238,7 +16238,7 @@
         <v>136699225</v>
       </c>
       <c r="B139" t="n">
-        <v>104876</v>
+        <v>104882</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
@@ -16335,7 +16335,7 @@
       </c>
       <c r="AX139" t="inlineStr">
         <is>
-          <t>Håkan Thenander, Bengt Oldhammer, Peter Turander, Birgitta Kvist</t>
+          <t>Håkan Thenander, Birgitta Kvist, Peter Turander, Bengt Oldhammer</t>
         </is>
       </c>
       <c r="AY139" t="inlineStr"/>
@@ -16350,7 +16350,7 @@
         <v>136689352</v>
       </c>
       <c r="B140" t="n">
-        <v>99630</v>
+        <v>99636</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
@@ -16462,7 +16462,7 @@
         <v>136689353</v>
       </c>
       <c r="B141" t="n">
-        <v>99159</v>
+        <v>99165</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>

--- a/artfynd/A 20531-2025 artfynd.xlsx
+++ b/artfynd/A 20531-2025 artfynd.xlsx
@@ -1457,7 +1457,7 @@
         <v>136687803</v>
       </c>
       <c r="B9" t="n">
-        <v>79512</v>
+        <v>79514</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1589,7 +1589,7 @@
         <v>136687805</v>
       </c>
       <c r="B10" t="n">
-        <v>79512</v>
+        <v>79514</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1721,7 +1721,7 @@
         <v>136687806</v>
       </c>
       <c r="B11" t="n">
-        <v>79512</v>
+        <v>79514</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1853,7 +1853,7 @@
         <v>136689322</v>
       </c>
       <c r="B12" t="n">
-        <v>79512</v>
+        <v>79514</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1965,7 +1965,7 @@
         <v>136689361</v>
       </c>
       <c r="B13" t="n">
-        <v>79512</v>
+        <v>79514</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2077,7 +2077,7 @@
         <v>136687804</v>
       </c>
       <c r="B14" t="n">
-        <v>83347</v>
+        <v>83349</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2204,7 +2204,7 @@
         <v>136689343</v>
       </c>
       <c r="B15" t="n">
-        <v>91891</v>
+        <v>91893</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2316,7 +2316,7 @@
         <v>136689338</v>
       </c>
       <c r="B16" t="n">
-        <v>93057</v>
+        <v>93059</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2428,7 +2428,7 @@
         <v>136689333</v>
       </c>
       <c r="B17" t="n">
-        <v>93085</v>
+        <v>93087</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2540,7 +2540,7 @@
         <v>136689344</v>
       </c>
       <c r="B18" t="n">
-        <v>93085</v>
+        <v>93087</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2652,7 +2652,7 @@
         <v>136689356</v>
       </c>
       <c r="B19" t="n">
-        <v>93085</v>
+        <v>93087</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2764,7 +2764,7 @@
         <v>136689357</v>
       </c>
       <c r="B20" t="n">
-        <v>93085</v>
+        <v>93087</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2880,7 +2880,7 @@
         <v>136689363</v>
       </c>
       <c r="B21" t="n">
-        <v>93085</v>
+        <v>93087</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2992,7 +2992,7 @@
         <v>136699216</v>
       </c>
       <c r="B22" t="n">
-        <v>93085</v>
+        <v>93087</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3093,7 +3093,7 @@
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Håkan Thenander, Birgitta Kvist, Peter Turander, Bengt Oldhammer</t>
+          <t>Håkan Thenander, Bengt Oldhammer, Peter Turander, Birgitta Kvist</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
@@ -9842,7 +9842,7 @@
         <v>136689324</v>
       </c>
       <c r="B83" t="n">
-        <v>79480</v>
+        <v>79482</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -9954,7 +9954,7 @@
         <v>136689329</v>
       </c>
       <c r="B84" t="n">
-        <v>79480</v>
+        <v>79482</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -10858,7 +10858,7 @@
         <v>136689345</v>
       </c>
       <c r="B92" t="n">
-        <v>83467</v>
+        <v>83469</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -10970,7 +10970,7 @@
         <v>136699227</v>
       </c>
       <c r="B93" t="n">
-        <v>83467</v>
+        <v>83469</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -11067,7 +11067,7 @@
       </c>
       <c r="AX93" t="inlineStr">
         <is>
-          <t>Håkan Thenander, Birgitta Kvist, Peter Turander, Bengt Oldhammer</t>
+          <t>Håkan Thenander, Bengt Oldhammer, Peter Turander, Birgitta Kvist</t>
         </is>
       </c>
       <c r="AY93" t="inlineStr"/>
@@ -12329,7 +12329,7 @@
       </c>
       <c r="AX104" t="inlineStr">
         <is>
-          <t>Håkan Thenander, Birgitta Kvist, Peter Turander, Bengt Oldhammer</t>
+          <t>Håkan Thenander, Bengt Oldhammer, Peter Turander, Birgitta Kvist</t>
         </is>
       </c>
       <c r="AY104" t="inlineStr"/>
@@ -12446,7 +12446,7 @@
       </c>
       <c r="AX105" t="inlineStr">
         <is>
-          <t>Håkan Thenander, Birgitta Kvist, Peter Turander, Bengt Oldhammer</t>
+          <t>Håkan Thenander, Bengt Oldhammer, Peter Turander, Birgitta Kvist</t>
         </is>
       </c>
       <c r="AY105" t="inlineStr"/>
@@ -12563,7 +12563,7 @@
       </c>
       <c r="AX106" t="inlineStr">
         <is>
-          <t>Håkan Thenander, Birgitta Kvist, Peter Turander, Bengt Oldhammer</t>
+          <t>Håkan Thenander, Bengt Oldhammer, Peter Turander, Birgitta Kvist</t>
         </is>
       </c>
       <c r="AY106" t="inlineStr"/>
@@ -12689,7 +12689,7 @@
       </c>
       <c r="AX107" t="inlineStr">
         <is>
-          <t>Håkan Thenander, Birgitta Kvist, Peter Turander, Bengt Oldhammer</t>
+          <t>Håkan Thenander, Bengt Oldhammer, Peter Turander, Birgitta Kvist</t>
         </is>
       </c>
       <c r="AY107" t="inlineStr"/>
@@ -14780,7 +14780,7 @@
         <v>136689348</v>
       </c>
       <c r="B126" t="n">
-        <v>108384</v>
+        <v>108386</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -14892,7 +14892,7 @@
         <v>136689336</v>
       </c>
       <c r="B127" t="n">
-        <v>108454</v>
+        <v>108456</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -15227,7 +15227,7 @@
         <v>136689318</v>
       </c>
       <c r="B130" t="n">
-        <v>98221</v>
+        <v>98223</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
@@ -15339,7 +15339,7 @@
         <v>136689331</v>
       </c>
       <c r="B131" t="n">
-        <v>98221</v>
+        <v>98223</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
@@ -15451,7 +15451,7 @@
         <v>136689342</v>
       </c>
       <c r="B132" t="n">
-        <v>98221</v>
+        <v>98223</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
@@ -15782,7 +15782,7 @@
         <v>136689346</v>
       </c>
       <c r="B135" t="n">
-        <v>104882</v>
+        <v>104884</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
@@ -15898,7 +15898,7 @@
         <v>136689350</v>
       </c>
       <c r="B136" t="n">
-        <v>104882</v>
+        <v>104884</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
@@ -16010,7 +16010,7 @@
         <v>136689358</v>
       </c>
       <c r="B137" t="n">
-        <v>104882</v>
+        <v>104884</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
@@ -16122,7 +16122,7 @@
         <v>136699224</v>
       </c>
       <c r="B138" t="n">
-        <v>104882</v>
+        <v>104884</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
@@ -16223,7 +16223,7 @@
       </c>
       <c r="AX138" t="inlineStr">
         <is>
-          <t>Håkan Thenander, Birgitta Kvist, Peter Turander, Bengt Oldhammer</t>
+          <t>Håkan Thenander, Bengt Oldhammer, Peter Turander, Birgitta Kvist</t>
         </is>
       </c>
       <c r="AY138" t="inlineStr"/>
@@ -16238,7 +16238,7 @@
         <v>136699225</v>
       </c>
       <c r="B139" t="n">
-        <v>104882</v>
+        <v>104884</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
@@ -16335,7 +16335,7 @@
       </c>
       <c r="AX139" t="inlineStr">
         <is>
-          <t>Håkan Thenander, Birgitta Kvist, Peter Turander, Bengt Oldhammer</t>
+          <t>Håkan Thenander, Bengt Oldhammer, Peter Turander, Birgitta Kvist</t>
         </is>
       </c>
       <c r="AY139" t="inlineStr"/>
@@ -16350,7 +16350,7 @@
         <v>136689352</v>
       </c>
       <c r="B140" t="n">
-        <v>99636</v>
+        <v>99638</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
@@ -16462,7 +16462,7 @@
         <v>136689353</v>
       </c>
       <c r="B141" t="n">
-        <v>99165</v>
+        <v>99167</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>

--- a/artfynd/A 20531-2025 artfynd.xlsx
+++ b/artfynd/A 20531-2025 artfynd.xlsx
@@ -1457,7 +1457,7 @@
         <v>136687803</v>
       </c>
       <c r="B9" t="n">
-        <v>79514</v>
+        <v>79515</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1589,7 +1589,7 @@
         <v>136687805</v>
       </c>
       <c r="B10" t="n">
-        <v>79514</v>
+        <v>79515</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1721,7 +1721,7 @@
         <v>136687806</v>
       </c>
       <c r="B11" t="n">
-        <v>79514</v>
+        <v>79515</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1853,7 +1853,7 @@
         <v>136689322</v>
       </c>
       <c r="B12" t="n">
-        <v>79514</v>
+        <v>79515</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1965,7 +1965,7 @@
         <v>136689361</v>
       </c>
       <c r="B13" t="n">
-        <v>79514</v>
+        <v>79515</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2077,7 +2077,7 @@
         <v>136687804</v>
       </c>
       <c r="B14" t="n">
-        <v>83349</v>
+        <v>83350</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2204,7 +2204,7 @@
         <v>136689343</v>
       </c>
       <c r="B15" t="n">
-        <v>91893</v>
+        <v>91894</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2316,7 +2316,7 @@
         <v>136689338</v>
       </c>
       <c r="B16" t="n">
-        <v>93059</v>
+        <v>93060</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2428,7 +2428,7 @@
         <v>136689333</v>
       </c>
       <c r="B17" t="n">
-        <v>93087</v>
+        <v>93088</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2540,7 +2540,7 @@
         <v>136689344</v>
       </c>
       <c r="B18" t="n">
-        <v>93087</v>
+        <v>93088</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2652,7 +2652,7 @@
         <v>136689356</v>
       </c>
       <c r="B19" t="n">
-        <v>93087</v>
+        <v>93088</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2764,7 +2764,7 @@
         <v>136689357</v>
       </c>
       <c r="B20" t="n">
-        <v>93087</v>
+        <v>93088</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2880,7 +2880,7 @@
         <v>136689363</v>
       </c>
       <c r="B21" t="n">
-        <v>93087</v>
+        <v>93088</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2992,7 +2992,7 @@
         <v>136699216</v>
       </c>
       <c r="B22" t="n">
-        <v>93087</v>
+        <v>93088</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -9842,7 +9842,7 @@
         <v>136689324</v>
       </c>
       <c r="B83" t="n">
-        <v>79482</v>
+        <v>79483</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -9954,7 +9954,7 @@
         <v>136689329</v>
       </c>
       <c r="B84" t="n">
-        <v>79482</v>
+        <v>79483</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -10858,7 +10858,7 @@
         <v>136689345</v>
       </c>
       <c r="B92" t="n">
-        <v>83469</v>
+        <v>83470</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -10970,7 +10970,7 @@
         <v>136699227</v>
       </c>
       <c r="B93" t="n">
-        <v>83469</v>
+        <v>83470</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -14780,7 +14780,7 @@
         <v>136689348</v>
       </c>
       <c r="B126" t="n">
-        <v>108386</v>
+        <v>108387</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -14892,7 +14892,7 @@
         <v>136689336</v>
       </c>
       <c r="B127" t="n">
-        <v>108456</v>
+        <v>108457</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -15227,7 +15227,7 @@
         <v>136689318</v>
       </c>
       <c r="B130" t="n">
-        <v>98223</v>
+        <v>98224</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
@@ -15339,7 +15339,7 @@
         <v>136689331</v>
       </c>
       <c r="B131" t="n">
-        <v>98223</v>
+        <v>98224</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
@@ -15451,7 +15451,7 @@
         <v>136689342</v>
       </c>
       <c r="B132" t="n">
-        <v>98223</v>
+        <v>98224</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
@@ -15782,7 +15782,7 @@
         <v>136689346</v>
       </c>
       <c r="B135" t="n">
-        <v>104884</v>
+        <v>104885</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
@@ -15898,7 +15898,7 @@
         <v>136689350</v>
       </c>
       <c r="B136" t="n">
-        <v>104884</v>
+        <v>104885</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
@@ -16010,7 +16010,7 @@
         <v>136689358</v>
       </c>
       <c r="B137" t="n">
-        <v>104884</v>
+        <v>104885</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
@@ -16122,7 +16122,7 @@
         <v>136699224</v>
       </c>
       <c r="B138" t="n">
-        <v>104884</v>
+        <v>104885</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
@@ -16238,7 +16238,7 @@
         <v>136699225</v>
       </c>
       <c r="B139" t="n">
-        <v>104884</v>
+        <v>104885</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
@@ -16350,7 +16350,7 @@
         <v>136689352</v>
       </c>
       <c r="B140" t="n">
-        <v>99638</v>
+        <v>99639</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
@@ -16462,7 +16462,7 @@
         <v>136689353</v>
       </c>
       <c r="B141" t="n">
-        <v>99167</v>
+        <v>99168</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>

--- a/artfynd/A 20531-2025 artfynd.xlsx
+++ b/artfynd/A 20531-2025 artfynd.xlsx
@@ -2204,7 +2204,7 @@
         <v>136689343</v>
       </c>
       <c r="B15" t="n">
-        <v>91894</v>
+        <v>91900</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2316,7 +2316,7 @@
         <v>136689338</v>
       </c>
       <c r="B16" t="n">
-        <v>93060</v>
+        <v>93066</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2428,7 +2428,7 @@
         <v>136689333</v>
       </c>
       <c r="B17" t="n">
-        <v>93088</v>
+        <v>93094</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2540,7 +2540,7 @@
         <v>136689344</v>
       </c>
       <c r="B18" t="n">
-        <v>93088</v>
+        <v>93094</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2652,7 +2652,7 @@
         <v>136689356</v>
       </c>
       <c r="B19" t="n">
-        <v>93088</v>
+        <v>93094</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2764,7 +2764,7 @@
         <v>136689357</v>
       </c>
       <c r="B20" t="n">
-        <v>93088</v>
+        <v>93094</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2880,7 +2880,7 @@
         <v>136689363</v>
       </c>
       <c r="B21" t="n">
-        <v>93088</v>
+        <v>93094</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2992,7 +2992,7 @@
         <v>136699216</v>
       </c>
       <c r="B22" t="n">
-        <v>93088</v>
+        <v>93094</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -14780,7 +14780,7 @@
         <v>136689348</v>
       </c>
       <c r="B126" t="n">
-        <v>108387</v>
+        <v>108393</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -14892,7 +14892,7 @@
         <v>136689336</v>
       </c>
       <c r="B127" t="n">
-        <v>108457</v>
+        <v>108463</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -15227,7 +15227,7 @@
         <v>136689318</v>
       </c>
       <c r="B130" t="n">
-        <v>98224</v>
+        <v>98230</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
@@ -15339,7 +15339,7 @@
         <v>136689331</v>
       </c>
       <c r="B131" t="n">
-        <v>98224</v>
+        <v>98230</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
@@ -15451,7 +15451,7 @@
         <v>136689342</v>
       </c>
       <c r="B132" t="n">
-        <v>98224</v>
+        <v>98230</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
@@ -15782,7 +15782,7 @@
         <v>136689346</v>
       </c>
       <c r="B135" t="n">
-        <v>104885</v>
+        <v>104891</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
@@ -15898,7 +15898,7 @@
         <v>136689350</v>
       </c>
       <c r="B136" t="n">
-        <v>104885</v>
+        <v>104891</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
@@ -16010,7 +16010,7 @@
         <v>136689358</v>
       </c>
       <c r="B137" t="n">
-        <v>104885</v>
+        <v>104891</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
@@ -16122,7 +16122,7 @@
         <v>136699224</v>
       </c>
       <c r="B138" t="n">
-        <v>104885</v>
+        <v>104891</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
@@ -16238,7 +16238,7 @@
         <v>136699225</v>
       </c>
       <c r="B139" t="n">
-        <v>104885</v>
+        <v>104891</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
@@ -16350,7 +16350,7 @@
         <v>136689352</v>
       </c>
       <c r="B140" t="n">
-        <v>99639</v>
+        <v>99645</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
@@ -16462,7 +16462,7 @@
         <v>136689353</v>
       </c>
       <c r="B141" t="n">
-        <v>99168</v>
+        <v>99174</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>

--- a/artfynd/A 20531-2025 artfynd.xlsx
+++ b/artfynd/A 20531-2025 artfynd.xlsx
@@ -1457,7 +1457,7 @@
         <v>136687803</v>
       </c>
       <c r="B9" t="n">
-        <v>79515</v>
+        <v>79517</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1589,7 +1589,7 @@
         <v>136687805</v>
       </c>
       <c r="B10" t="n">
-        <v>79515</v>
+        <v>79517</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1721,7 +1721,7 @@
         <v>136687806</v>
       </c>
       <c r="B11" t="n">
-        <v>79515</v>
+        <v>79517</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1853,7 +1853,7 @@
         <v>136689322</v>
       </c>
       <c r="B12" t="n">
-        <v>79515</v>
+        <v>79517</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1965,7 +1965,7 @@
         <v>136689361</v>
       </c>
       <c r="B13" t="n">
-        <v>79515</v>
+        <v>79517</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2077,7 +2077,7 @@
         <v>136687804</v>
       </c>
       <c r="B14" t="n">
-        <v>83350</v>
+        <v>83354</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2204,7 +2204,7 @@
         <v>136689343</v>
       </c>
       <c r="B15" t="n">
-        <v>91900</v>
+        <v>91904</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2316,7 +2316,7 @@
         <v>136689338</v>
       </c>
       <c r="B16" t="n">
-        <v>93066</v>
+        <v>93070</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2428,7 +2428,7 @@
         <v>136689333</v>
       </c>
       <c r="B17" t="n">
-        <v>93094</v>
+        <v>93098</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2540,7 +2540,7 @@
         <v>136689344</v>
       </c>
       <c r="B18" t="n">
-        <v>93094</v>
+        <v>93098</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2652,7 +2652,7 @@
         <v>136689356</v>
       </c>
       <c r="B19" t="n">
-        <v>93094</v>
+        <v>93098</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2764,7 +2764,7 @@
         <v>136689357</v>
       </c>
       <c r="B20" t="n">
-        <v>93094</v>
+        <v>93098</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2880,7 +2880,7 @@
         <v>136689363</v>
       </c>
       <c r="B21" t="n">
-        <v>93094</v>
+        <v>93098</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2992,7 +2992,7 @@
         <v>136699216</v>
       </c>
       <c r="B22" t="n">
-        <v>93094</v>
+        <v>93098</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -9842,7 +9842,7 @@
         <v>136689324</v>
       </c>
       <c r="B83" t="n">
-        <v>79483</v>
+        <v>79485</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -9954,7 +9954,7 @@
         <v>136689329</v>
       </c>
       <c r="B84" t="n">
-        <v>79483</v>
+        <v>79485</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -10858,7 +10858,7 @@
         <v>136689345</v>
       </c>
       <c r="B92" t="n">
-        <v>83470</v>
+        <v>83474</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -10970,7 +10970,7 @@
         <v>136699227</v>
       </c>
       <c r="B93" t="n">
-        <v>83470</v>
+        <v>83474</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -14780,7 +14780,7 @@
         <v>136689348</v>
       </c>
       <c r="B126" t="n">
-        <v>108393</v>
+        <v>108397</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -14892,7 +14892,7 @@
         <v>136689336</v>
       </c>
       <c r="B127" t="n">
-        <v>108463</v>
+        <v>108467</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -15227,7 +15227,7 @@
         <v>136689318</v>
       </c>
       <c r="B130" t="n">
-        <v>98230</v>
+        <v>98234</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
@@ -15339,7 +15339,7 @@
         <v>136689331</v>
       </c>
       <c r="B131" t="n">
-        <v>98230</v>
+        <v>98234</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
@@ -15451,7 +15451,7 @@
         <v>136689342</v>
       </c>
       <c r="B132" t="n">
-        <v>98230</v>
+        <v>98234</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
@@ -15782,7 +15782,7 @@
         <v>136689346</v>
       </c>
       <c r="B135" t="n">
-        <v>104891</v>
+        <v>104895</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
@@ -15898,7 +15898,7 @@
         <v>136689350</v>
       </c>
       <c r="B136" t="n">
-        <v>104891</v>
+        <v>104895</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
@@ -16010,7 +16010,7 @@
         <v>136689358</v>
       </c>
       <c r="B137" t="n">
-        <v>104891</v>
+        <v>104895</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
@@ -16122,7 +16122,7 @@
         <v>136699224</v>
       </c>
       <c r="B138" t="n">
-        <v>104891</v>
+        <v>104895</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
@@ -16238,7 +16238,7 @@
         <v>136699225</v>
       </c>
       <c r="B139" t="n">
-        <v>104891</v>
+        <v>104895</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
@@ -16350,7 +16350,7 @@
         <v>136689352</v>
       </c>
       <c r="B140" t="n">
-        <v>99645</v>
+        <v>99649</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
@@ -16462,7 +16462,7 @@
         <v>136689353</v>
       </c>
       <c r="B141" t="n">
-        <v>99174</v>
+        <v>99178</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>

--- a/artfynd/A 20531-2025 artfynd.xlsx
+++ b/artfynd/A 20531-2025 artfynd.xlsx
@@ -14780,7 +14780,7 @@
         <v>136689348</v>
       </c>
       <c r="B126" t="n">
-        <v>108397</v>
+        <v>108399</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -14892,7 +14892,7 @@
         <v>136689336</v>
       </c>
       <c r="B127" t="n">
-        <v>108467</v>
+        <v>108469</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -15227,7 +15227,7 @@
         <v>136689318</v>
       </c>
       <c r="B130" t="n">
-        <v>98234</v>
+        <v>98236</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
@@ -15339,7 +15339,7 @@
         <v>136689331</v>
       </c>
       <c r="B131" t="n">
-        <v>98234</v>
+        <v>98236</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
@@ -15451,7 +15451,7 @@
         <v>136689342</v>
       </c>
       <c r="B132" t="n">
-        <v>98234</v>
+        <v>98236</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
@@ -15782,7 +15782,7 @@
         <v>136689346</v>
       </c>
       <c r="B135" t="n">
-        <v>104895</v>
+        <v>104897</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
@@ -15898,7 +15898,7 @@
         <v>136689350</v>
       </c>
       <c r="B136" t="n">
-        <v>104895</v>
+        <v>104897</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
@@ -16010,7 +16010,7 @@
         <v>136689358</v>
       </c>
       <c r="B137" t="n">
-        <v>104895</v>
+        <v>104897</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
@@ -16122,7 +16122,7 @@
         <v>136699224</v>
       </c>
       <c r="B138" t="n">
-        <v>104895</v>
+        <v>104897</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
@@ -16238,7 +16238,7 @@
         <v>136699225</v>
       </c>
       <c r="B139" t="n">
-        <v>104895</v>
+        <v>104897</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
@@ -16350,7 +16350,7 @@
         <v>136689352</v>
       </c>
       <c r="B140" t="n">
-        <v>99649</v>
+        <v>99651</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
@@ -16462,7 +16462,7 @@
         <v>136689353</v>
       </c>
       <c r="B141" t="n">
-        <v>99178</v>
+        <v>99180</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>

--- a/artfynd/A 20531-2025 artfynd.xlsx
+++ b/artfynd/A 20531-2025 artfynd.xlsx
@@ -1457,7 +1457,7 @@
         <v>136687803</v>
       </c>
       <c r="B9" t="n">
-        <v>79517</v>
+        <v>79520</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1589,7 +1589,7 @@
         <v>136687805</v>
       </c>
       <c r="B10" t="n">
-        <v>79517</v>
+        <v>79520</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1721,7 +1721,7 @@
         <v>136687806</v>
       </c>
       <c r="B11" t="n">
-        <v>79517</v>
+        <v>79520</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1853,7 +1853,7 @@
         <v>136689322</v>
       </c>
       <c r="B12" t="n">
-        <v>79517</v>
+        <v>79520</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1965,7 +1965,7 @@
         <v>136689361</v>
       </c>
       <c r="B13" t="n">
-        <v>79517</v>
+        <v>79520</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2077,7 +2077,7 @@
         <v>136687804</v>
       </c>
       <c r="B14" t="n">
-        <v>83354</v>
+        <v>83356</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2204,7 +2204,7 @@
         <v>136689343</v>
       </c>
       <c r="B15" t="n">
-        <v>91904</v>
+        <v>91906</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2316,7 +2316,7 @@
         <v>136689338</v>
       </c>
       <c r="B16" t="n">
-        <v>93070</v>
+        <v>93072</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2428,7 +2428,7 @@
         <v>136689333</v>
       </c>
       <c r="B17" t="n">
-        <v>93098</v>
+        <v>93100</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2540,7 +2540,7 @@
         <v>136689344</v>
       </c>
       <c r="B18" t="n">
-        <v>93098</v>
+        <v>93100</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2652,7 +2652,7 @@
         <v>136689356</v>
       </c>
       <c r="B19" t="n">
-        <v>93098</v>
+        <v>93100</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2764,7 +2764,7 @@
         <v>136689357</v>
       </c>
       <c r="B20" t="n">
-        <v>93098</v>
+        <v>93100</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2880,7 +2880,7 @@
         <v>136689363</v>
       </c>
       <c r="B21" t="n">
-        <v>93098</v>
+        <v>93100</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2992,7 +2992,7 @@
         <v>136699216</v>
       </c>
       <c r="B22" t="n">
-        <v>93098</v>
+        <v>93100</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -9842,7 +9842,7 @@
         <v>136689324</v>
       </c>
       <c r="B83" t="n">
-        <v>79485</v>
+        <v>79488</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -9954,7 +9954,7 @@
         <v>136689329</v>
       </c>
       <c r="B84" t="n">
-        <v>79485</v>
+        <v>79488</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -10858,7 +10858,7 @@
         <v>136689345</v>
       </c>
       <c r="B92" t="n">
-        <v>83474</v>
+        <v>83476</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -10970,7 +10970,7 @@
         <v>136699227</v>
       </c>
       <c r="B93" t="n">
-        <v>83474</v>
+        <v>83476</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -14780,7 +14780,7 @@
         <v>136689348</v>
       </c>
       <c r="B126" t="n">
-        <v>108399</v>
+        <v>108401</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -14892,7 +14892,7 @@
         <v>136689336</v>
       </c>
       <c r="B127" t="n">
-        <v>108469</v>
+        <v>108471</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -15227,7 +15227,7 @@
         <v>136689318</v>
       </c>
       <c r="B130" t="n">
-        <v>98236</v>
+        <v>98238</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
@@ -15339,7 +15339,7 @@
         <v>136689331</v>
       </c>
       <c r="B131" t="n">
-        <v>98236</v>
+        <v>98238</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
@@ -15451,7 +15451,7 @@
         <v>136689342</v>
       </c>
       <c r="B132" t="n">
-        <v>98236</v>
+        <v>98238</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
@@ -15782,7 +15782,7 @@
         <v>136689346</v>
       </c>
       <c r="B135" t="n">
-        <v>104897</v>
+        <v>104899</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
@@ -15898,7 +15898,7 @@
         <v>136689350</v>
       </c>
       <c r="B136" t="n">
-        <v>104897</v>
+        <v>104899</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
@@ -16010,7 +16010,7 @@
         <v>136689358</v>
       </c>
       <c r="B137" t="n">
-        <v>104897</v>
+        <v>104899</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
@@ -16122,7 +16122,7 @@
         <v>136699224</v>
       </c>
       <c r="B138" t="n">
-        <v>104897</v>
+        <v>104899</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
@@ -16238,7 +16238,7 @@
         <v>136699225</v>
       </c>
       <c r="B139" t="n">
-        <v>104897</v>
+        <v>104899</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
@@ -16350,7 +16350,7 @@
         <v>136689352</v>
       </c>
       <c r="B140" t="n">
-        <v>99651</v>
+        <v>99653</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
@@ -16462,7 +16462,7 @@
         <v>136689353</v>
       </c>
       <c r="B141" t="n">
-        <v>99180</v>
+        <v>99182</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>

--- a/artfynd/A 20531-2025 artfynd.xlsx
+++ b/artfynd/A 20531-2025 artfynd.xlsx
@@ -1457,7 +1457,7 @@
         <v>136687803</v>
       </c>
       <c r="B9" t="n">
-        <v>79520</v>
+        <v>79533</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1589,7 +1589,7 @@
         <v>136687805</v>
       </c>
       <c r="B10" t="n">
-        <v>79520</v>
+        <v>79533</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1721,7 +1721,7 @@
         <v>136687806</v>
       </c>
       <c r="B11" t="n">
-        <v>79520</v>
+        <v>79533</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1853,7 +1853,7 @@
         <v>136689322</v>
       </c>
       <c r="B12" t="n">
-        <v>79520</v>
+        <v>79533</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1965,7 +1965,7 @@
         <v>136689361</v>
       </c>
       <c r="B13" t="n">
-        <v>79520</v>
+        <v>79533</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2077,7 +2077,7 @@
         <v>136687804</v>
       </c>
       <c r="B14" t="n">
-        <v>83356</v>
+        <v>83369</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2204,7 +2204,7 @@
         <v>136689343</v>
       </c>
       <c r="B15" t="n">
-        <v>91906</v>
+        <v>91919</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2316,7 +2316,7 @@
         <v>136689338</v>
       </c>
       <c r="B16" t="n">
-        <v>93072</v>
+        <v>93085</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2428,7 +2428,7 @@
         <v>136689333</v>
       </c>
       <c r="B17" t="n">
-        <v>93100</v>
+        <v>93113</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2540,7 +2540,7 @@
         <v>136689344</v>
       </c>
       <c r="B18" t="n">
-        <v>93100</v>
+        <v>93113</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2652,7 +2652,7 @@
         <v>136689356</v>
       </c>
       <c r="B19" t="n">
-        <v>93100</v>
+        <v>93113</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2764,7 +2764,7 @@
         <v>136689357</v>
       </c>
       <c r="B20" t="n">
-        <v>93100</v>
+        <v>93113</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2880,7 +2880,7 @@
         <v>136689363</v>
       </c>
       <c r="B21" t="n">
-        <v>93100</v>
+        <v>93113</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2992,7 +2992,7 @@
         <v>136699216</v>
       </c>
       <c r="B22" t="n">
-        <v>93100</v>
+        <v>93113</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -9842,7 +9842,7 @@
         <v>136689324</v>
       </c>
       <c r="B83" t="n">
-        <v>79488</v>
+        <v>79501</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -9954,7 +9954,7 @@
         <v>136689329</v>
       </c>
       <c r="B84" t="n">
-        <v>79488</v>
+        <v>79501</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -10858,7 +10858,7 @@
         <v>136689345</v>
       </c>
       <c r="B92" t="n">
-        <v>83476</v>
+        <v>83489</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -10970,7 +10970,7 @@
         <v>136699227</v>
       </c>
       <c r="B93" t="n">
-        <v>83476</v>
+        <v>83489</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -12227,7 +12227,7 @@
         <v>136699220</v>
       </c>
       <c r="B104" t="n">
-        <v>58008</v>
+        <v>58021</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -12344,7 +12344,7 @@
         <v>136699222</v>
       </c>
       <c r="B105" t="n">
-        <v>58008</v>
+        <v>58021</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -12461,7 +12461,7 @@
         <v>136699223</v>
       </c>
       <c r="B106" t="n">
-        <v>58008</v>
+        <v>58021</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -12578,7 +12578,7 @@
         <v>136699229</v>
       </c>
       <c r="B107" t="n">
-        <v>58008</v>
+        <v>58021</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -12704,7 +12704,7 @@
         <v>136689339</v>
       </c>
       <c r="B108" t="n">
-        <v>57195</v>
+        <v>57208</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -13172,7 +13172,7 @@
         <v>136689332</v>
       </c>
       <c r="B112" t="n">
-        <v>58169</v>
+        <v>58182</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -13284,7 +13284,7 @@
         <v>136689326</v>
       </c>
       <c r="B113" t="n">
-        <v>58629</v>
+        <v>58642</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -13401,7 +13401,7 @@
         <v>136689334</v>
       </c>
       <c r="B114" t="n">
-        <v>58667</v>
+        <v>58680</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -14780,7 +14780,7 @@
         <v>136689348</v>
       </c>
       <c r="B126" t="n">
-        <v>108401</v>
+        <v>108414</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -14892,7 +14892,7 @@
         <v>136689336</v>
       </c>
       <c r="B127" t="n">
-        <v>108471</v>
+        <v>108484</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -15227,7 +15227,7 @@
         <v>136689318</v>
       </c>
       <c r="B130" t="n">
-        <v>98238</v>
+        <v>98251</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
@@ -15339,7 +15339,7 @@
         <v>136689331</v>
       </c>
       <c r="B131" t="n">
-        <v>98238</v>
+        <v>98251</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
@@ -15451,7 +15451,7 @@
         <v>136689342</v>
       </c>
       <c r="B132" t="n">
-        <v>98238</v>
+        <v>98251</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
@@ -15782,7 +15782,7 @@
         <v>136689346</v>
       </c>
       <c r="B135" t="n">
-        <v>104899</v>
+        <v>104912</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
@@ -15898,7 +15898,7 @@
         <v>136689350</v>
       </c>
       <c r="B136" t="n">
-        <v>104899</v>
+        <v>104912</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
@@ -16010,7 +16010,7 @@
         <v>136689358</v>
       </c>
       <c r="B137" t="n">
-        <v>104899</v>
+        <v>104912</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
@@ -16122,7 +16122,7 @@
         <v>136699224</v>
       </c>
       <c r="B138" t="n">
-        <v>104899</v>
+        <v>104912</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
@@ -16238,7 +16238,7 @@
         <v>136699225</v>
       </c>
       <c r="B139" t="n">
-        <v>104899</v>
+        <v>104912</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
@@ -16350,7 +16350,7 @@
         <v>136689352</v>
       </c>
       <c r="B140" t="n">
-        <v>99653</v>
+        <v>99666</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
@@ -16462,7 +16462,7 @@
         <v>136689353</v>
       </c>
       <c r="B141" t="n">
-        <v>99182</v>
+        <v>99195</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>

--- a/artfynd/A 20531-2025 artfynd.xlsx
+++ b/artfynd/A 20531-2025 artfynd.xlsx
@@ -1457,7 +1457,7 @@
         <v>136687803</v>
       </c>
       <c r="B9" t="n">
-        <v>79533</v>
+        <v>79535</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1589,7 +1589,7 @@
         <v>136687805</v>
       </c>
       <c r="B10" t="n">
-        <v>79533</v>
+        <v>79535</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1721,7 +1721,7 @@
         <v>136687806</v>
       </c>
       <c r="B11" t="n">
-        <v>79533</v>
+        <v>79535</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1853,7 +1853,7 @@
         <v>136689322</v>
       </c>
       <c r="B12" t="n">
-        <v>79533</v>
+        <v>79535</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1965,7 +1965,7 @@
         <v>136689361</v>
       </c>
       <c r="B13" t="n">
-        <v>79533</v>
+        <v>79535</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2077,7 +2077,7 @@
         <v>136687804</v>
       </c>
       <c r="B14" t="n">
-        <v>83369</v>
+        <v>83371</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2204,7 +2204,7 @@
         <v>136689343</v>
       </c>
       <c r="B15" t="n">
-        <v>91919</v>
+        <v>91921</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2316,7 +2316,7 @@
         <v>136689338</v>
       </c>
       <c r="B16" t="n">
-        <v>93085</v>
+        <v>93087</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2428,7 +2428,7 @@
         <v>136689333</v>
       </c>
       <c r="B17" t="n">
-        <v>93113</v>
+        <v>93115</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2540,7 +2540,7 @@
         <v>136689344</v>
       </c>
       <c r="B18" t="n">
-        <v>93113</v>
+        <v>93115</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2652,7 +2652,7 @@
         <v>136689356</v>
       </c>
       <c r="B19" t="n">
-        <v>93113</v>
+        <v>93115</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2764,7 +2764,7 @@
         <v>136689357</v>
       </c>
       <c r="B20" t="n">
-        <v>93113</v>
+        <v>93115</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2880,7 +2880,7 @@
         <v>136689363</v>
       </c>
       <c r="B21" t="n">
-        <v>93113</v>
+        <v>93115</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2992,7 +2992,7 @@
         <v>136699216</v>
       </c>
       <c r="B22" t="n">
-        <v>93113</v>
+        <v>93115</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -9842,7 +9842,7 @@
         <v>136689324</v>
       </c>
       <c r="B83" t="n">
-        <v>79501</v>
+        <v>79503</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -9954,7 +9954,7 @@
         <v>136689329</v>
       </c>
       <c r="B84" t="n">
-        <v>79501</v>
+        <v>79503</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -10858,7 +10858,7 @@
         <v>136689345</v>
       </c>
       <c r="B92" t="n">
-        <v>83489</v>
+        <v>83491</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -10970,7 +10970,7 @@
         <v>136699227</v>
       </c>
       <c r="B93" t="n">
-        <v>83489</v>
+        <v>83491</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -12227,7 +12227,7 @@
         <v>136699220</v>
       </c>
       <c r="B104" t="n">
-        <v>58021</v>
+        <v>58023</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -12344,7 +12344,7 @@
         <v>136699222</v>
       </c>
       <c r="B105" t="n">
-        <v>58021</v>
+        <v>58023</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -12461,7 +12461,7 @@
         <v>136699223</v>
       </c>
       <c r="B106" t="n">
-        <v>58021</v>
+        <v>58023</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -12578,7 +12578,7 @@
         <v>136699229</v>
       </c>
       <c r="B107" t="n">
-        <v>58021</v>
+        <v>58023</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -12704,7 +12704,7 @@
         <v>136689339</v>
       </c>
       <c r="B108" t="n">
-        <v>57208</v>
+        <v>57210</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -13172,7 +13172,7 @@
         <v>136689332</v>
       </c>
       <c r="B112" t="n">
-        <v>58182</v>
+        <v>58184</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -13284,7 +13284,7 @@
         <v>136689326</v>
       </c>
       <c r="B113" t="n">
-        <v>58642</v>
+        <v>58644</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -13401,7 +13401,7 @@
         <v>136689334</v>
       </c>
       <c r="B114" t="n">
-        <v>58680</v>
+        <v>58682</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -14551,7 +14551,7 @@
         <v>136689325</v>
       </c>
       <c r="B124" t="n">
-        <v>8463</v>
+        <v>8464</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -14780,7 +14780,7 @@
         <v>136689348</v>
       </c>
       <c r="B126" t="n">
-        <v>108414</v>
+        <v>108416</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -14892,7 +14892,7 @@
         <v>136689336</v>
       </c>
       <c r="B127" t="n">
-        <v>108484</v>
+        <v>108486</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -15227,7 +15227,7 @@
         <v>136689318</v>
       </c>
       <c r="B130" t="n">
-        <v>98251</v>
+        <v>98253</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
@@ -15339,7 +15339,7 @@
         <v>136689331</v>
       </c>
       <c r="B131" t="n">
-        <v>98251</v>
+        <v>98253</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
@@ -15451,7 +15451,7 @@
         <v>136689342</v>
       </c>
       <c r="B132" t="n">
-        <v>98251</v>
+        <v>98253</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
@@ -15782,7 +15782,7 @@
         <v>136689346</v>
       </c>
       <c r="B135" t="n">
-        <v>104912</v>
+        <v>104914</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
@@ -15898,7 +15898,7 @@
         <v>136689350</v>
       </c>
       <c r="B136" t="n">
-        <v>104912</v>
+        <v>104914</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
@@ -16010,7 +16010,7 @@
         <v>136689358</v>
       </c>
       <c r="B137" t="n">
-        <v>104912</v>
+        <v>104914</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
@@ -16122,7 +16122,7 @@
         <v>136699224</v>
       </c>
       <c r="B138" t="n">
-        <v>104912</v>
+        <v>104914</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
@@ -16238,7 +16238,7 @@
         <v>136699225</v>
       </c>
       <c r="B139" t="n">
-        <v>104912</v>
+        <v>104914</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
@@ -16350,7 +16350,7 @@
         <v>136689352</v>
       </c>
       <c r="B140" t="n">
-        <v>99666</v>
+        <v>99668</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
@@ -16462,7 +16462,7 @@
         <v>136689353</v>
       </c>
       <c r="B141" t="n">
-        <v>99195</v>
+        <v>99197</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>

--- a/artfynd/A 20531-2025 artfynd.xlsx
+++ b/artfynd/A 20531-2025 artfynd.xlsx
@@ -12253,11 +12253,7 @@
         </is>
       </c>
       <c r="I104" t="inlineStr"/>
-      <c r="M104" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
+      <c r="M104" t="inlineStr"/>
       <c r="P104" t="inlineStr">
         <is>
           <t>Kölbron, Dlr</t>
@@ -12370,11 +12366,7 @@
         </is>
       </c>
       <c r="I105" t="inlineStr"/>
-      <c r="M105" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
+      <c r="M105" t="inlineStr"/>
       <c r="P105" t="inlineStr">
         <is>
           <t>Kölbron, Dlr</t>
@@ -12487,11 +12479,7 @@
         </is>
       </c>
       <c r="I106" t="inlineStr"/>
-      <c r="M106" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
+      <c r="M106" t="inlineStr"/>
       <c r="P106" t="inlineStr">
         <is>
           <t>Kölbron, Dlr</t>
@@ -12608,11 +12596,7 @@
           <t>2</t>
         </is>
       </c>
-      <c r="M107" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
+      <c r="M107" t="inlineStr"/>
       <c r="P107" t="inlineStr">
         <is>
           <t>Kölbron, Dlr</t>
@@ -12847,11 +12831,7 @@
         </is>
       </c>
       <c r="I109" t="inlineStr"/>
-      <c r="M109" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
+      <c r="M109" t="inlineStr"/>
       <c r="P109" t="inlineStr">
         <is>
           <t>Kölbron, Dlr</t>
@@ -13310,11 +13290,7 @@
         </is>
       </c>
       <c r="I113" t="inlineStr"/>
-      <c r="M113" t="inlineStr">
-        <is>
-          <t>sträckande</t>
-        </is>
-      </c>
+      <c r="M113" t="inlineStr"/>
       <c r="P113" t="inlineStr">
         <is>
           <t>Kölbron, Dlr</t>
@@ -13427,11 +13403,7 @@
         </is>
       </c>
       <c r="I114" t="inlineStr"/>
-      <c r="M114" t="inlineStr">
-        <is>
-          <t>förbiflygande</t>
-        </is>
-      </c>
+      <c r="M114" t="inlineStr"/>
       <c r="P114" t="inlineStr">
         <is>
           <t>Kölbron, Dlr</t>
@@ -13544,11 +13516,7 @@
         </is>
       </c>
       <c r="I115" t="inlineStr"/>
-      <c r="M115" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
+      <c r="M115" t="inlineStr"/>
       <c r="P115" t="inlineStr">
         <is>
           <t>Kölbron, Dlr</t>
@@ -14577,11 +14545,7 @@
         </is>
       </c>
       <c r="I124" t="inlineStr"/>
-      <c r="M124" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
+      <c r="M124" t="inlineStr"/>
       <c r="P124" t="inlineStr">
         <is>
           <t>Kölbron, Dlr</t>

--- a/artfynd/A 20531-2025 artfynd.xlsx
+++ b/artfynd/A 20531-2025 artfynd.xlsx
@@ -2204,7 +2204,7 @@
         <v>136689343</v>
       </c>
       <c r="B15" t="n">
-        <v>91921</v>
+        <v>91924</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2316,7 +2316,7 @@
         <v>136689338</v>
       </c>
       <c r="B16" t="n">
-        <v>93087</v>
+        <v>93090</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2428,7 +2428,7 @@
         <v>136689333</v>
       </c>
       <c r="B17" t="n">
-        <v>93115</v>
+        <v>93118</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2540,7 +2540,7 @@
         <v>136689344</v>
       </c>
       <c r="B18" t="n">
-        <v>93115</v>
+        <v>93118</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2652,7 +2652,7 @@
         <v>136689356</v>
       </c>
       <c r="B19" t="n">
-        <v>93115</v>
+        <v>93118</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2764,7 +2764,7 @@
         <v>136689357</v>
       </c>
       <c r="B20" t="n">
-        <v>93115</v>
+        <v>93118</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2880,7 +2880,7 @@
         <v>136689363</v>
       </c>
       <c r="B21" t="n">
-        <v>93115</v>
+        <v>93118</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2992,7 +2992,7 @@
         <v>136699216</v>
       </c>
       <c r="B22" t="n">
-        <v>93115</v>
+        <v>93118</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -10858,7 +10858,7 @@
         <v>136689345</v>
       </c>
       <c r="B92" t="n">
-        <v>83491</v>
+        <v>83494</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -10970,7 +10970,7 @@
         <v>136699227</v>
       </c>
       <c r="B93" t="n">
-        <v>83491</v>
+        <v>83494</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -14744,7 +14744,7 @@
         <v>136689348</v>
       </c>
       <c r="B126" t="n">
-        <v>108416</v>
+        <v>108421</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -14856,7 +14856,7 @@
         <v>136689336</v>
       </c>
       <c r="B127" t="n">
-        <v>108486</v>
+        <v>108491</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -15191,7 +15191,7 @@
         <v>136689318</v>
       </c>
       <c r="B130" t="n">
-        <v>98253</v>
+        <v>98256</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
@@ -15303,7 +15303,7 @@
         <v>136689331</v>
       </c>
       <c r="B131" t="n">
-        <v>98253</v>
+        <v>98256</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
@@ -15415,7 +15415,7 @@
         <v>136689342</v>
       </c>
       <c r="B132" t="n">
-        <v>98253</v>
+        <v>98256</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
@@ -15746,7 +15746,7 @@
         <v>136689346</v>
       </c>
       <c r="B135" t="n">
-        <v>104914</v>
+        <v>104917</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
@@ -15862,7 +15862,7 @@
         <v>136689350</v>
       </c>
       <c r="B136" t="n">
-        <v>104914</v>
+        <v>104917</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
@@ -15974,7 +15974,7 @@
         <v>136689358</v>
       </c>
       <c r="B137" t="n">
-        <v>104914</v>
+        <v>104917</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
@@ -16086,7 +16086,7 @@
         <v>136699224</v>
       </c>
       <c r="B138" t="n">
-        <v>104914</v>
+        <v>104917</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
@@ -16202,7 +16202,7 @@
         <v>136699225</v>
       </c>
       <c r="B139" t="n">
-        <v>104914</v>
+        <v>104917</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
@@ -16314,7 +16314,7 @@
         <v>136689352</v>
       </c>
       <c r="B140" t="n">
-        <v>99668</v>
+        <v>99671</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
@@ -16426,7 +16426,7 @@
         <v>136689353</v>
       </c>
       <c r="B141" t="n">
-        <v>99197</v>
+        <v>99200</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>

--- a/artfynd/A 20531-2025 artfynd.xlsx
+++ b/artfynd/A 20531-2025 artfynd.xlsx
@@ -2992,7 +2992,7 @@
         <v>136699216</v>
       </c>
       <c r="B22" t="n">
-        <v>93118</v>
+        <v>93128</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -10970,7 +10970,7 @@
         <v>136699227</v>
       </c>
       <c r="B93" t="n">
-        <v>83494</v>
+        <v>83504</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -12227,7 +12227,7 @@
         <v>136699220</v>
       </c>
       <c r="B104" t="n">
-        <v>58023</v>
+        <v>58033</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -12340,7 +12340,7 @@
         <v>136699222</v>
       </c>
       <c r="B105" t="n">
-        <v>58023</v>
+        <v>58033</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -12453,7 +12453,7 @@
         <v>136699223</v>
       </c>
       <c r="B106" t="n">
-        <v>58023</v>
+        <v>58033</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -12566,7 +12566,7 @@
         <v>136699229</v>
       </c>
       <c r="B107" t="n">
-        <v>58023</v>
+        <v>58033</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -16086,7 +16086,7 @@
         <v>136699224</v>
       </c>
       <c r="B138" t="n">
-        <v>104917</v>
+        <v>104936</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
@@ -16202,7 +16202,7 @@
         <v>136699225</v>
       </c>
       <c r="B139" t="n">
-        <v>104917</v>
+        <v>104936</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
